--- a/outputs/tables/tabla_dinamica_hotspots.xlsx
+++ b/outputs/tables/tabla_dinamica_hotspots.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="564">
   <si>
     <t>cod_subcircu</t>
   </si>
@@ -2097,10 +2097,10 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>3.89040179067335</v>
+        <v>3.297173999891045</v>
       </c>
       <c r="C2">
-        <v>3.89040179067335</v>
+        <v>3.297173999891045</v>
       </c>
       <c r="D2" t="s">
         <v>251</v>
@@ -2120,10 +2120,10 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>2.451098221118982</v>
+        <v>1.951687028201299</v>
       </c>
       <c r="C3">
-        <v>2.451098221118982</v>
+        <v>1.951687028201299</v>
       </c>
       <c r="D3" t="s">
         <v>251</v>
@@ -2143,10 +2143,10 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2.483015829243147</v>
+        <v>2.023133253806931</v>
       </c>
       <c r="C4">
-        <v>2.483015829243147</v>
+        <v>2.023133253806931</v>
       </c>
       <c r="D4" t="s">
         <v>251</v>
@@ -2166,10 +2166,10 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.8868820243229498</v>
+        <v>0.9885161641784795</v>
       </c>
       <c r="C5">
-        <v>0.8868820243229498</v>
+        <v>0.9885161641784795</v>
       </c>
       <c r="D5" t="s">
         <v>252</v>
@@ -2189,10 +2189,10 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>2.819200646008032</v>
+        <v>2.1826293124072</v>
       </c>
       <c r="C6">
-        <v>2.819200646008032</v>
+        <v>2.1826293124072</v>
       </c>
       <c r="D6" t="s">
         <v>251</v>
@@ -2212,10 +2212,10 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.603220421176321</v>
+        <v>0.5516000226888013</v>
       </c>
       <c r="C7">
-        <v>0.603220421176321</v>
+        <v>0.5516000226888013</v>
       </c>
       <c r="D7" t="s">
         <v>252</v>
@@ -2235,10 +2235,10 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>2.704109956653151</v>
+        <v>2.113843492718625</v>
       </c>
       <c r="C8">
-        <v>2.704109956653151</v>
+        <v>2.113843492718625</v>
       </c>
       <c r="D8" t="s">
         <v>251</v>
@@ -2258,10 +2258,10 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.899803223058107</v>
+        <v>0.7551769812447893</v>
       </c>
       <c r="C9">
-        <v>0.899803223058107</v>
+        <v>0.7551769812447893</v>
       </c>
       <c r="D9" t="s">
         <v>252</v>
@@ -2281,10 +2281,10 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>2.896092650030435</v>
+        <v>2.354285281895629</v>
       </c>
       <c r="C10">
-        <v>2.896092650030435</v>
+        <v>2.354285281895629</v>
       </c>
       <c r="D10" t="s">
         <v>251</v>
@@ -2304,13 +2304,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>1.336341647401659</v>
+        <v>1.120953674588055</v>
       </c>
       <c r="C11">
-        <v>1.336341647401659</v>
+        <v>1.120953674588055</v>
       </c>
       <c r="D11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E11" t="s">
         <v>262</v>
@@ -2327,10 +2327,10 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>1.129969882984609</v>
+        <v>0.9378634024017813</v>
       </c>
       <c r="C12">
-        <v>1.129969882984609</v>
+        <v>0.9378634024017813</v>
       </c>
       <c r="D12" t="s">
         <v>252</v>
@@ -2350,10 +2350,10 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.7513629162960719</v>
+        <v>0.7097971989287984</v>
       </c>
       <c r="C13">
-        <v>0.7513629162960719</v>
+        <v>0.7097971989287984</v>
       </c>
       <c r="D13" t="s">
         <v>252</v>
@@ -2373,10 +2373,10 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>2.949623253574014</v>
+        <v>2.295108353133979</v>
       </c>
       <c r="C14">
-        <v>2.949623253574014</v>
+        <v>2.295108353133979</v>
       </c>
       <c r="D14" t="s">
         <v>251</v>
@@ -2396,13 +2396,13 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>1.241570020054762</v>
+        <v>1.010736466878467</v>
       </c>
       <c r="C15">
-        <v>1.241570020054762</v>
+        <v>1.010736466878467</v>
       </c>
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E15" t="s">
         <v>266</v>
@@ -2419,10 +2419,10 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.6748306298242659</v>
+        <v>0.6583119128124297</v>
       </c>
       <c r="C16">
-        <v>0.6748306298242659</v>
+        <v>0.6583119128124297</v>
       </c>
       <c r="D16" t="s">
         <v>252</v>
@@ -2442,10 +2442,10 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.5923512186429392</v>
+        <v>0.6590451611698267</v>
       </c>
       <c r="C17">
-        <v>0.5923512186429392</v>
+        <v>0.6590451611698267</v>
       </c>
       <c r="D17" t="s">
         <v>252</v>
@@ -2465,10 +2465,10 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.32372717326998</v>
+        <v>0.3681664642687644</v>
       </c>
       <c r="C18">
-        <v>0.32372717326998</v>
+        <v>0.3681664642687644</v>
       </c>
       <c r="D18" t="s">
         <v>252</v>
@@ -2488,10 +2488,10 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.4015611042768785</v>
+        <v>0.4408410849449526</v>
       </c>
       <c r="C19">
-        <v>0.4015611042768785</v>
+        <v>0.4408410849449526</v>
       </c>
       <c r="D19" t="s">
         <v>252</v>
@@ -2511,10 +2511,10 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.3871682001817343</v>
+        <v>0.4558728267042159</v>
       </c>
       <c r="C20">
-        <v>0.3871682001817343</v>
+        <v>0.4558728267042159</v>
       </c>
       <c r="D20" t="s">
         <v>252</v>
@@ -2534,10 +2534,10 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.01385701803124605</v>
+        <v>0.1254085601523959</v>
       </c>
       <c r="C21">
-        <v>0.01385701803124605</v>
+        <v>0.1254085601523959</v>
       </c>
       <c r="D21" t="s">
         <v>252</v>
@@ -2557,10 +2557,10 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.01990448097592278</v>
+        <v>0.1296207798567628</v>
       </c>
       <c r="C22">
-        <v>0.01990448097592278</v>
+        <v>0.1296207798567628</v>
       </c>
       <c r="D22" t="s">
         <v>252</v>
@@ -2580,10 +2580,10 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.03808040857414949</v>
+        <v>0.1581457245871749</v>
       </c>
       <c r="C23">
-        <v>0.03808040857414949</v>
+        <v>0.1581457245871749</v>
       </c>
       <c r="D23" t="s">
         <v>252</v>
@@ -2603,10 +2603,10 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.03933880954266595</v>
+        <v>0.1594046967249186</v>
       </c>
       <c r="C24">
-        <v>0.03933880954266595</v>
+        <v>0.1594046967249186</v>
       </c>
       <c r="D24" t="s">
         <v>252</v>
@@ -2626,10 +2626,10 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.8097085422480874</v>
+        <v>0.8552854571170985</v>
       </c>
       <c r="C25">
-        <v>0.8097085422480874</v>
+        <v>0.8552854571170985</v>
       </c>
       <c r="D25" t="s">
         <v>252</v>
@@ -2649,10 +2649,10 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.966673545675947</v>
+        <v>0.9009845817659277</v>
       </c>
       <c r="C26">
-        <v>0.966673545675947</v>
+        <v>0.9009845817659277</v>
       </c>
       <c r="D26" t="s">
         <v>252</v>
@@ -2672,10 +2672,10 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>1.146149060340028</v>
+        <v>1.005114441989536</v>
       </c>
       <c r="C27">
-        <v>1.146149060340028</v>
+        <v>1.005114441989536</v>
       </c>
       <c r="D27" t="s">
         <v>252</v>
@@ -2695,10 +2695,10 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>1.838784731907037</v>
+        <v>1.561722461493026</v>
       </c>
       <c r="C28">
-        <v>1.838784731907037</v>
+        <v>1.561722461493026</v>
       </c>
       <c r="D28" t="s">
         <v>251</v>
@@ -2718,10 +2718,10 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.8197341124513993</v>
+        <v>0.7635492063859279</v>
       </c>
       <c r="C29">
-        <v>0.8197341124513993</v>
+        <v>0.7635492063859279</v>
       </c>
       <c r="D29" t="s">
         <v>252</v>
@@ -2741,10 +2741,10 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>2.123449879744237</v>
+        <v>1.624613533381907</v>
       </c>
       <c r="C30">
-        <v>2.123449879744237</v>
+        <v>1.624613533381907</v>
       </c>
       <c r="D30" t="s">
         <v>251</v>
@@ -2764,10 +2764,10 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>2.081294690764058</v>
+        <v>1.539841802840974</v>
       </c>
       <c r="C31">
-        <v>2.081294690764058</v>
+        <v>1.539841802840974</v>
       </c>
       <c r="D31" t="s">
         <v>251</v>
@@ -2787,10 +2787,10 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.4278612704777045</v>
+        <v>0.4105517291065681</v>
       </c>
       <c r="C32">
-        <v>0.4278612704777045</v>
+        <v>0.4105517291065681</v>
       </c>
       <c r="D32" t="s">
         <v>252</v>
@@ -2810,13 +2810,13 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>1.460444710168832</v>
+        <v>1.080545095889559</v>
       </c>
       <c r="C33">
-        <v>1.460444710168832</v>
+        <v>1.080545095889559</v>
       </c>
       <c r="D33" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E33" t="s">
         <v>284</v>
@@ -2833,10 +2833,10 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>2.470601548141173</v>
+        <v>1.881413442010019</v>
       </c>
       <c r="C34">
-        <v>2.470601548141173</v>
+        <v>1.881413442010019</v>
       </c>
       <c r="D34" t="s">
         <v>251</v>
@@ -2856,10 +2856,10 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>1.101616867350727</v>
+        <v>0.8870129026600648</v>
       </c>
       <c r="C35">
-        <v>1.101616867350727</v>
+        <v>0.8870129026600648</v>
       </c>
       <c r="D35" t="s">
         <v>252</v>
@@ -2879,10 +2879,10 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>3.240624977880871</v>
+        <v>2.298858853714695</v>
       </c>
       <c r="C36">
-        <v>3.240624977880871</v>
+        <v>2.298858853714695</v>
       </c>
       <c r="D36" t="s">
         <v>251</v>
@@ -2902,10 +2902,10 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>1.095054394244645</v>
+        <v>0.8428874435946355</v>
       </c>
       <c r="C37">
-        <v>1.095054394244645</v>
+        <v>0.8428874435946355</v>
       </c>
       <c r="D37" t="s">
         <v>252</v>
@@ -2925,10 +2925,10 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>2.226040841226418</v>
+        <v>1.621484436044065</v>
       </c>
       <c r="C38">
-        <v>2.226040841226418</v>
+        <v>1.621484436044065</v>
       </c>
       <c r="D38" t="s">
         <v>251</v>
@@ -2948,13 +2948,13 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>1.52806905513767</v>
+        <v>1.144177960975358</v>
       </c>
       <c r="C39">
-        <v>1.52806905513767</v>
+        <v>1.144177960975358</v>
       </c>
       <c r="D39" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E39" t="s">
         <v>290</v>
@@ -2971,10 +2971,10 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>1.75743080367983</v>
+        <v>1.357610882003726</v>
       </c>
       <c r="C40">
-        <v>1.75743080367983</v>
+        <v>1.357610882003726</v>
       </c>
       <c r="D40" t="s">
         <v>251</v>
@@ -2994,10 +2994,10 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>1.244591561882689</v>
+        <v>1.254833717355365</v>
       </c>
       <c r="C41">
-        <v>1.244591561882689</v>
+        <v>1.254833717355365</v>
       </c>
       <c r="D41" t="s">
         <v>251</v>
@@ -3017,10 +3017,10 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>2.259996799191557</v>
+        <v>1.588157448170999</v>
       </c>
       <c r="C42">
-        <v>2.259996799191557</v>
+        <v>1.588157448170999</v>
       </c>
       <c r="D42" t="s">
         <v>251</v>
@@ -3040,10 +3040,10 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>1.067478761208034</v>
+        <v>0.7976440048555848</v>
       </c>
       <c r="C43">
-        <v>1.067478761208034</v>
+        <v>0.7976440048555848</v>
       </c>
       <c r="D43" t="s">
         <v>252</v>
@@ -3063,10 +3063,10 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.3580029895384696</v>
+        <v>0.4224776582924136</v>
       </c>
       <c r="C44">
-        <v>0.3580029895384696</v>
+        <v>0.4224776582924136</v>
       </c>
       <c r="D44" t="s">
         <v>252</v>
@@ -3086,10 +3086,10 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.4360698842373428</v>
+        <v>0.4865161273710955</v>
       </c>
       <c r="C45">
-        <v>0.4360698842373428</v>
+        <v>0.4865161273710955</v>
       </c>
       <c r="D45" t="s">
         <v>252</v>
@@ -3109,10 +3109,10 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.3888000687387337</v>
+        <v>0.4802535898730681</v>
       </c>
       <c r="C46">
-        <v>0.3888000687387337</v>
+        <v>0.4802535898730681</v>
       </c>
       <c r="D46" t="s">
         <v>252</v>
@@ -3132,10 +3132,10 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.680616417008117</v>
+        <v>0.7236310321082501</v>
       </c>
       <c r="C47">
-        <v>0.680616417008117</v>
+        <v>0.7236310321082501</v>
       </c>
       <c r="D47" t="s">
         <v>252</v>
@@ -3155,10 +3155,10 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.1111461374110862</v>
+        <v>0.2445725831168871</v>
       </c>
       <c r="C48">
-        <v>0.1111461374110862</v>
+        <v>0.2445725831168871</v>
       </c>
       <c r="D48" t="s">
         <v>252</v>
@@ -3178,10 +3178,10 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.079727983072498</v>
+        <v>0.1863282553234051</v>
       </c>
       <c r="C49">
-        <v>0.079727983072498</v>
+        <v>0.1863282553234051</v>
       </c>
       <c r="D49" t="s">
         <v>252</v>
@@ -3201,10 +3201,10 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>0.1439313659647261</v>
+        <v>0.2345679198226612</v>
       </c>
       <c r="C50">
-        <v>0.1439313659647261</v>
+        <v>0.2345679198226612</v>
       </c>
       <c r="D50" t="s">
         <v>252</v>
@@ -3224,10 +3224,10 @@
         <v>56</v>
       </c>
       <c r="B51">
-        <v>0.5887083195650668</v>
+        <v>0.6649078868829655</v>
       </c>
       <c r="C51">
-        <v>0.5887083195650668</v>
+        <v>0.6649078868829655</v>
       </c>
       <c r="D51" t="s">
         <v>252</v>
@@ -3247,10 +3247,10 @@
         <v>57</v>
       </c>
       <c r="B52">
-        <v>0.1156325485156884</v>
+        <v>0.17454487677178</v>
       </c>
       <c r="C52">
-        <v>0.1156325485156884</v>
+        <v>0.17454487677178</v>
       </c>
       <c r="D52" t="s">
         <v>252</v>
@@ -3270,10 +3270,10 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>0.3106263106000643</v>
+        <v>0.3681225797818403</v>
       </c>
       <c r="C53">
-        <v>0.3106263106000643</v>
+        <v>0.3681225797818403</v>
       </c>
       <c r="D53" t="s">
         <v>252</v>
@@ -3293,10 +3293,10 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>0.2368221232154073</v>
+        <v>0.3065119725170509</v>
       </c>
       <c r="C54">
-        <v>0.2368221232154073</v>
+        <v>0.3065119725170509</v>
       </c>
       <c r="D54" t="s">
         <v>252</v>
@@ -3316,10 +3316,10 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>0.6023287508608397</v>
+        <v>0.67165584942253</v>
       </c>
       <c r="C55">
-        <v>0.6023287508608397</v>
+        <v>0.67165584942253</v>
       </c>
       <c r="D55" t="s">
         <v>252</v>
@@ -3339,10 +3339,10 @@
         <v>61</v>
       </c>
       <c r="B56">
-        <v>0.7067176544284611</v>
+        <v>0.6665161520988496</v>
       </c>
       <c r="C56">
-        <v>0.7067176544284611</v>
+        <v>0.6665161520988496</v>
       </c>
       <c r="D56" t="s">
         <v>252</v>
@@ -3362,10 +3362,10 @@
         <v>62</v>
       </c>
       <c r="B57">
-        <v>0.5282492162158343</v>
+        <v>0.5500379985247736</v>
       </c>
       <c r="C57">
-        <v>0.5282492162158343</v>
+        <v>0.5500379985247736</v>
       </c>
       <c r="D57" t="s">
         <v>252</v>
@@ -3385,10 +3385,10 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>0.2425954516603558</v>
+        <v>0.3402830537818915</v>
       </c>
       <c r="C58">
-        <v>0.2425954516603558</v>
+        <v>0.3402830537818915</v>
       </c>
       <c r="D58" t="s">
         <v>252</v>
@@ -3408,10 +3408,10 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>1.28913126015504</v>
+        <v>1.20161501879365</v>
       </c>
       <c r="C59">
-        <v>1.28913126015504</v>
+        <v>1.20161501879365</v>
       </c>
       <c r="D59" t="s">
         <v>251</v>
@@ -3431,10 +3431,10 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>0.4329863413675168</v>
+        <v>0.4663758170776857</v>
       </c>
       <c r="C60">
-        <v>0.4329863413675168</v>
+        <v>0.4663758170776857</v>
       </c>
       <c r="D60" t="s">
         <v>252</v>
@@ -3454,10 +3454,10 @@
         <v>66</v>
       </c>
       <c r="B61">
-        <v>0.9667614386798917</v>
+        <v>0.9049783635926023</v>
       </c>
       <c r="C61">
-        <v>0.9667614386798917</v>
+        <v>0.9049783635926023</v>
       </c>
       <c r="D61" t="s">
         <v>252</v>
@@ -3477,10 +3477,10 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>0.8669625311586899</v>
+        <v>0.7836563240848913</v>
       </c>
       <c r="C62">
-        <v>0.8669625311586899</v>
+        <v>0.7836563240848913</v>
       </c>
       <c r="D62" t="s">
         <v>252</v>
@@ -3500,10 +3500,10 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>0.5191529510311149</v>
+        <v>0.5140931127561927</v>
       </c>
       <c r="C63">
-        <v>0.5191529510311149</v>
+        <v>0.5140931127561927</v>
       </c>
       <c r="D63" t="s">
         <v>252</v>
@@ -3523,10 +3523,10 @@
         <v>69</v>
       </c>
       <c r="B64">
-        <v>0.6013602332797312</v>
+        <v>0.598007143711434</v>
       </c>
       <c r="C64">
-        <v>0.6013602332797312</v>
+        <v>0.598007143711434</v>
       </c>
       <c r="D64" t="s">
         <v>252</v>
@@ -3546,10 +3546,10 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>0.905558700006175</v>
+        <v>0.8484406267923688</v>
       </c>
       <c r="C65">
-        <v>0.905558700006175</v>
+        <v>0.8484406267923688</v>
       </c>
       <c r="D65" t="s">
         <v>252</v>
@@ -3569,10 +3569,10 @@
         <v>71</v>
       </c>
       <c r="B66">
-        <v>0.9577528195517254</v>
+        <v>0.820775685030958</v>
       </c>
       <c r="C66">
-        <v>0.9577528195517254</v>
+        <v>0.820775685030958</v>
       </c>
       <c r="D66" t="s">
         <v>252</v>
@@ -3592,10 +3592,10 @@
         <v>72</v>
       </c>
       <c r="B67">
-        <v>2.313553334963176</v>
+        <v>1.875270179428823</v>
       </c>
       <c r="C67">
-        <v>2.313553334963176</v>
+        <v>1.875270179428823</v>
       </c>
       <c r="D67" t="s">
         <v>251</v>
@@ -3615,10 +3615,10 @@
         <v>73</v>
       </c>
       <c r="B68">
-        <v>1.005619875036918</v>
+        <v>0.8652037997032342</v>
       </c>
       <c r="C68">
-        <v>1.005619875036918</v>
+        <v>0.8652037997032342</v>
       </c>
       <c r="D68" t="s">
         <v>252</v>
@@ -3638,13 +3638,13 @@
         <v>74</v>
       </c>
       <c r="B69">
-        <v>1.540020132218251</v>
+        <v>1.167655200140736</v>
       </c>
       <c r="C69">
-        <v>1.540020132218251</v>
+        <v>1.167655200140736</v>
       </c>
       <c r="D69" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E69" t="s">
         <v>320</v>
@@ -3661,10 +3661,10 @@
         <v>75</v>
       </c>
       <c r="B70">
-        <v>1.715212438641389</v>
+        <v>1.363450063127189</v>
       </c>
       <c r="C70">
-        <v>1.715212438641389</v>
+        <v>1.363450063127189</v>
       </c>
       <c r="D70" t="s">
         <v>251</v>
@@ -3684,10 +3684,10 @@
         <v>76</v>
       </c>
       <c r="B71">
-        <v>2.127185538149961</v>
+        <v>1.611424613069323</v>
       </c>
       <c r="C71">
-        <v>2.127185538149961</v>
+        <v>1.611424613069323</v>
       </c>
       <c r="D71" t="s">
         <v>251</v>
@@ -3707,10 +3707,10 @@
         <v>77</v>
       </c>
       <c r="B72">
-        <v>0.513612303711088</v>
+        <v>0.4833375476265242</v>
       </c>
       <c r="C72">
-        <v>0.513612303711088</v>
+        <v>0.4833375476265242</v>
       </c>
       <c r="D72" t="s">
         <v>252</v>
@@ -3730,10 +3730,10 @@
         <v>78</v>
       </c>
       <c r="B73">
-        <v>1.619745981368442</v>
+        <v>1.346530819642678</v>
       </c>
       <c r="C73">
-        <v>1.619745981368442</v>
+        <v>1.346530819642678</v>
       </c>
       <c r="D73" t="s">
         <v>251</v>
@@ -3753,13 +3753,13 @@
         <v>79</v>
       </c>
       <c r="B74">
-        <v>1.414399679393216</v>
+        <v>1.116031092758516</v>
       </c>
       <c r="C74">
-        <v>1.414399679393216</v>
+        <v>1.116031092758516</v>
       </c>
       <c r="D74" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E74" t="s">
         <v>325</v>
@@ -3776,10 +3776,10 @@
         <v>80</v>
       </c>
       <c r="B75">
-        <v>1.728099186689899</v>
+        <v>1.329911821546185</v>
       </c>
       <c r="C75">
-        <v>1.728099186689899</v>
+        <v>1.329911821546185</v>
       </c>
       <c r="D75" t="s">
         <v>251</v>
@@ -3799,10 +3799,10 @@
         <v>81</v>
       </c>
       <c r="B76">
-        <v>1.802295065179561</v>
+        <v>1.490929959248393</v>
       </c>
       <c r="C76">
-        <v>1.802295065179561</v>
+        <v>1.490929959248393</v>
       </c>
       <c r="D76" t="s">
         <v>251</v>
@@ -3822,10 +3822,10 @@
         <v>82</v>
       </c>
       <c r="B77">
-        <v>1.173732501805216</v>
+        <v>1.00906587477722</v>
       </c>
       <c r="C77">
-        <v>1.173732501805216</v>
+        <v>1.00906587477722</v>
       </c>
       <c r="D77" t="s">
         <v>252</v>
@@ -3845,10 +3845,10 @@
         <v>83</v>
       </c>
       <c r="B78">
-        <v>0.7102374302301487</v>
+        <v>0.6030189726361728</v>
       </c>
       <c r="C78">
-        <v>0.7102374302301487</v>
+        <v>0.6030189726361728</v>
       </c>
       <c r="D78" t="s">
         <v>252</v>
@@ -3868,10 +3868,10 @@
         <v>84</v>
       </c>
       <c r="B79">
-        <v>0.4374383806260368</v>
+        <v>0.3659499811391691</v>
       </c>
       <c r="C79">
-        <v>0.4374383806260368</v>
+        <v>0.3659499811391691</v>
       </c>
       <c r="D79" t="s">
         <v>252</v>
@@ -3891,10 +3891,10 @@
         <v>85</v>
       </c>
       <c r="B80">
-        <v>0.6888860307713423</v>
+        <v>0.6521481851543429</v>
       </c>
       <c r="C80">
-        <v>0.6888860307713423</v>
+        <v>0.6521481851543429</v>
       </c>
       <c r="D80" t="s">
         <v>252</v>
@@ -3914,10 +3914,10 @@
         <v>86</v>
       </c>
       <c r="B81">
-        <v>0.3802042798957102</v>
+        <v>0.3687230329412986</v>
       </c>
       <c r="C81">
-        <v>0.3802042798957102</v>
+        <v>0.3687230329412986</v>
       </c>
       <c r="D81" t="s">
         <v>252</v>
@@ -3937,13 +3937,13 @@
         <v>87</v>
       </c>
       <c r="B82">
-        <v>1.406558316064012</v>
+        <v>1.168042734047975</v>
       </c>
       <c r="C82">
-        <v>1.406558316064012</v>
+        <v>1.168042734047975</v>
       </c>
       <c r="D82" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E82" t="s">
         <v>333</v>
@@ -3960,13 +3960,13 @@
         <v>88</v>
       </c>
       <c r="B83">
-        <v>1.364707507236254</v>
+        <v>1.194954921144546</v>
       </c>
       <c r="C83">
-        <v>1.364707507236254</v>
+        <v>1.194954921144546</v>
       </c>
       <c r="D83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E83" t="s">
         <v>334</v>
@@ -3983,10 +3983,10 @@
         <v>89</v>
       </c>
       <c r="B84">
-        <v>1.621959564219518</v>
+        <v>1.30221716199086</v>
       </c>
       <c r="C84">
-        <v>1.621959564219518</v>
+        <v>1.30221716199086</v>
       </c>
       <c r="D84" t="s">
         <v>251</v>
@@ -4006,10 +4006,10 @@
         <v>90</v>
       </c>
       <c r="B85">
-        <v>1.858905103867289</v>
+        <v>1.550695168320296</v>
       </c>
       <c r="C85">
-        <v>1.858905103867289</v>
+        <v>1.550695168320296</v>
       </c>
       <c r="D85" t="s">
         <v>251</v>
@@ -4029,10 +4029,10 @@
         <v>91</v>
       </c>
       <c r="B86">
-        <v>0.9411016145698374</v>
+        <v>0.8096393617481863</v>
       </c>
       <c r="C86">
-        <v>0.9411016145698374</v>
+        <v>0.8096393617481863</v>
       </c>
       <c r="D86" t="s">
         <v>252</v>
@@ -4052,10 +4052,10 @@
         <v>92</v>
       </c>
       <c r="B87">
-        <v>1.054435714310517</v>
+        <v>0.951449725901565</v>
       </c>
       <c r="C87">
-        <v>1.054435714310517</v>
+        <v>0.951449725901565</v>
       </c>
       <c r="D87" t="s">
         <v>252</v>
@@ -4075,10 +4075,10 @@
         <v>93</v>
       </c>
       <c r="B88">
-        <v>1.948990868194439</v>
+        <v>1.48070341252915</v>
       </c>
       <c r="C88">
-        <v>1.948990868194439</v>
+        <v>1.48070341252915</v>
       </c>
       <c r="D88" t="s">
         <v>251</v>
@@ -4098,10 +4098,10 @@
         <v>94</v>
       </c>
       <c r="B89">
-        <v>2.519630948274375</v>
+        <v>1.977295530443556</v>
       </c>
       <c r="C89">
-        <v>2.519630948274375</v>
+        <v>1.977295530443556</v>
       </c>
       <c r="D89" t="s">
         <v>251</v>
@@ -4121,10 +4121,10 @@
         <v>95</v>
       </c>
       <c r="B90">
-        <v>1.576651570564114</v>
+        <v>1.240218885772566</v>
       </c>
       <c r="C90">
-        <v>1.576651570564114</v>
+        <v>1.240218885772566</v>
       </c>
       <c r="D90" t="s">
         <v>251</v>
@@ -4144,10 +4144,10 @@
         <v>96</v>
       </c>
       <c r="B91">
-        <v>0.8510095631957543</v>
+        <v>0.72419467717264</v>
       </c>
       <c r="C91">
-        <v>0.8510095631957543</v>
+        <v>0.72419467717264</v>
       </c>
       <c r="D91" t="s">
         <v>252</v>
@@ -4167,10 +4167,10 @@
         <v>97</v>
       </c>
       <c r="B92">
-        <v>1.917639154411906</v>
+        <v>1.307456276708541</v>
       </c>
       <c r="C92">
-        <v>1.917639154411906</v>
+        <v>1.307456276708541</v>
       </c>
       <c r="D92" t="s">
         <v>251</v>
@@ -4190,10 +4190,10 @@
         <v>98</v>
       </c>
       <c r="B93">
-        <v>2.215033562948325</v>
+        <v>1.632961284307301</v>
       </c>
       <c r="C93">
-        <v>2.215033562948325</v>
+        <v>1.632961284307301</v>
       </c>
       <c r="D93" t="s">
         <v>251</v>
@@ -4213,13 +4213,13 @@
         <v>99</v>
       </c>
       <c r="B94">
-        <v>1.287102387008164</v>
+        <v>1.058781381492569</v>
       </c>
       <c r="C94">
-        <v>1.287102387008164</v>
+        <v>1.058781381492569</v>
       </c>
       <c r="D94" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E94" t="s">
         <v>345</v>
@@ -4236,10 +4236,10 @@
         <v>100</v>
       </c>
       <c r="B95">
-        <v>0.6119415203360349</v>
+        <v>0.5148544671676737</v>
       </c>
       <c r="C95">
-        <v>0.6119415203360349</v>
+        <v>0.5148544671676737</v>
       </c>
       <c r="D95" t="s">
         <v>252</v>
@@ -4259,10 +4259,10 @@
         <v>101</v>
       </c>
       <c r="B96">
-        <v>1.700508275834245</v>
+        <v>1.379777881810632</v>
       </c>
       <c r="C96">
-        <v>1.700508275834245</v>
+        <v>1.379777881810632</v>
       </c>
       <c r="D96" t="s">
         <v>251</v>
@@ -4282,10 +4282,10 @@
         <v>102</v>
       </c>
       <c r="B97">
-        <v>0.1670328492883438</v>
+        <v>0.3131514789997867</v>
       </c>
       <c r="C97">
-        <v>0.1670328492883438</v>
+        <v>0.3131514789997867</v>
       </c>
       <c r="D97" t="s">
         <v>252</v>
@@ -4305,10 +4305,10 @@
         <v>103</v>
       </c>
       <c r="B98">
-        <v>0.1621662173256876</v>
+        <v>0.2968466506075073</v>
       </c>
       <c r="C98">
-        <v>0.1621662173256876</v>
+        <v>0.2968466506075073</v>
       </c>
       <c r="D98" t="s">
         <v>252</v>
@@ -4328,10 +4328,10 @@
         <v>104</v>
       </c>
       <c r="B99">
-        <v>0.1323875120026722</v>
+        <v>0.2573079431943824</v>
       </c>
       <c r="C99">
-        <v>0.1323875120026722</v>
+        <v>0.2573079431943824</v>
       </c>
       <c r="D99" t="s">
         <v>252</v>
@@ -4351,10 +4351,10 @@
         <v>105</v>
       </c>
       <c r="B100">
-        <v>0.1659147880222819</v>
+        <v>0.3060786344535934</v>
       </c>
       <c r="C100">
-        <v>0.1659147880222819</v>
+        <v>0.3060786344535934</v>
       </c>
       <c r="D100" t="s">
         <v>252</v>
@@ -4374,10 +4374,10 @@
         <v>106</v>
       </c>
       <c r="B101">
-        <v>0.1110870418964228</v>
+        <v>0.2390165273021266</v>
       </c>
       <c r="C101">
-        <v>0.1110870418964228</v>
+        <v>0.2390165273021266</v>
       </c>
       <c r="D101" t="s">
         <v>252</v>
@@ -4397,10 +4397,10 @@
         <v>107</v>
       </c>
       <c r="B102">
-        <v>0.3141694899333385</v>
+        <v>0.466551301890559</v>
       </c>
       <c r="C102">
-        <v>0.3141694899333385</v>
+        <v>0.466551301890559</v>
       </c>
       <c r="D102" t="s">
         <v>252</v>
@@ -4420,10 +4420,10 @@
         <v>108</v>
       </c>
       <c r="B103">
-        <v>0.1013921760601239</v>
+        <v>0.2187811037098076</v>
       </c>
       <c r="C103">
-        <v>0.1013921760601239</v>
+        <v>0.2187811037098076</v>
       </c>
       <c r="D103" t="s">
         <v>252</v>
@@ -4443,10 +4443,10 @@
         <v>109</v>
       </c>
       <c r="B104">
-        <v>0.05972694887996607</v>
+        <v>0.1800822122418989</v>
       </c>
       <c r="C104">
-        <v>0.05972694887996607</v>
+        <v>0.1800822122418989</v>
       </c>
       <c r="D104" t="s">
         <v>252</v>
@@ -4466,10 +4466,10 @@
         <v>110</v>
       </c>
       <c r="B105">
-        <v>0.3097108306749954</v>
+        <v>0.4641951140236773</v>
       </c>
       <c r="C105">
-        <v>0.3097108306749954</v>
+        <v>0.4641951140236773</v>
       </c>
       <c r="D105" t="s">
         <v>252</v>
@@ -4489,10 +4489,10 @@
         <v>111</v>
       </c>
       <c r="B106">
-        <v>0.1840406064350226</v>
+        <v>0.319903746295285</v>
       </c>
       <c r="C106">
-        <v>0.1840406064350226</v>
+        <v>0.319903746295285</v>
       </c>
       <c r="D106" t="s">
         <v>252</v>
@@ -4512,10 +4512,10 @@
         <v>112</v>
       </c>
       <c r="B107">
-        <v>0.1135673483107346</v>
+        <v>0.2253895341284574</v>
       </c>
       <c r="C107">
-        <v>0.1135673483107346</v>
+        <v>0.2253895341284574</v>
       </c>
       <c r="D107" t="s">
         <v>252</v>
@@ -4535,10 +4535,10 @@
         <v>113</v>
       </c>
       <c r="B108">
-        <v>0.5091245477766955</v>
+        <v>0.6195892245819334</v>
       </c>
       <c r="C108">
-        <v>0.5091245477766955</v>
+        <v>0.6195892245819334</v>
       </c>
       <c r="D108" t="s">
         <v>252</v>
@@ -4558,10 +4558,10 @@
         <v>114</v>
       </c>
       <c r="B109">
-        <v>0.5070083466499163</v>
+        <v>0.5893378122039625</v>
       </c>
       <c r="C109">
-        <v>0.5070083466499163</v>
+        <v>0.5893378122039625</v>
       </c>
       <c r="D109" t="s">
         <v>252</v>
@@ -4581,10 +4581,10 @@
         <v>115</v>
       </c>
       <c r="B110">
-        <v>0.5721334734089181</v>
+        <v>0.7197804593222257</v>
       </c>
       <c r="C110">
-        <v>0.5721334734089181</v>
+        <v>0.7197804593222257</v>
       </c>
       <c r="D110" t="s">
         <v>252</v>
@@ -4604,10 +4604,10 @@
         <v>116</v>
       </c>
       <c r="B111">
-        <v>0.1233752572789331</v>
+        <v>0.2200032391751138</v>
       </c>
       <c r="C111">
-        <v>0.1233752572789331</v>
+        <v>0.2200032391751138</v>
       </c>
       <c r="D111" t="s">
         <v>252</v>
@@ -4627,10 +4627,10 @@
         <v>117</v>
       </c>
       <c r="B112">
-        <v>0.1287379955821156</v>
+        <v>0.2222369021401799</v>
       </c>
       <c r="C112">
-        <v>0.1287379955821156</v>
+        <v>0.2222369021401799</v>
       </c>
       <c r="D112" t="s">
         <v>252</v>
@@ -4650,10 +4650,10 @@
         <v>118</v>
       </c>
       <c r="B113">
-        <v>0.1143518198937055</v>
+        <v>0.2218139778543431</v>
       </c>
       <c r="C113">
-        <v>0.1143518198937055</v>
+        <v>0.2218139778543431</v>
       </c>
       <c r="D113" t="s">
         <v>252</v>
@@ -4673,10 +4673,10 @@
         <v>119</v>
       </c>
       <c r="B114">
-        <v>0.1886112636818649</v>
+        <v>0.3036252447493155</v>
       </c>
       <c r="C114">
-        <v>0.1886112636818649</v>
+        <v>0.3036252447493155</v>
       </c>
       <c r="D114" t="s">
         <v>252</v>
@@ -4696,10 +4696,10 @@
         <v>120</v>
       </c>
       <c r="B115">
-        <v>0.2171777204495691</v>
+        <v>0.3433433055249128</v>
       </c>
       <c r="C115">
-        <v>0.2171777204495691</v>
+        <v>0.3433433055249128</v>
       </c>
       <c r="D115" t="s">
         <v>252</v>
@@ -4719,10 +4719,10 @@
         <v>121</v>
       </c>
       <c r="B116">
-        <v>0.1295958592395836</v>
+        <v>0.2602613410816455</v>
       </c>
       <c r="C116">
-        <v>0.1295958592395836</v>
+        <v>0.2602613410816455</v>
       </c>
       <c r="D116" t="s">
         <v>252</v>
@@ -4742,10 +4742,10 @@
         <v>122</v>
       </c>
       <c r="B117">
-        <v>0.109033476671113</v>
+        <v>0.2159238950116324</v>
       </c>
       <c r="C117">
-        <v>0.109033476671113</v>
+        <v>0.2159238950116324</v>
       </c>
       <c r="D117" t="s">
         <v>252</v>
@@ -4765,10 +4765,10 @@
         <v>123</v>
       </c>
       <c r="B118">
-        <v>0.1250655957215741</v>
+        <v>0.1941867638097169</v>
       </c>
       <c r="C118">
-        <v>0.1250655957215741</v>
+        <v>0.1941867638097169</v>
       </c>
       <c r="D118" t="s">
         <v>252</v>
@@ -4788,10 +4788,10 @@
         <v>124</v>
       </c>
       <c r="B119">
-        <v>0.131633394843825</v>
+        <v>0.2534141965724233</v>
       </c>
       <c r="C119">
-        <v>0.131633394843825</v>
+        <v>0.2534141965724233</v>
       </c>
       <c r="D119" t="s">
         <v>252</v>
@@ -4811,10 +4811,10 @@
         <v>125</v>
       </c>
       <c r="B120">
-        <v>0.2436280141615195</v>
+        <v>0.3865266611777778</v>
       </c>
       <c r="C120">
-        <v>0.2436280141615195</v>
+        <v>0.3865266611777778</v>
       </c>
       <c r="D120" t="s">
         <v>252</v>
@@ -4834,10 +4834,10 @@
         <v>126</v>
       </c>
       <c r="B121">
-        <v>0.2736894103029217</v>
+        <v>0.4390559432310531</v>
       </c>
       <c r="C121">
-        <v>0.2736894103029217</v>
+        <v>0.4390559432310531</v>
       </c>
       <c r="D121" t="s">
         <v>252</v>
@@ -4857,10 +4857,10 @@
         <v>127</v>
       </c>
       <c r="B122">
-        <v>0.2367665737931747</v>
+        <v>0.3825532123509178</v>
       </c>
       <c r="C122">
-        <v>0.2367665737931747</v>
+        <v>0.3825532123509178</v>
       </c>
       <c r="D122" t="s">
         <v>252</v>
@@ -4880,10 +4880,10 @@
         <v>128</v>
       </c>
       <c r="B123">
-        <v>0.08261146396111632</v>
+        <v>0.1715494415352036</v>
       </c>
       <c r="C123">
-        <v>0.08261146396111632</v>
+        <v>0.1715494415352036</v>
       </c>
       <c r="D123" t="s">
         <v>252</v>
@@ -4903,10 +4903,10 @@
         <v>129</v>
       </c>
       <c r="B124">
-        <v>0.1802261223195731</v>
+        <v>0.3046327674883141</v>
       </c>
       <c r="C124">
-        <v>0.1802261223195731</v>
+        <v>0.3046327674883141</v>
       </c>
       <c r="D124" t="s">
         <v>252</v>
@@ -4926,10 +4926,10 @@
         <v>130</v>
       </c>
       <c r="B125">
-        <v>0.1070679346586595</v>
+        <v>0.2161463463713901</v>
       </c>
       <c r="C125">
-        <v>0.1070679346586595</v>
+        <v>0.2161463463713901</v>
       </c>
       <c r="D125" t="s">
         <v>252</v>
@@ -4949,10 +4949,10 @@
         <v>131</v>
       </c>
       <c r="B126">
-        <v>0.402647232107051</v>
+        <v>0.5973649336307022</v>
       </c>
       <c r="C126">
-        <v>0.402647232107051</v>
+        <v>0.5973649336307022</v>
       </c>
       <c r="D126" t="s">
         <v>252</v>
@@ -4972,10 +4972,10 @@
         <v>132</v>
       </c>
       <c r="B127">
-        <v>0.04734042703085564</v>
+        <v>0.1734266660798341</v>
       </c>
       <c r="C127">
-        <v>0.04734042703085564</v>
+        <v>0.1734266660798341</v>
       </c>
       <c r="D127" t="s">
         <v>252</v>
@@ -4995,10 +4995,10 @@
         <v>133</v>
       </c>
       <c r="B128">
-        <v>0.04049744803993921</v>
+        <v>0.1647096964294844</v>
       </c>
       <c r="C128">
-        <v>0.04049744803993921</v>
+        <v>0.1647096964294844</v>
       </c>
       <c r="D128" t="s">
         <v>252</v>
@@ -5018,10 +5018,10 @@
         <v>134</v>
       </c>
       <c r="B129">
-        <v>0.06566994258956575</v>
+        <v>0.1761704169680019</v>
       </c>
       <c r="C129">
-        <v>0.06566994258956575</v>
+        <v>0.1761704169680019</v>
       </c>
       <c r="D129" t="s">
         <v>252</v>
@@ -5041,10 +5041,10 @@
         <v>135</v>
       </c>
       <c r="B130">
-        <v>0.06165971889621792</v>
+        <v>0.1722429524031946</v>
       </c>
       <c r="C130">
-        <v>0.06165971889621792</v>
+        <v>0.1722429524031946</v>
       </c>
       <c r="D130" t="s">
         <v>252</v>
@@ -5064,10 +5064,10 @@
         <v>136</v>
       </c>
       <c r="B131">
-        <v>0.1947509043944769</v>
+        <v>0.3308590192794425</v>
       </c>
       <c r="C131">
-        <v>0.1947509043944769</v>
+        <v>0.3308590192794425</v>
       </c>
       <c r="D131" t="s">
         <v>252</v>
@@ -5087,10 +5087,10 @@
         <v>137</v>
       </c>
       <c r="B132">
-        <v>0.06715495607990579</v>
+        <v>0.1657379992590396</v>
       </c>
       <c r="C132">
-        <v>0.06715495607990579</v>
+        <v>0.1657379992590396</v>
       </c>
       <c r="D132" t="s">
         <v>252</v>
@@ -5110,10 +5110,10 @@
         <v>138</v>
       </c>
       <c r="B133">
-        <v>0.9095498312432152</v>
+        <v>0.9604929381068512</v>
       </c>
       <c r="C133">
-        <v>0.9095498312432152</v>
+        <v>0.9604929381068512</v>
       </c>
       <c r="D133" t="s">
         <v>252</v>
@@ -5133,10 +5133,10 @@
         <v>139</v>
       </c>
       <c r="B134">
-        <v>0.0978544152118849</v>
+        <v>0.2136023882949683</v>
       </c>
       <c r="C134">
-        <v>0.0978544152118849</v>
+        <v>0.2136023882949683</v>
       </c>
       <c r="D134" t="s">
         <v>252</v>
@@ -5156,10 +5156,10 @@
         <v>140</v>
       </c>
       <c r="B135">
-        <v>0.2540036694337267</v>
+        <v>0.4188791746948259</v>
       </c>
       <c r="C135">
-        <v>0.2540036694337267</v>
+        <v>0.4188791746948259</v>
       </c>
       <c r="D135" t="s">
         <v>252</v>
@@ -5179,10 +5179,10 @@
         <v>141</v>
       </c>
       <c r="B136">
-        <v>0.1045865815550541</v>
+        <v>0.2531390517194896</v>
       </c>
       <c r="C136">
-        <v>0.1045865815550541</v>
+        <v>0.2531390517194896</v>
       </c>
       <c r="D136" t="s">
         <v>252</v>
@@ -5202,10 +5202,10 @@
         <v>142</v>
       </c>
       <c r="B137">
-        <v>0.063430275621043</v>
+        <v>0.1665947451761763</v>
       </c>
       <c r="C137">
-        <v>0.063430275621043</v>
+        <v>0.1665947451761763</v>
       </c>
       <c r="D137" t="s">
         <v>252</v>
@@ -5225,10 +5225,10 @@
         <v>143</v>
       </c>
       <c r="B138">
-        <v>0.04117814748569778</v>
+        <v>0.2034208260385811</v>
       </c>
       <c r="C138">
-        <v>0.04117814748569778</v>
+        <v>0.2034208260385811</v>
       </c>
       <c r="D138" t="s">
         <v>252</v>
@@ -5248,10 +5248,10 @@
         <v>144</v>
       </c>
       <c r="B139">
-        <v>0.3685273497050161</v>
+        <v>0.502290209393474</v>
       </c>
       <c r="C139">
-        <v>0.3685273497050161</v>
+        <v>0.502290209393474</v>
       </c>
       <c r="D139" t="s">
         <v>252</v>
@@ -5271,10 +5271,10 @@
         <v>145</v>
       </c>
       <c r="B140">
-        <v>0.1658640343345422</v>
+        <v>0.2968694617400232</v>
       </c>
       <c r="C140">
-        <v>0.1658640343345422</v>
+        <v>0.2968694617400232</v>
       </c>
       <c r="D140" t="s">
         <v>252</v>
@@ -5294,10 +5294,10 @@
         <v>146</v>
       </c>
       <c r="B141">
-        <v>0.100016658371323</v>
+        <v>0.2100973542289373</v>
       </c>
       <c r="C141">
-        <v>0.100016658371323</v>
+        <v>0.2100973542289373</v>
       </c>
       <c r="D141" t="s">
         <v>252</v>
@@ -5317,10 +5317,10 @@
         <v>147</v>
       </c>
       <c r="B142">
-        <v>0.3710887912065733</v>
+        <v>0.609415877442453</v>
       </c>
       <c r="C142">
-        <v>0.3710887912065733</v>
+        <v>0.609415877442453</v>
       </c>
       <c r="D142" t="s">
         <v>252</v>
@@ -5340,10 +5340,10 @@
         <v>148</v>
       </c>
       <c r="B143">
-        <v>0.4982174501224569</v>
+        <v>0.7092502755364898</v>
       </c>
       <c r="C143">
-        <v>0.4982174501224569</v>
+        <v>0.7092502755364898</v>
       </c>
       <c r="D143" t="s">
         <v>252</v>
@@ -5363,10 +5363,10 @@
         <v>149</v>
       </c>
       <c r="B144">
-        <v>0.1052353556863537</v>
+        <v>0.2161128012388492</v>
       </c>
       <c r="C144">
-        <v>0.1052353556863537</v>
+        <v>0.2161128012388492</v>
       </c>
       <c r="D144" t="s">
         <v>252</v>
@@ -5386,10 +5386,10 @@
         <v>150</v>
       </c>
       <c r="B145">
-        <v>0.9719464870068241</v>
+        <v>1.098465479909049</v>
       </c>
       <c r="C145">
-        <v>0.9719464870068241</v>
+        <v>1.098465479909049</v>
       </c>
       <c r="D145" t="s">
         <v>252</v>
@@ -5409,10 +5409,10 @@
         <v>151</v>
       </c>
       <c r="B146">
-        <v>0.5356987304775895</v>
+        <v>0.6751323758121949</v>
       </c>
       <c r="C146">
-        <v>0.5356987304775895</v>
+        <v>0.6751323758121949</v>
       </c>
       <c r="D146" t="s">
         <v>252</v>
@@ -5432,10 +5432,10 @@
         <v>152</v>
       </c>
       <c r="B147">
-        <v>0.08598453899966274</v>
+        <v>0.1613427037280464</v>
       </c>
       <c r="C147">
-        <v>0.08598453899966274</v>
+        <v>0.1613427037280464</v>
       </c>
       <c r="D147" t="s">
         <v>252</v>
@@ -5455,10 +5455,10 @@
         <v>153</v>
       </c>
       <c r="B148">
-        <v>0.1514911756343083</v>
+        <v>0.2016979271231993</v>
       </c>
       <c r="C148">
-        <v>0.1514911756343083</v>
+        <v>0.2016979271231993</v>
       </c>
       <c r="D148" t="s">
         <v>252</v>
@@ -5478,10 +5478,10 @@
         <v>154</v>
       </c>
       <c r="B149">
-        <v>0.4786068118056825</v>
+        <v>0.5417235115004537</v>
       </c>
       <c r="C149">
-        <v>0.4786068118056825</v>
+        <v>0.5417235115004537</v>
       </c>
       <c r="D149" t="s">
         <v>252</v>
@@ -5501,10 +5501,10 @@
         <v>155</v>
       </c>
       <c r="B150">
-        <v>1.100754570959786</v>
+        <v>1.169148967211045</v>
       </c>
       <c r="C150">
-        <v>1.100754570959786</v>
+        <v>1.169148967211045</v>
       </c>
       <c r="D150" t="s">
         <v>252</v>
@@ -5524,10 +5524,10 @@
         <v>156</v>
       </c>
       <c r="B151">
-        <v>0.5223778371619039</v>
+        <v>0.5254428931665969</v>
       </c>
       <c r="C151">
-        <v>0.5223778371619039</v>
+        <v>0.5254428931665969</v>
       </c>
       <c r="D151" t="s">
         <v>252</v>
@@ -5547,10 +5547,10 @@
         <v>157</v>
       </c>
       <c r="B152">
-        <v>0.2477589258517974</v>
+        <v>0.3695948127950857</v>
       </c>
       <c r="C152">
-        <v>0.2477589258517974</v>
+        <v>0.3695948127950857</v>
       </c>
       <c r="D152" t="s">
         <v>252</v>
@@ -5570,10 +5570,10 @@
         <v>158</v>
       </c>
       <c r="B153">
-        <v>0.2083520996869104</v>
+        <v>0.3155452858147467</v>
       </c>
       <c r="C153">
-        <v>0.2083520996869104</v>
+        <v>0.3155452858147467</v>
       </c>
       <c r="D153" t="s">
         <v>252</v>
@@ -5593,10 +5593,10 @@
         <v>159</v>
       </c>
       <c r="B154">
-        <v>0.1085038251145049</v>
+        <v>0.2164478847925181</v>
       </c>
       <c r="C154">
-        <v>0.1085038251145049</v>
+        <v>0.2164478847925181</v>
       </c>
       <c r="D154" t="s">
         <v>252</v>
@@ -5616,10 +5616,10 @@
         <v>160</v>
       </c>
       <c r="B155">
-        <v>0.4524918673134182</v>
+        <v>0.5903493376873458</v>
       </c>
       <c r="C155">
-        <v>0.4524918673134182</v>
+        <v>0.5903493376873458</v>
       </c>
       <c r="D155" t="s">
         <v>252</v>
@@ -5639,10 +5639,10 @@
         <v>161</v>
       </c>
       <c r="B156">
-        <v>1.380789548320954</v>
+        <v>1.326327330829845</v>
       </c>
       <c r="C156">
-        <v>1.380789548320954</v>
+        <v>1.326327330829845</v>
       </c>
       <c r="D156" t="s">
         <v>251</v>
@@ -5662,10 +5662,10 @@
         <v>162</v>
       </c>
       <c r="B157">
-        <v>0.4175118663582278</v>
+        <v>0.4684406890107497</v>
       </c>
       <c r="C157">
-        <v>0.4175118663582278</v>
+        <v>0.4684406890107497</v>
       </c>
       <c r="D157" t="s">
         <v>252</v>
@@ -5685,10 +5685,10 @@
         <v>163</v>
       </c>
       <c r="B158">
-        <v>0.440183144867361</v>
+        <v>0.483951057089578</v>
       </c>
       <c r="C158">
-        <v>0.440183144867361</v>
+        <v>0.483951057089578</v>
       </c>
       <c r="D158" t="s">
         <v>252</v>
@@ -5708,10 +5708,10 @@
         <v>164</v>
       </c>
       <c r="B159">
-        <v>0.8226788636294475</v>
+        <v>0.7464093754613894</v>
       </c>
       <c r="C159">
-        <v>0.8226788636294475</v>
+        <v>0.7464093754613894</v>
       </c>
       <c r="D159" t="s">
         <v>252</v>
@@ -5731,10 +5731,10 @@
         <v>165</v>
       </c>
       <c r="B160">
-        <v>1.437349685182509</v>
+        <v>1.289585902909272</v>
       </c>
       <c r="C160">
-        <v>1.437349685182509</v>
+        <v>1.289585902909272</v>
       </c>
       <c r="D160" t="s">
         <v>251</v>
@@ -5754,10 +5754,10 @@
         <v>166</v>
       </c>
       <c r="B161">
-        <v>0.4536695161526452</v>
+        <v>0.556244591313235</v>
       </c>
       <c r="C161">
-        <v>0.4536695161526452</v>
+        <v>0.556244591313235</v>
       </c>
       <c r="D161" t="s">
         <v>252</v>
@@ -5777,10 +5777,10 @@
         <v>167</v>
       </c>
       <c r="B162">
-        <v>1.631746715416664</v>
+        <v>1.62622438559785</v>
       </c>
       <c r="C162">
-        <v>1.631746715416664</v>
+        <v>1.62622438559785</v>
       </c>
       <c r="D162" t="s">
         <v>251</v>
@@ -5800,10 +5800,10 @@
         <v>168</v>
       </c>
       <c r="B163">
-        <v>1.147991824036969</v>
+        <v>1.150855009169258</v>
       </c>
       <c r="C163">
-        <v>1.147991824036969</v>
+        <v>1.150855009169258</v>
       </c>
       <c r="D163" t="s">
         <v>252</v>
@@ -5823,10 +5823,10 @@
         <v>169</v>
       </c>
       <c r="B164">
-        <v>0.6980603310293925</v>
+        <v>0.6685670989348809</v>
       </c>
       <c r="C164">
-        <v>0.6980603310293925</v>
+        <v>0.6685670989348809</v>
       </c>
       <c r="D164" t="s">
         <v>252</v>
@@ -5846,10 +5846,10 @@
         <v>170</v>
       </c>
       <c r="B165">
-        <v>0.300332082012111</v>
+        <v>0.3885807783693424</v>
       </c>
       <c r="C165">
-        <v>0.300332082012111</v>
+        <v>0.3885807783693424</v>
       </c>
       <c r="D165" t="s">
         <v>252</v>
@@ -5869,10 +5869,10 @@
         <v>171</v>
       </c>
       <c r="B166">
-        <v>0.3516635711503299</v>
+        <v>0.4230312944424679</v>
       </c>
       <c r="C166">
-        <v>0.3516635711503299</v>
+        <v>0.4230312944424679</v>
       </c>
       <c r="D166" t="s">
         <v>252</v>
@@ -5892,10 +5892,10 @@
         <v>172</v>
       </c>
       <c r="B167">
-        <v>0.318783589636461</v>
+        <v>0.4181083949139988</v>
       </c>
       <c r="C167">
-        <v>0.318783589636461</v>
+        <v>0.4181083949139988</v>
       </c>
       <c r="D167" t="s">
         <v>252</v>
@@ -5915,10 +5915,10 @@
         <v>173</v>
       </c>
       <c r="B168">
-        <v>0.2786207217392058</v>
+        <v>0.3616720314041254</v>
       </c>
       <c r="C168">
-        <v>0.2786207217392058</v>
+        <v>0.3616720314041254</v>
       </c>
       <c r="D168" t="s">
         <v>252</v>
@@ -5938,10 +5938,10 @@
         <v>174</v>
       </c>
       <c r="B169">
-        <v>0.2832644250894595</v>
+        <v>0.3446755389533725</v>
       </c>
       <c r="C169">
-        <v>0.2832644250894595</v>
+        <v>0.3446755389533725</v>
       </c>
       <c r="D169" t="s">
         <v>252</v>
@@ -5961,10 +5961,10 @@
         <v>175</v>
       </c>
       <c r="B170">
-        <v>0.3154107879888194</v>
+        <v>0.3217735891837091</v>
       </c>
       <c r="C170">
-        <v>0.3154107879888194</v>
+        <v>0.3217735891837091</v>
       </c>
       <c r="D170" t="s">
         <v>252</v>
@@ -5984,10 +5984,10 @@
         <v>176</v>
       </c>
       <c r="B171">
-        <v>0.1819352079495502</v>
+        <v>0.1988521865343649</v>
       </c>
       <c r="C171">
-        <v>0.1819352079495502</v>
+        <v>0.1988521865343649</v>
       </c>
       <c r="D171" t="s">
         <v>252</v>
@@ -6007,10 +6007,10 @@
         <v>177</v>
       </c>
       <c r="B172">
-        <v>0.5959292692978064</v>
+        <v>0.5689439639341153</v>
       </c>
       <c r="C172">
-        <v>0.5959292692978064</v>
+        <v>0.5689439639341153</v>
       </c>
       <c r="D172" t="s">
         <v>252</v>
@@ -6030,10 +6030,10 @@
         <v>178</v>
       </c>
       <c r="B173">
-        <v>0.5644958441606405</v>
+        <v>0.5696399271064999</v>
       </c>
       <c r="C173">
-        <v>0.5644958441606405</v>
+        <v>0.5696399271064999</v>
       </c>
       <c r="D173" t="s">
         <v>252</v>
@@ -6053,10 +6053,10 @@
         <v>179</v>
       </c>
       <c r="B174">
-        <v>0.7369642921553532</v>
+        <v>0.7976217783846491</v>
       </c>
       <c r="C174">
-        <v>0.7369642921553532</v>
+        <v>0.7976217783846491</v>
       </c>
       <c r="D174" t="s">
         <v>252</v>
@@ -6076,10 +6076,10 @@
         <v>180</v>
       </c>
       <c r="B175">
-        <v>1.119228653486176</v>
+        <v>0.9862697884587978</v>
       </c>
       <c r="C175">
-        <v>1.119228653486176</v>
+        <v>0.9862697884587978</v>
       </c>
       <c r="D175" t="s">
         <v>252</v>
@@ -6099,10 +6099,10 @@
         <v>181</v>
       </c>
       <c r="B176">
-        <v>1.159784102196596</v>
+        <v>1.070147019417754</v>
       </c>
       <c r="C176">
-        <v>1.159784102196596</v>
+        <v>1.070147019417754</v>
       </c>
       <c r="D176" t="s">
         <v>252</v>
@@ -6122,10 +6122,10 @@
         <v>182</v>
       </c>
       <c r="B177">
-        <v>2.402392272767671</v>
+        <v>1.884359081488862</v>
       </c>
       <c r="C177">
-        <v>2.402392272767671</v>
+        <v>1.884359081488862</v>
       </c>
       <c r="D177" t="s">
         <v>251</v>
@@ -6145,10 +6145,10 @@
         <v>183</v>
       </c>
       <c r="B178">
-        <v>1.144384723004465</v>
+        <v>0.9019259498410475</v>
       </c>
       <c r="C178">
-        <v>1.144384723004465</v>
+        <v>0.9019259498410475</v>
       </c>
       <c r="D178" t="s">
         <v>252</v>
@@ -6168,13 +6168,13 @@
         <v>184</v>
       </c>
       <c r="B179">
-        <v>1.341879515783484</v>
+        <v>1.179725002970204</v>
       </c>
       <c r="C179">
-        <v>1.341879515783484</v>
+        <v>1.179725002970204</v>
       </c>
       <c r="D179" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E179" t="s">
         <v>430</v>
@@ -6191,10 +6191,10 @@
         <v>185</v>
       </c>
       <c r="B180">
-        <v>0.7865117250594763</v>
+        <v>0.818210812776218</v>
       </c>
       <c r="C180">
-        <v>0.7865117250594763</v>
+        <v>0.818210812776218</v>
       </c>
       <c r="D180" t="s">
         <v>252</v>
@@ -6214,10 +6214,10 @@
         <v>186</v>
       </c>
       <c r="B181">
-        <v>0.691303709602735</v>
+        <v>0.6842416361882694</v>
       </c>
       <c r="C181">
-        <v>0.691303709602735</v>
+        <v>0.6842416361882694</v>
       </c>
       <c r="D181" t="s">
         <v>252</v>
@@ -6237,10 +6237,10 @@
         <v>187</v>
       </c>
       <c r="B182">
-        <v>0.7646665169192892</v>
+        <v>0.7388510472993535</v>
       </c>
       <c r="C182">
-        <v>0.7646665169192892</v>
+        <v>0.7388510472993535</v>
       </c>
       <c r="D182" t="s">
         <v>252</v>
@@ -6260,10 +6260,10 @@
         <v>188</v>
       </c>
       <c r="B183">
-        <v>2.360016704147423</v>
+        <v>2.14559469442563</v>
       </c>
       <c r="C183">
-        <v>2.360016704147423</v>
+        <v>2.14559469442563</v>
       </c>
       <c r="D183" t="s">
         <v>251</v>
@@ -6283,10 +6283,10 @@
         <v>189</v>
       </c>
       <c r="B184">
-        <v>1.759100153744908</v>
+        <v>1.586829791428348</v>
       </c>
       <c r="C184">
-        <v>1.759100153744908</v>
+        <v>1.586829791428348</v>
       </c>
       <c r="D184" t="s">
         <v>251</v>
@@ -6306,10 +6306,10 @@
         <v>190</v>
       </c>
       <c r="B185">
-        <v>0.09474429092142897</v>
+        <v>0.1614780333049499</v>
       </c>
       <c r="C185">
-        <v>0.09474429092142897</v>
+        <v>0.1614780333049499</v>
       </c>
       <c r="D185" t="s">
         <v>252</v>
@@ -6329,10 +6329,10 @@
         <v>191</v>
       </c>
       <c r="B186">
-        <v>0.1807507458217197</v>
+        <v>0.3188759614097341</v>
       </c>
       <c r="C186">
-        <v>0.1807507458217197</v>
+        <v>0.3188759614097341</v>
       </c>
       <c r="D186" t="s">
         <v>252</v>
@@ -6352,10 +6352,10 @@
         <v>192</v>
       </c>
       <c r="B187">
-        <v>0.2089180648495037</v>
+        <v>0.3013961929485604</v>
       </c>
       <c r="C187">
-        <v>0.2089180648495037</v>
+        <v>0.3013961929485604</v>
       </c>
       <c r="D187" t="s">
         <v>252</v>
@@ -6375,10 +6375,10 @@
         <v>193</v>
       </c>
       <c r="B188">
-        <v>0.4647343896456086</v>
+        <v>0.5104389663020492</v>
       </c>
       <c r="C188">
-        <v>0.4647343896456086</v>
+        <v>0.5104389663020492</v>
       </c>
       <c r="D188" t="s">
         <v>252</v>
@@ -6398,10 +6398,10 @@
         <v>194</v>
       </c>
       <c r="B189">
-        <v>1.87033207555329</v>
+        <v>1.475420576381739</v>
       </c>
       <c r="C189">
-        <v>1.87033207555329</v>
+        <v>1.475420576381739</v>
       </c>
       <c r="D189" t="s">
         <v>251</v>
@@ -6421,10 +6421,10 @@
         <v>195</v>
       </c>
       <c r="B190">
-        <v>3.742940087348431</v>
+        <v>2.923328151727987</v>
       </c>
       <c r="C190">
-        <v>3.742940087348431</v>
+        <v>2.923328151727987</v>
       </c>
       <c r="D190" t="s">
         <v>251</v>
@@ -6444,10 +6444,10 @@
         <v>196</v>
       </c>
       <c r="B191">
-        <v>3.064309154525343</v>
+        <v>2.397565674343954</v>
       </c>
       <c r="C191">
-        <v>3.064309154525343</v>
+        <v>2.397565674343954</v>
       </c>
       <c r="D191" t="s">
         <v>251</v>
@@ -6467,10 +6467,10 @@
         <v>197</v>
       </c>
       <c r="B192">
-        <v>1.991112455651511</v>
+        <v>1.563061655336474</v>
       </c>
       <c r="C192">
-        <v>1.991112455651511</v>
+        <v>1.563061655336474</v>
       </c>
       <c r="D192" t="s">
         <v>251</v>
@@ -6490,10 +6490,10 @@
         <v>198</v>
       </c>
       <c r="B193">
-        <v>0.3856327622545422</v>
+        <v>0.376688203544541</v>
       </c>
       <c r="C193">
-        <v>0.3856327622545422</v>
+        <v>0.376688203544541</v>
       </c>
       <c r="D193" t="s">
         <v>252</v>
@@ -6513,10 +6513,10 @@
         <v>199</v>
       </c>
       <c r="B194">
-        <v>3.645518172018442</v>
+        <v>3.80581278170723</v>
       </c>
       <c r="C194">
-        <v>3.645518172018442</v>
+        <v>3.80581278170723</v>
       </c>
       <c r="D194" t="s">
         <v>251</v>
@@ -6536,10 +6536,10 @@
         <v>200</v>
       </c>
       <c r="B195">
-        <v>0.09511702090021783</v>
+        <v>0.1981190112773145</v>
       </c>
       <c r="C195">
-        <v>0.09511702090021783</v>
+        <v>0.1981190112773145</v>
       </c>
       <c r="D195" t="s">
         <v>252</v>
@@ -6559,10 +6559,10 @@
         <v>201</v>
       </c>
       <c r="B196">
-        <v>0.27295406188244</v>
+        <v>0.406381757291338</v>
       </c>
       <c r="C196">
-        <v>0.27295406188244</v>
+        <v>0.406381757291338</v>
       </c>
       <c r="D196" t="s">
         <v>252</v>
@@ -6582,10 +6582,10 @@
         <v>202</v>
       </c>
       <c r="B197">
-        <v>0.2162034100581531</v>
+        <v>0.3518899322823309</v>
       </c>
       <c r="C197">
-        <v>0.2162034100581531</v>
+        <v>0.3518899322823309</v>
       </c>
       <c r="D197" t="s">
         <v>252</v>
@@ -6605,10 +6605,10 @@
         <v>203</v>
       </c>
       <c r="B198">
-        <v>0.417998542400099</v>
+        <v>0.6097859396082213</v>
       </c>
       <c r="C198">
-        <v>0.417998542400099</v>
+        <v>0.6097859396082213</v>
       </c>
       <c r="D198" t="s">
         <v>252</v>
@@ -6628,10 +6628,10 @@
         <v>204</v>
       </c>
       <c r="B199">
-        <v>0.2403035857995265</v>
+        <v>0.3996122299553391</v>
       </c>
       <c r="C199">
-        <v>0.2403035857995265</v>
+        <v>0.3996122299553391</v>
       </c>
       <c r="D199" t="s">
         <v>252</v>
@@ -6651,10 +6651,10 @@
         <v>205</v>
       </c>
       <c r="B200">
-        <v>1.16596464437327</v>
+        <v>1.045554335832944</v>
       </c>
       <c r="C200">
-        <v>1.16596464437327</v>
+        <v>1.045554335832944</v>
       </c>
       <c r="D200" t="s">
         <v>252</v>
@@ -6674,10 +6674,10 @@
         <v>206</v>
       </c>
       <c r="B201">
-        <v>4.096347082879531</v>
+        <v>3.283580159538675</v>
       </c>
       <c r="C201">
-        <v>4.096347082879531</v>
+        <v>3.283580159538675</v>
       </c>
       <c r="D201" t="s">
         <v>251</v>
@@ -6697,10 +6697,10 @@
         <v>207</v>
       </c>
       <c r="B202">
-        <v>2.829764462548432</v>
+        <v>2.507462909583045</v>
       </c>
       <c r="C202">
-        <v>2.829764462548432</v>
+        <v>2.507462909583045</v>
       </c>
       <c r="D202" t="s">
         <v>251</v>
@@ -6720,10 +6720,10 @@
         <v>208</v>
       </c>
       <c r="B203">
-        <v>2.482191652503703</v>
+        <v>1.913256730893455</v>
       </c>
       <c r="C203">
-        <v>2.482191652503703</v>
+        <v>1.913256730893455</v>
       </c>
       <c r="D203" t="s">
         <v>251</v>
@@ -6743,10 +6743,10 @@
         <v>209</v>
       </c>
       <c r="B204">
-        <v>2.660664586867846</v>
+        <v>2.126256744596708</v>
       </c>
       <c r="C204">
-        <v>2.660664586867846</v>
+        <v>2.126256744596708</v>
       </c>
       <c r="D204" t="s">
         <v>251</v>
@@ -6766,10 +6766,10 @@
         <v>210</v>
       </c>
       <c r="B205">
-        <v>2.745314697616455</v>
+        <v>2.067846362335033</v>
       </c>
       <c r="C205">
-        <v>2.745314697616455</v>
+        <v>2.067846362335033</v>
       </c>
       <c r="D205" t="s">
         <v>251</v>
@@ -6789,13 +6789,13 @@
         <v>211</v>
       </c>
       <c r="B206">
-        <v>1.411327558168296</v>
+        <v>1.119479338620849</v>
       </c>
       <c r="C206">
-        <v>1.411327558168296</v>
+        <v>1.119479338620849</v>
       </c>
       <c r="D206" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E206" t="s">
         <v>457</v>
@@ -6812,10 +6812,10 @@
         <v>212</v>
       </c>
       <c r="B207">
-        <v>2.715936541655879</v>
+        <v>2.009240498602042</v>
       </c>
       <c r="C207">
-        <v>2.715936541655879</v>
+        <v>2.009240498602042</v>
       </c>
       <c r="D207" t="s">
         <v>251</v>
@@ -6835,10 +6835,10 @@
         <v>213</v>
       </c>
       <c r="B208">
-        <v>2.134493556984296</v>
+        <v>1.652703653255336</v>
       </c>
       <c r="C208">
-        <v>2.134493556984296</v>
+        <v>1.652703653255336</v>
       </c>
       <c r="D208" t="s">
         <v>251</v>
@@ -6858,10 +6858,10 @@
         <v>214</v>
       </c>
       <c r="B209">
-        <v>2.683122059156792</v>
+        <v>2.168187659485925</v>
       </c>
       <c r="C209">
-        <v>2.683122059156792</v>
+        <v>2.168187659485925</v>
       </c>
       <c r="D209" t="s">
         <v>251</v>
@@ -6881,10 +6881,10 @@
         <v>215</v>
       </c>
       <c r="B210">
-        <v>3.931615259172553</v>
+        <v>2.839752059249172</v>
       </c>
       <c r="C210">
-        <v>3.931615259172553</v>
+        <v>2.839752059249172</v>
       </c>
       <c r="D210" t="s">
         <v>251</v>
@@ -6904,10 +6904,10 @@
         <v>216</v>
       </c>
       <c r="B211">
-        <v>2.033978903813767</v>
+        <v>1.809721902617147</v>
       </c>
       <c r="C211">
-        <v>2.033978903813767</v>
+        <v>1.809721902617147</v>
       </c>
       <c r="D211" t="s">
         <v>251</v>
@@ -6927,10 +6927,10 @@
         <v>217</v>
       </c>
       <c r="B212">
-        <v>0.1466935110305427</v>
+        <v>0.1981799572578488</v>
       </c>
       <c r="C212">
-        <v>0.1466935110305427</v>
+        <v>0.1981799572578488</v>
       </c>
       <c r="D212" t="s">
         <v>252</v>
@@ -6950,10 +6950,10 @@
         <v>218</v>
       </c>
       <c r="B213">
-        <v>0.175886739239405</v>
+        <v>0.276722096118986</v>
       </c>
       <c r="C213">
-        <v>0.175886739239405</v>
+        <v>0.276722096118986</v>
       </c>
       <c r="D213" t="s">
         <v>252</v>
@@ -6973,10 +6973,10 @@
         <v>219</v>
       </c>
       <c r="B214">
-        <v>0.07391856206352615</v>
+        <v>0.1617796573084457</v>
       </c>
       <c r="C214">
-        <v>0.07391856206352615</v>
+        <v>0.1617796573084457</v>
       </c>
       <c r="D214" t="s">
         <v>252</v>
@@ -6996,10 +6996,10 @@
         <v>220</v>
       </c>
       <c r="B215">
-        <v>0.3712196202298648</v>
+        <v>0.4997036294960714</v>
       </c>
       <c r="C215">
-        <v>0.3712196202298648</v>
+        <v>0.4997036294960714</v>
       </c>
       <c r="D215" t="s">
         <v>252</v>
@@ -7019,10 +7019,10 @@
         <v>221</v>
       </c>
       <c r="B216">
-        <v>0.4342657777957802</v>
+        <v>0.4485530365341921</v>
       </c>
       <c r="C216">
-        <v>0.4342657777957802</v>
+        <v>0.4485530365341921</v>
       </c>
       <c r="D216" t="s">
         <v>252</v>
@@ -7042,10 +7042,10 @@
         <v>222</v>
       </c>
       <c r="B217">
-        <v>1.325037744727902</v>
+        <v>1.21194703541521</v>
       </c>
       <c r="C217">
-        <v>1.325037744727902</v>
+        <v>1.21194703541521</v>
       </c>
       <c r="D217" t="s">
         <v>251</v>
@@ -7065,10 +7065,10 @@
         <v>223</v>
       </c>
       <c r="B218">
-        <v>2.477607409262046</v>
+        <v>2.017263891660435</v>
       </c>
       <c r="C218">
-        <v>2.477607409262046</v>
+        <v>2.017263891660435</v>
       </c>
       <c r="D218" t="s">
         <v>251</v>
@@ -7088,10 +7088,10 @@
         <v>224</v>
       </c>
       <c r="B219">
-        <v>0.1729873022874832</v>
+        <v>0.2506646509293406</v>
       </c>
       <c r="C219">
-        <v>0.1729873022874832</v>
+        <v>0.2506646509293406</v>
       </c>
       <c r="D219" t="s">
         <v>252</v>
@@ -7111,10 +7111,10 @@
         <v>225</v>
       </c>
       <c r="B220">
-        <v>2.406403683855669</v>
+        <v>2.166418301857287</v>
       </c>
       <c r="C220">
-        <v>2.406403683855669</v>
+        <v>2.166418301857287</v>
       </c>
       <c r="D220" t="s">
         <v>251</v>
@@ -7134,10 +7134,10 @@
         <v>226</v>
       </c>
       <c r="B221">
-        <v>0.7241758291760385</v>
+        <v>0.6748452468923527</v>
       </c>
       <c r="C221">
-        <v>0.7241758291760385</v>
+        <v>0.6748452468923527</v>
       </c>
       <c r="D221" t="s">
         <v>252</v>
@@ -7157,10 +7157,10 @@
         <v>227</v>
       </c>
       <c r="B222">
-        <v>0.1353251953595012</v>
+        <v>0.206241838924159</v>
       </c>
       <c r="C222">
-        <v>0.1353251953595012</v>
+        <v>0.206241838924159</v>
       </c>
       <c r="D222" t="s">
         <v>252</v>
@@ -7180,10 +7180,10 @@
         <v>228</v>
       </c>
       <c r="B223">
-        <v>0.2102015074516767</v>
+        <v>0.3128461833275324</v>
       </c>
       <c r="C223">
-        <v>0.2102015074516767</v>
+        <v>0.3128461833275324</v>
       </c>
       <c r="D223" t="s">
         <v>252</v>
@@ -7203,10 +7203,10 @@
         <v>229</v>
       </c>
       <c r="B224">
-        <v>0.1516293219959439</v>
+        <v>0.2657078875949781</v>
       </c>
       <c r="C224">
-        <v>0.1516293219959439</v>
+        <v>0.2657078875949781</v>
       </c>
       <c r="D224" t="s">
         <v>252</v>
@@ -7226,10 +7226,10 @@
         <v>230</v>
       </c>
       <c r="B225">
-        <v>1.041767683527171</v>
+        <v>1.157888166541531</v>
       </c>
       <c r="C225">
-        <v>1.041767683527171</v>
+        <v>1.157888166541531</v>
       </c>
       <c r="D225" t="s">
         <v>252</v>
@@ -7249,10 +7249,10 @@
         <v>231</v>
       </c>
       <c r="B226">
-        <v>0.1365822714292987</v>
+        <v>0.2546266230547727</v>
       </c>
       <c r="C226">
-        <v>0.1365822714292987</v>
+        <v>0.2546266230547727</v>
       </c>
       <c r="D226" t="s">
         <v>252</v>
@@ -7272,10 +7272,10 @@
         <v>232</v>
       </c>
       <c r="B227">
-        <v>0.3139088066593636</v>
+        <v>0.3845460706736431</v>
       </c>
       <c r="C227">
-        <v>0.3139088066593636</v>
+        <v>0.3845460706736431</v>
       </c>
       <c r="D227" t="s">
         <v>252</v>
@@ -7295,10 +7295,10 @@
         <v>233</v>
       </c>
       <c r="B228">
-        <v>1.717460387055564</v>
+        <v>1.53744586332613</v>
       </c>
       <c r="C228">
-        <v>1.717460387055564</v>
+        <v>1.53744586332613</v>
       </c>
       <c r="D228" t="s">
         <v>251</v>
@@ -7318,10 +7318,10 @@
         <v>234</v>
       </c>
       <c r="B229">
-        <v>2.47211161628411</v>
+        <v>1.901704016569898</v>
       </c>
       <c r="C229">
-        <v>2.47211161628411</v>
+        <v>1.901704016569898</v>
       </c>
       <c r="D229" t="s">
         <v>251</v>
@@ -7341,10 +7341,10 @@
         <v>235</v>
       </c>
       <c r="B230">
-        <v>4.024949990012017</v>
+        <v>2.847586156263175</v>
       </c>
       <c r="C230">
-        <v>4.024949990012017</v>
+        <v>2.847586156263175</v>
       </c>
       <c r="D230" t="s">
         <v>251</v>
@@ -7364,10 +7364,10 @@
         <v>236</v>
       </c>
       <c r="B231">
-        <v>0.577000738243307</v>
+        <v>0.5805746824975025</v>
       </c>
       <c r="C231">
-        <v>0.577000738243307</v>
+        <v>0.5805746824975025</v>
       </c>
       <c r="D231" t="s">
         <v>252</v>
@@ -7387,10 +7387,10 @@
         <v>237</v>
       </c>
       <c r="B232">
-        <v>0.2467334879631766</v>
+        <v>0.3938039788361174</v>
       </c>
       <c r="C232">
-        <v>0.2467334879631766</v>
+        <v>0.3938039788361174</v>
       </c>
       <c r="D232" t="s">
         <v>252</v>
@@ -7410,10 +7410,10 @@
         <v>238</v>
       </c>
       <c r="B233">
-        <v>0.5294346179776163</v>
+        <v>0.7627801047354767</v>
       </c>
       <c r="C233">
-        <v>0.5294346179776163</v>
+        <v>0.7627801047354767</v>
       </c>
       <c r="D233" t="s">
         <v>252</v>
@@ -7433,10 +7433,10 @@
         <v>239</v>
       </c>
       <c r="B234">
-        <v>0.1103862721504846</v>
+        <v>0.2389021043175681</v>
       </c>
       <c r="C234">
-        <v>0.1103862721504846</v>
+        <v>0.2389021043175681</v>
       </c>
       <c r="D234" t="s">
         <v>252</v>
@@ -7456,10 +7456,10 @@
         <v>240</v>
       </c>
       <c r="B235">
-        <v>0.04908803462063768</v>
+        <v>0.1462381381999354</v>
       </c>
       <c r="C235">
-        <v>0.04908803462063768</v>
+        <v>0.1462381381999354</v>
       </c>
       <c r="D235" t="s">
         <v>252</v>
@@ -7479,10 +7479,10 @@
         <v>241</v>
       </c>
       <c r="B236">
-        <v>0.1047580262859999</v>
+        <v>0.2426531155041098</v>
       </c>
       <c r="C236">
-        <v>0.1047580262859999</v>
+        <v>0.2426531155041098</v>
       </c>
       <c r="D236" t="s">
         <v>252</v>
@@ -7502,10 +7502,10 @@
         <v>242</v>
       </c>
       <c r="B237">
-        <v>0.2434957122640616</v>
+        <v>0.4031541354566255</v>
       </c>
       <c r="C237">
-        <v>0.2434957122640616</v>
+        <v>0.4031541354566255</v>
       </c>
       <c r="D237" t="s">
         <v>252</v>
@@ -7525,10 +7525,10 @@
         <v>243</v>
       </c>
       <c r="B238">
-        <v>1.00165725606164</v>
+        <v>1.141686886610116</v>
       </c>
       <c r="C238">
-        <v>1.00165725606164</v>
+        <v>1.141686886610116</v>
       </c>
       <c r="D238" t="s">
         <v>252</v>
@@ -7548,10 +7548,10 @@
         <v>244</v>
       </c>
       <c r="B239">
-        <v>0.07102519971562482</v>
+        <v>0.2151785004880436</v>
       </c>
       <c r="C239">
-        <v>0.07102519971562482</v>
+        <v>0.2151785004880436</v>
       </c>
       <c r="D239" t="s">
         <v>252</v>
@@ -7571,10 +7571,10 @@
         <v>245</v>
       </c>
       <c r="B240">
-        <v>1.731273680761678</v>
+        <v>2.682767748598091</v>
       </c>
       <c r="C240">
-        <v>1.731273680761678</v>
+        <v>2.682767748598091</v>
       </c>
       <c r="D240" t="s">
         <v>251</v>
@@ -7594,10 +7594,10 @@
         <v>246</v>
       </c>
       <c r="B241">
-        <v>1.472486176066294</v>
+        <v>3.194026854164585</v>
       </c>
       <c r="C241">
-        <v>1.472486176066294</v>
+        <v>3.194026854164585</v>
       </c>
       <c r="D241" t="s">
         <v>251</v>
@@ -7617,10 +7617,10 @@
         <v>247</v>
       </c>
       <c r="B242">
-        <v>0.1121689134593232</v>
+        <v>0.2895092210775965</v>
       </c>
       <c r="C242">
-        <v>0.1121689134593232</v>
+        <v>0.2895092210775965</v>
       </c>
       <c r="D242" t="s">
         <v>252</v>
@@ -7640,10 +7640,10 @@
         <v>248</v>
       </c>
       <c r="B243">
-        <v>0.121077514869134</v>
+        <v>0.2568121381485905</v>
       </c>
       <c r="C243">
-        <v>0.121077514869134</v>
+        <v>0.2568121381485905</v>
       </c>
       <c r="D243" t="s">
         <v>252</v>
@@ -7663,10 +7663,10 @@
         <v>249</v>
       </c>
       <c r="B244">
-        <v>0.1119423428362973</v>
+        <v>0.2365235031498298</v>
       </c>
       <c r="C244">
-        <v>0.1119423428362973</v>
+        <v>0.2365235031498298</v>
       </c>
       <c r="D244" t="s">
         <v>252</v>
@@ -7686,10 +7686,10 @@
         <v>250</v>
       </c>
       <c r="B245">
-        <v>0.1015775830865154</v>
+        <v>0.2639118563389303</v>
       </c>
       <c r="C245">
-        <v>0.1015775830865154</v>
+        <v>0.2639118563389303</v>
       </c>
       <c r="D245" t="s">
         <v>252</v>
@@ -7711,7 +7711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7739,68 +7739,68 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B2">
-        <v>4.096347082879531</v>
+        <v>3.80581278170723</v>
       </c>
       <c r="C2">
-        <v>4.096347082879531</v>
+        <v>3.80581278170723</v>
       </c>
       <c r="D2" t="s">
         <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>4.024949990012017</v>
+        <v>3.297173999891045</v>
       </c>
       <c r="C3">
-        <v>4.024949990012017</v>
+        <v>3.297173999891045</v>
       </c>
       <c r="D3" t="s">
         <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>481</v>
+        <v>253</v>
       </c>
       <c r="F3" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="G3" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B4">
-        <v>3.931615259172553</v>
+        <v>3.283580159538675</v>
       </c>
       <c r="C4">
-        <v>3.931615259172553</v>
+        <v>3.283580159538675</v>
       </c>
       <c r="D4" t="s">
         <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="F4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G4" t="s">
         <v>542</v>
@@ -7808,25 +7808,25 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>246</v>
       </c>
       <c r="B5">
-        <v>3.89040179067335</v>
+        <v>3.194026854164585</v>
       </c>
       <c r="C5">
-        <v>3.89040179067335</v>
+        <v>3.194026854164585</v>
       </c>
       <c r="D5" t="s">
         <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>253</v>
+        <v>492</v>
       </c>
       <c r="F5" t="s">
-        <v>497</v>
+        <v>553</v>
       </c>
       <c r="G5" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -7834,10 +7834,10 @@
         <v>195</v>
       </c>
       <c r="B6">
-        <v>3.742940087348431</v>
+        <v>2.923328151727987</v>
       </c>
       <c r="C6">
-        <v>3.742940087348431</v>
+        <v>2.923328151727987</v>
       </c>
       <c r="D6" t="s">
         <v>251</v>
@@ -7854,252 +7854,252 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="B7">
-        <v>3.645518172018442</v>
+        <v>2.847586156263175</v>
       </c>
       <c r="C7">
-        <v>3.645518172018442</v>
+        <v>2.847586156263175</v>
       </c>
       <c r="D7" t="s">
         <v>251</v>
       </c>
       <c r="E7" t="s">
-        <v>445</v>
+        <v>481</v>
       </c>
       <c r="F7" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="G7" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>215</v>
       </c>
       <c r="B8">
-        <v>3.240624977880871</v>
+        <v>2.839752059249172</v>
       </c>
       <c r="C8">
-        <v>3.240624977880871</v>
+        <v>2.839752059249172</v>
       </c>
       <c r="D8" t="s">
         <v>251</v>
       </c>
       <c r="E8" t="s">
-        <v>287</v>
+        <v>461</v>
       </c>
       <c r="F8" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="G8" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="B9">
-        <v>3.064309154525343</v>
+        <v>2.682767748598091</v>
       </c>
       <c r="C9">
-        <v>3.064309154525343</v>
+        <v>2.682767748598091</v>
       </c>
       <c r="D9" t="s">
         <v>251</v>
       </c>
       <c r="E9" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F9" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="G9" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>207</v>
       </c>
       <c r="B10">
-        <v>2.949623253574014</v>
+        <v>2.507462909583045</v>
       </c>
       <c r="C10">
-        <v>2.949623253574014</v>
+        <v>2.507462909583045</v>
       </c>
       <c r="D10" t="s">
         <v>251</v>
       </c>
       <c r="E10" t="s">
-        <v>265</v>
+        <v>453</v>
       </c>
       <c r="F10" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="G10" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="B11">
-        <v>2.896092650030435</v>
+        <v>2.397565674343954</v>
       </c>
       <c r="C11">
-        <v>2.896092650030435</v>
+        <v>2.397565674343954</v>
       </c>
       <c r="D11" t="s">
         <v>251</v>
       </c>
       <c r="E11" t="s">
-        <v>261</v>
+        <v>442</v>
       </c>
       <c r="F11" t="s">
-        <v>499</v>
+        <v>539</v>
       </c>
       <c r="G11" t="s">
-        <v>558</v>
+        <v>539</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>2.829764462548432</v>
+        <v>2.354285281895629</v>
       </c>
       <c r="C12">
-        <v>2.829764462548432</v>
+        <v>2.354285281895629</v>
       </c>
       <c r="D12" t="s">
         <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>453</v>
+        <v>261</v>
       </c>
       <c r="F12" t="s">
-        <v>542</v>
+        <v>499</v>
       </c>
       <c r="G12" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B13">
-        <v>2.819200646008032</v>
+        <v>2.298858853714695</v>
       </c>
       <c r="C13">
-        <v>2.819200646008032</v>
+        <v>2.298858853714695</v>
       </c>
       <c r="D13" t="s">
         <v>251</v>
       </c>
       <c r="E13" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="F13" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="G13" t="s">
-        <v>558</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>2.745314697616455</v>
+        <v>2.295108353133979</v>
       </c>
       <c r="C14">
-        <v>2.745314697616455</v>
+        <v>2.295108353133979</v>
       </c>
       <c r="D14" t="s">
         <v>251</v>
       </c>
       <c r="E14" t="s">
-        <v>456</v>
+        <v>265</v>
       </c>
       <c r="F14" t="s">
-        <v>543</v>
+        <v>500</v>
       </c>
       <c r="G14" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>212</v>
+        <v>11</v>
       </c>
       <c r="B15">
-        <v>2.715936541655879</v>
+        <v>2.1826293124072</v>
       </c>
       <c r="C15">
-        <v>2.715936541655879</v>
+        <v>2.1826293124072</v>
       </c>
       <c r="D15" t="s">
         <v>251</v>
       </c>
       <c r="E15" t="s">
-        <v>458</v>
+        <v>257</v>
       </c>
       <c r="F15" t="s">
-        <v>544</v>
+        <v>498</v>
       </c>
       <c r="G15" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="B16">
-        <v>2.704109956653151</v>
+        <v>2.168187659485925</v>
       </c>
       <c r="C16">
-        <v>2.704109956653151</v>
+        <v>2.168187659485925</v>
       </c>
       <c r="D16" t="s">
         <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>259</v>
+        <v>460</v>
       </c>
       <c r="F16" t="s">
-        <v>498</v>
+        <v>544</v>
       </c>
       <c r="G16" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B17">
-        <v>2.683122059156792</v>
+        <v>2.166418301857287</v>
       </c>
       <c r="C17">
-        <v>2.683122059156792</v>
+        <v>2.166418301857287</v>
       </c>
       <c r="D17" t="s">
         <v>251</v>
       </c>
       <c r="E17" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="F17" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G17" t="s">
         <v>542</v>
@@ -8107,68 +8107,68 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="B18">
-        <v>2.660664586867846</v>
+        <v>2.14559469442563</v>
       </c>
       <c r="C18">
-        <v>2.660664586867846</v>
+        <v>2.14559469442563</v>
       </c>
       <c r="D18" t="s">
         <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="F18" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="G18" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>209</v>
       </c>
       <c r="B19">
-        <v>2.519630948274375</v>
+        <v>2.126256744596708</v>
       </c>
       <c r="C19">
-        <v>2.519630948274375</v>
+        <v>2.126256744596708</v>
       </c>
       <c r="D19" t="s">
         <v>251</v>
       </c>
       <c r="E19" t="s">
-        <v>340</v>
+        <v>455</v>
       </c>
       <c r="F19" t="s">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="G19" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B20">
-        <v>2.483015829243147</v>
+        <v>2.113843492718625</v>
       </c>
       <c r="C20">
-        <v>2.483015829243147</v>
+        <v>2.113843492718625</v>
       </c>
       <c r="D20" t="s">
         <v>251</v>
       </c>
       <c r="E20" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F20" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G20" t="s">
         <v>558</v>
@@ -8176,19 +8176,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B21">
-        <v>2.482191652503703</v>
+        <v>2.067846362335033</v>
       </c>
       <c r="C21">
-        <v>2.482191652503703</v>
+        <v>2.067846362335033</v>
       </c>
       <c r="D21" t="s">
         <v>251</v>
       </c>
       <c r="E21" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F21" t="s">
         <v>543</v>
@@ -8199,45 +8199,45 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>223</v>
+        <v>9</v>
       </c>
       <c r="B22">
-        <v>2.477607409262046</v>
+        <v>2.023133253806931</v>
       </c>
       <c r="C22">
-        <v>2.477607409262046</v>
+        <v>2.023133253806931</v>
       </c>
       <c r="D22" t="s">
         <v>251</v>
       </c>
       <c r="E22" t="s">
-        <v>469</v>
+        <v>255</v>
       </c>
       <c r="F22" t="s">
-        <v>545</v>
+        <v>497</v>
       </c>
       <c r="G22" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B23">
-        <v>2.47211161628411</v>
+        <v>2.017263891660435</v>
       </c>
       <c r="C23">
-        <v>2.47211161628411</v>
+        <v>2.017263891660435</v>
       </c>
       <c r="D23" t="s">
         <v>251</v>
       </c>
       <c r="E23" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="F23" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G23" t="s">
         <v>542</v>
@@ -8245,160 +8245,160 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>212</v>
       </c>
       <c r="B24">
-        <v>2.470601548141173</v>
+        <v>2.009240498602042</v>
       </c>
       <c r="C24">
-        <v>2.470601548141173</v>
+        <v>2.009240498602042</v>
       </c>
       <c r="D24" t="s">
         <v>251</v>
       </c>
       <c r="E24" t="s">
-        <v>285</v>
+        <v>458</v>
       </c>
       <c r="F24" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="G24" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="B25">
-        <v>2.451098221118982</v>
+        <v>1.977295530443556</v>
       </c>
       <c r="C25">
-        <v>2.451098221118982</v>
+        <v>1.977295530443556</v>
       </c>
       <c r="D25" t="s">
         <v>251</v>
       </c>
       <c r="E25" t="s">
-        <v>254</v>
+        <v>340</v>
       </c>
       <c r="F25" t="s">
-        <v>497</v>
+        <v>519</v>
       </c>
       <c r="G25" t="s">
-        <v>558</v>
+        <v>518</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>225</v>
+        <v>8</v>
       </c>
       <c r="B26">
-        <v>2.406403683855669</v>
+        <v>1.951687028201299</v>
       </c>
       <c r="C26">
-        <v>2.406403683855669</v>
+        <v>1.951687028201299</v>
       </c>
       <c r="D26" t="s">
         <v>251</v>
       </c>
       <c r="E26" t="s">
-        <v>471</v>
+        <v>254</v>
       </c>
       <c r="F26" t="s">
-        <v>546</v>
+        <v>497</v>
       </c>
       <c r="G26" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="B27">
-        <v>2.402392272767671</v>
+        <v>1.913256730893455</v>
       </c>
       <c r="C27">
-        <v>2.402392272767671</v>
+        <v>1.913256730893455</v>
       </c>
       <c r="D27" t="s">
         <v>251</v>
       </c>
       <c r="E27" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="F27" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="G27" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="B28">
-        <v>2.360016704147423</v>
+        <v>1.901704016569898</v>
       </c>
       <c r="C28">
-        <v>2.360016704147423</v>
+        <v>1.901704016569898</v>
       </c>
       <c r="D28" t="s">
         <v>251</v>
       </c>
       <c r="E28" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
       <c r="F28" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="G28" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="B29">
-        <v>2.313553334963176</v>
+        <v>1.884359081488862</v>
       </c>
       <c r="C29">
-        <v>2.313553334963176</v>
+        <v>1.884359081488862</v>
       </c>
       <c r="D29" t="s">
         <v>251</v>
       </c>
       <c r="E29" t="s">
-        <v>318</v>
+        <v>428</v>
       </c>
       <c r="F29" t="s">
-        <v>513</v>
+        <v>536</v>
       </c>
       <c r="G29" t="s">
-        <v>510</v>
+        <v>539</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B30">
-        <v>2.259996799191557</v>
+        <v>1.881413442010019</v>
       </c>
       <c r="C30">
-        <v>2.259996799191557</v>
+        <v>1.881413442010019</v>
       </c>
       <c r="D30" t="s">
         <v>251</v>
       </c>
       <c r="E30" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F30" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G30" t="s">
         <v>503</v>
@@ -8406,48 +8406,48 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="B31">
-        <v>2.226040841226418</v>
+        <v>1.875270179428823</v>
       </c>
       <c r="C31">
-        <v>2.226040841226418</v>
+        <v>1.875270179428823</v>
       </c>
       <c r="D31" t="s">
         <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="F31" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="G31" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>216</v>
       </c>
       <c r="B32">
-        <v>2.215033562948325</v>
+        <v>1.809721902617147</v>
       </c>
       <c r="C32">
-        <v>2.215033562948325</v>
+        <v>1.809721902617147</v>
       </c>
       <c r="D32" t="s">
         <v>251</v>
       </c>
       <c r="E32" t="s">
-        <v>344</v>
+        <v>462</v>
       </c>
       <c r="F32" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="G32" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -8455,10 +8455,10 @@
         <v>213</v>
       </c>
       <c r="B33">
-        <v>2.134493556984296</v>
+        <v>1.652703653255336</v>
       </c>
       <c r="C33">
-        <v>2.134493556984296</v>
+        <v>1.652703653255336</v>
       </c>
       <c r="D33" t="s">
         <v>251</v>
@@ -8475,65 +8475,65 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="B34">
-        <v>2.127185538149961</v>
+        <v>1.632961284307301</v>
       </c>
       <c r="C34">
-        <v>2.127185538149961</v>
+        <v>1.632961284307301</v>
       </c>
       <c r="D34" t="s">
         <v>251</v>
       </c>
       <c r="E34" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="F34" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="G34" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="B35">
-        <v>2.123449879744237</v>
+        <v>1.62622438559785</v>
       </c>
       <c r="C35">
-        <v>2.123449879744237</v>
+        <v>1.62622438559785</v>
       </c>
       <c r="D35" t="s">
         <v>251</v>
       </c>
       <c r="E35" t="s">
-        <v>281</v>
+        <v>413</v>
       </c>
       <c r="F35" t="s">
-        <v>504</v>
+        <v>532</v>
       </c>
       <c r="G35" t="s">
-        <v>503</v>
+        <v>532</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>2.081294690764058</v>
+        <v>1.624613533381907</v>
       </c>
       <c r="C36">
-        <v>2.081294690764058</v>
+        <v>1.624613533381907</v>
       </c>
       <c r="D36" t="s">
         <v>251</v>
       </c>
       <c r="E36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F36" t="s">
         <v>504</v>
@@ -8544,111 +8544,111 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>216</v>
+        <v>43</v>
       </c>
       <c r="B37">
-        <v>2.033978903813767</v>
+        <v>1.621484436044065</v>
       </c>
       <c r="C37">
-        <v>2.033978903813767</v>
+        <v>1.621484436044065</v>
       </c>
       <c r="D37" t="s">
         <v>251</v>
       </c>
       <c r="E37" t="s">
-        <v>462</v>
+        <v>289</v>
       </c>
       <c r="F37" t="s">
-        <v>545</v>
+        <v>506</v>
       </c>
       <c r="G37" t="s">
-        <v>542</v>
+        <v>503</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="B38">
-        <v>1.991112455651511</v>
+        <v>1.611424613069323</v>
       </c>
       <c r="C38">
-        <v>1.991112455651511</v>
+        <v>1.611424613069323</v>
       </c>
       <c r="D38" t="s">
         <v>251</v>
       </c>
       <c r="E38" t="s">
-        <v>443</v>
+        <v>322</v>
       </c>
       <c r="F38" t="s">
-        <v>539</v>
+        <v>514</v>
       </c>
       <c r="G38" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="B39">
-        <v>1.948990868194439</v>
+        <v>1.588157448170999</v>
       </c>
       <c r="C39">
-        <v>1.948990868194439</v>
+        <v>1.588157448170999</v>
       </c>
       <c r="D39" t="s">
         <v>251</v>
       </c>
       <c r="E39" t="s">
-        <v>339</v>
+        <v>293</v>
       </c>
       <c r="F39" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="G39" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="B40">
-        <v>1.917639154411906</v>
+        <v>1.586829791428348</v>
       </c>
       <c r="C40">
-        <v>1.917639154411906</v>
+        <v>1.586829791428348</v>
       </c>
       <c r="D40" t="s">
         <v>251</v>
       </c>
       <c r="E40" t="s">
-        <v>343</v>
+        <v>435</v>
       </c>
       <c r="F40" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="G40" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B41">
-        <v>1.87033207555329</v>
+        <v>1.563061655336474</v>
       </c>
       <c r="C41">
-        <v>1.87033207555329</v>
+        <v>1.563061655336474</v>
       </c>
       <c r="D41" t="s">
         <v>251</v>
       </c>
       <c r="E41" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F41" t="s">
         <v>539</v>
@@ -8659,186 +8659,186 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="B42">
-        <v>1.858905103867289</v>
+        <v>1.561722461493026</v>
       </c>
       <c r="C42">
-        <v>1.858905103867289</v>
+        <v>1.561722461493026</v>
       </c>
       <c r="D42" t="s">
         <v>251</v>
       </c>
       <c r="E42" t="s">
-        <v>336</v>
+        <v>279</v>
       </c>
       <c r="F42" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="G42" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="B43">
-        <v>1.838784731907037</v>
+        <v>1.550695168320296</v>
       </c>
       <c r="C43">
-        <v>1.838784731907037</v>
+        <v>1.550695168320296</v>
       </c>
       <c r="D43" t="s">
         <v>251</v>
       </c>
       <c r="E43" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
       <c r="F43" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="G43" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="B44">
-        <v>1.802295065179561</v>
+        <v>1.539841802840974</v>
       </c>
       <c r="C44">
-        <v>1.802295065179561</v>
+        <v>1.539841802840974</v>
       </c>
       <c r="D44" t="s">
         <v>251</v>
       </c>
       <c r="E44" t="s">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="F44" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="G44" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="B45">
-        <v>1.759100153744908</v>
+        <v>1.53744586332613</v>
       </c>
       <c r="C45">
-        <v>1.759100153744908</v>
+        <v>1.53744586332613</v>
       </c>
       <c r="D45" t="s">
         <v>251</v>
       </c>
       <c r="E45" t="s">
-        <v>435</v>
+        <v>479</v>
       </c>
       <c r="F45" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="G45" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B46">
-        <v>1.75743080367983</v>
+        <v>1.490929959248393</v>
       </c>
       <c r="C46">
-        <v>1.75743080367983</v>
+        <v>1.490929959248393</v>
       </c>
       <c r="D46" t="s">
         <v>251</v>
       </c>
       <c r="E46" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="F46" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="G46" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>245</v>
+        <v>93</v>
       </c>
       <c r="B47">
-        <v>1.731273680761678</v>
+        <v>1.48070341252915</v>
       </c>
       <c r="C47">
-        <v>1.731273680761678</v>
+        <v>1.48070341252915</v>
       </c>
       <c r="D47" t="s">
         <v>251</v>
       </c>
       <c r="E47" t="s">
-        <v>491</v>
+        <v>339</v>
       </c>
       <c r="F47" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="G47" t="s">
-        <v>553</v>
+        <v>518</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="B48">
-        <v>1.728099186689899</v>
+        <v>1.475420576381739</v>
       </c>
       <c r="C48">
-        <v>1.728099186689899</v>
+        <v>1.475420576381739</v>
       </c>
       <c r="D48" t="s">
         <v>251</v>
       </c>
       <c r="E48" t="s">
-        <v>326</v>
+        <v>440</v>
       </c>
       <c r="F48" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="G48" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>233</v>
+        <v>101</v>
       </c>
       <c r="B49">
-        <v>1.717460387055564</v>
+        <v>1.379777881810632</v>
       </c>
       <c r="C49">
-        <v>1.717460387055564</v>
+        <v>1.379777881810632</v>
       </c>
       <c r="D49" t="s">
         <v>251</v>
       </c>
       <c r="E49" t="s">
-        <v>479</v>
+        <v>347</v>
       </c>
       <c r="F49" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="G49" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -8846,10 +8846,10 @@
         <v>75</v>
       </c>
       <c r="B50">
-        <v>1.715212438641389</v>
+        <v>1.363450063127189</v>
       </c>
       <c r="C50">
-        <v>1.715212438641389</v>
+        <v>1.363450063127189</v>
       </c>
       <c r="D50" t="s">
         <v>251</v>
@@ -8866,68 +8866,68 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="B51">
-        <v>1.700508275834245</v>
+        <v>1.357610882003726</v>
       </c>
       <c r="C51">
-        <v>1.700508275834245</v>
+        <v>1.357610882003726</v>
       </c>
       <c r="D51" t="s">
         <v>251</v>
       </c>
       <c r="E51" t="s">
-        <v>347</v>
+        <v>291</v>
       </c>
       <c r="F51" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="G51" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="B52">
-        <v>1.631746715416664</v>
+        <v>1.346530819642678</v>
       </c>
       <c r="C52">
-        <v>1.631746715416664</v>
+        <v>1.346530819642678</v>
       </c>
       <c r="D52" t="s">
         <v>251</v>
       </c>
       <c r="E52" t="s">
-        <v>413</v>
+        <v>324</v>
       </c>
       <c r="F52" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="G52" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B53">
-        <v>1.621959564219518</v>
+        <v>1.329911821546185</v>
       </c>
       <c r="C53">
-        <v>1.621959564219518</v>
+        <v>1.329911821546185</v>
       </c>
       <c r="D53" t="s">
         <v>251</v>
       </c>
       <c r="E53" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="F53" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G53" t="s">
         <v>518</v>
@@ -8935,45 +8935,45 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="B54">
-        <v>1.619745981368442</v>
+        <v>1.326327330829845</v>
       </c>
       <c r="C54">
-        <v>1.619745981368442</v>
+        <v>1.326327330829845</v>
       </c>
       <c r="D54" t="s">
         <v>251</v>
       </c>
       <c r="E54" t="s">
-        <v>324</v>
+        <v>407</v>
       </c>
       <c r="F54" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="G54" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B55">
-        <v>1.576651570564114</v>
+        <v>1.307456276708541</v>
       </c>
       <c r="C55">
-        <v>1.576651570564114</v>
+        <v>1.307456276708541</v>
       </c>
       <c r="D55" t="s">
         <v>251</v>
       </c>
       <c r="E55" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F55" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G55" t="s">
         <v>518</v>
@@ -8981,393 +8981,140 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B56">
-        <v>1.540020132218251</v>
+        <v>1.30221716199086</v>
       </c>
       <c r="C56">
-        <v>1.540020132218251</v>
+        <v>1.30221716199086</v>
       </c>
       <c r="D56" t="s">
         <v>251</v>
       </c>
       <c r="E56" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="F56" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="G56" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="B57">
-        <v>1.52806905513767</v>
+        <v>1.289585902909272</v>
       </c>
       <c r="C57">
-        <v>1.52806905513767</v>
+        <v>1.289585902909272</v>
       </c>
       <c r="D57" t="s">
         <v>251</v>
       </c>
       <c r="E57" t="s">
-        <v>290</v>
+        <v>411</v>
       </c>
       <c r="F57" t="s">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="G57" t="s">
-        <v>503</v>
+        <v>532</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>246</v>
+        <v>46</v>
       </c>
       <c r="B58">
-        <v>1.472486176066294</v>
+        <v>1.254833717355365</v>
       </c>
       <c r="C58">
-        <v>1.472486176066294</v>
+        <v>1.254833717355365</v>
       </c>
       <c r="D58" t="s">
         <v>251</v>
       </c>
       <c r="E58" t="s">
-        <v>492</v>
+        <v>292</v>
       </c>
       <c r="F58" t="s">
-        <v>553</v>
+        <v>507</v>
       </c>
       <c r="G58" t="s">
-        <v>553</v>
+        <v>503</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="B59">
-        <v>1.460444710168832</v>
+        <v>1.240218885772566</v>
       </c>
       <c r="C59">
-        <v>1.460444710168832</v>
+        <v>1.240218885772566</v>
       </c>
       <c r="D59" t="s">
         <v>251</v>
       </c>
       <c r="E59" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="F59" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="G59" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="B60">
-        <v>1.437349685182509</v>
+        <v>1.21194703541521</v>
       </c>
       <c r="C60">
-        <v>1.437349685182509</v>
+        <v>1.21194703541521</v>
       </c>
       <c r="D60" t="s">
         <v>251</v>
       </c>
       <c r="E60" t="s">
-        <v>411</v>
+        <v>468</v>
       </c>
       <c r="F60" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="G60" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B61">
-        <v>1.414399679393216</v>
+        <v>1.20161501879365</v>
       </c>
       <c r="C61">
-        <v>1.414399679393216</v>
+        <v>1.20161501879365</v>
       </c>
       <c r="D61" t="s">
         <v>251</v>
       </c>
       <c r="E61" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="F61" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G61" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" t="s">
-        <v>211</v>
-      </c>
-      <c r="B62">
-        <v>1.411327558168296</v>
-      </c>
-      <c r="C62">
-        <v>1.411327558168296</v>
-      </c>
-      <c r="D62" t="s">
-        <v>251</v>
-      </c>
-      <c r="E62" t="s">
-        <v>457</v>
-      </c>
-      <c r="F62" t="s">
-        <v>543</v>
-      </c>
-      <c r="G62" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" t="s">
-        <v>87</v>
-      </c>
-      <c r="B63">
-        <v>1.406558316064012</v>
-      </c>
-      <c r="C63">
-        <v>1.406558316064012</v>
-      </c>
-      <c r="D63" t="s">
-        <v>251</v>
-      </c>
-      <c r="E63" t="s">
-        <v>333</v>
-      </c>
-      <c r="F63" t="s">
-        <v>517</v>
-      </c>
-      <c r="G63" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" t="s">
-        <v>161</v>
-      </c>
-      <c r="B64">
-        <v>1.380789548320954</v>
-      </c>
-      <c r="C64">
-        <v>1.380789548320954</v>
-      </c>
-      <c r="D64" t="s">
-        <v>251</v>
-      </c>
-      <c r="E64" t="s">
-        <v>407</v>
-      </c>
-      <c r="F64" t="s">
-        <v>531</v>
-      </c>
-      <c r="G64" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" t="s">
-        <v>88</v>
-      </c>
-      <c r="B65">
-        <v>1.364707507236254</v>
-      </c>
-      <c r="C65">
-        <v>1.364707507236254</v>
-      </c>
-      <c r="D65" t="s">
-        <v>251</v>
-      </c>
-      <c r="E65" t="s">
-        <v>334</v>
-      </c>
-      <c r="F65" t="s">
-        <v>517</v>
-      </c>
-      <c r="G65" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" t="s">
-        <v>184</v>
-      </c>
-      <c r="B66">
-        <v>1.341879515783484</v>
-      </c>
-      <c r="C66">
-        <v>1.341879515783484</v>
-      </c>
-      <c r="D66" t="s">
-        <v>251</v>
-      </c>
-      <c r="E66" t="s">
-        <v>430</v>
-      </c>
-      <c r="F66" t="s">
-        <v>536</v>
-      </c>
-      <c r="G66" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" t="s">
-        <v>16</v>
-      </c>
-      <c r="B67">
-        <v>1.336341647401659</v>
-      </c>
-      <c r="C67">
-        <v>1.336341647401659</v>
-      </c>
-      <c r="D67" t="s">
-        <v>251</v>
-      </c>
-      <c r="E67" t="s">
-        <v>262</v>
-      </c>
-      <c r="F67" t="s">
-        <v>499</v>
-      </c>
-      <c r="G67" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" t="s">
-        <v>222</v>
-      </c>
-      <c r="B68">
-        <v>1.325037744727902</v>
-      </c>
-      <c r="C68">
-        <v>1.325037744727902</v>
-      </c>
-      <c r="D68" t="s">
-        <v>251</v>
-      </c>
-      <c r="E68" t="s">
-        <v>468</v>
-      </c>
-      <c r="F68" t="s">
-        <v>545</v>
-      </c>
-      <c r="G68" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" t="s">
-        <v>64</v>
-      </c>
-      <c r="B69">
-        <v>1.28913126015504</v>
-      </c>
-      <c r="C69">
-        <v>1.28913126015504</v>
-      </c>
-      <c r="D69" t="s">
-        <v>251</v>
-      </c>
-      <c r="E69" t="s">
-        <v>310</v>
-      </c>
-      <c r="F69" t="s">
-        <v>511</v>
-      </c>
-      <c r="G69" t="s">
         <v>510</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" t="s">
-        <v>99</v>
-      </c>
-      <c r="B70">
-        <v>1.287102387008164</v>
-      </c>
-      <c r="C70">
-        <v>1.287102387008164</v>
-      </c>
-      <c r="D70" t="s">
-        <v>251</v>
-      </c>
-      <c r="E70" t="s">
-        <v>345</v>
-      </c>
-      <c r="F70" t="s">
-        <v>520</v>
-      </c>
-      <c r="G70" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" t="s">
-        <v>46</v>
-      </c>
-      <c r="B71">
-        <v>1.244591561882689</v>
-      </c>
-      <c r="C71">
-        <v>1.244591561882689</v>
-      </c>
-      <c r="D71" t="s">
-        <v>251</v>
-      </c>
-      <c r="E71" t="s">
-        <v>292</v>
-      </c>
-      <c r="F71" t="s">
-        <v>507</v>
-      </c>
-      <c r="G71" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" t="s">
-        <v>20</v>
-      </c>
-      <c r="B72">
-        <v>1.241570020054762</v>
-      </c>
-      <c r="C72">
-        <v>1.241570020054762</v>
-      </c>
-      <c r="D72" t="s">
-        <v>251</v>
-      </c>
-      <c r="E72" t="s">
-        <v>266</v>
-      </c>
-      <c r="F72" t="s">
-        <v>500</v>
-      </c>
-      <c r="G72" t="s">
-        <v>558</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_dinamica_hotspots.xlsx
+++ b/outputs/tables/tabla_dinamica_hotspots.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="564">
   <si>
     <t>cod_subcircu</t>
   </si>
@@ -2097,10 +2097,10 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>3.297173999891045</v>
+        <v>4.076886631703029</v>
       </c>
       <c r="C2">
-        <v>3.297173999891045</v>
+        <v>4.076886631703029</v>
       </c>
       <c r="D2" t="s">
         <v>251</v>
@@ -2120,10 +2120,10 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>1.951687028201299</v>
+        <v>2.426874559313921</v>
       </c>
       <c r="C3">
-        <v>1.951687028201299</v>
+        <v>2.426874559313921</v>
       </c>
       <c r="D3" t="s">
         <v>251</v>
@@ -2143,10 +2143,10 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2.023133253806931</v>
+        <v>2.397505475294293</v>
       </c>
       <c r="C4">
-        <v>2.023133253806931</v>
+        <v>2.397505475294293</v>
       </c>
       <c r="D4" t="s">
         <v>251</v>
@@ -2166,10 +2166,10 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.9885161641784795</v>
+        <v>0.8174714312001214</v>
       </c>
       <c r="C5">
-        <v>0.9885161641784795</v>
+        <v>0.8174714312001214</v>
       </c>
       <c r="D5" t="s">
         <v>252</v>
@@ -2189,10 +2189,10 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>2.1826293124072</v>
+        <v>2.898550700965599</v>
       </c>
       <c r="C6">
-        <v>2.1826293124072</v>
+        <v>2.898550700965599</v>
       </c>
       <c r="D6" t="s">
         <v>251</v>
@@ -2212,10 +2212,10 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.5516000226888013</v>
+        <v>0.6011792765660919</v>
       </c>
       <c r="C7">
-        <v>0.5516000226888013</v>
+        <v>0.6011792765660919</v>
       </c>
       <c r="D7" t="s">
         <v>252</v>
@@ -2235,10 +2235,10 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>2.113843492718625</v>
+        <v>2.821053068360476</v>
       </c>
       <c r="C8">
-        <v>2.113843492718625</v>
+        <v>2.821053068360476</v>
       </c>
       <c r="D8" t="s">
         <v>251</v>
@@ -2258,10 +2258,10 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.7551769812447893</v>
+        <v>0.888501251401697</v>
       </c>
       <c r="C9">
-        <v>0.7551769812447893</v>
+        <v>0.888501251401697</v>
       </c>
       <c r="D9" t="s">
         <v>252</v>
@@ -2281,10 +2281,10 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>2.354285281895629</v>
+        <v>2.895962996427035</v>
       </c>
       <c r="C10">
-        <v>2.354285281895629</v>
+        <v>2.895962996427035</v>
       </c>
       <c r="D10" t="s">
         <v>251</v>
@@ -2304,13 +2304,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>1.120953674588055</v>
+        <v>1.327083620851751</v>
       </c>
       <c r="C11">
-        <v>1.120953674588055</v>
+        <v>1.327083620851751</v>
       </c>
       <c r="D11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E11" t="s">
         <v>262</v>
@@ -2327,10 +2327,10 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.9378634024017813</v>
+        <v>1.136902637789493</v>
       </c>
       <c r="C12">
-        <v>0.9378634024017813</v>
+        <v>1.136902637789493</v>
       </c>
       <c r="D12" t="s">
         <v>252</v>
@@ -2350,10 +2350,10 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.7097971989287984</v>
+        <v>0.7378563205712541</v>
       </c>
       <c r="C13">
-        <v>0.7097971989287984</v>
+        <v>0.7378563205712541</v>
       </c>
       <c r="D13" t="s">
         <v>252</v>
@@ -2373,10 +2373,10 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>2.295108353133979</v>
+        <v>3.105894377617302</v>
       </c>
       <c r="C14">
-        <v>2.295108353133979</v>
+        <v>3.105894377617302</v>
       </c>
       <c r="D14" t="s">
         <v>251</v>
@@ -2396,13 +2396,13 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>1.010736466878467</v>
+        <v>1.265892252606359</v>
       </c>
       <c r="C15">
-        <v>1.010736466878467</v>
+        <v>1.265892252606359</v>
       </c>
       <c r="D15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E15" t="s">
         <v>266</v>
@@ -2419,10 +2419,10 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.6583119128124297</v>
+        <v>0.6552784339650152</v>
       </c>
       <c r="C16">
-        <v>0.6583119128124297</v>
+        <v>0.6552784339650152</v>
       </c>
       <c r="D16" t="s">
         <v>252</v>
@@ -2442,10 +2442,10 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.6590451611698267</v>
+        <v>0.5973041179527954</v>
       </c>
       <c r="C17">
-        <v>0.6590451611698267</v>
+        <v>0.5973041179527954</v>
       </c>
       <c r="D17" t="s">
         <v>252</v>
@@ -2465,10 +2465,10 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.3681664642687644</v>
+        <v>0.2812638924542025</v>
       </c>
       <c r="C18">
-        <v>0.3681664642687644</v>
+        <v>0.2812638924542025</v>
       </c>
       <c r="D18" t="s">
         <v>252</v>
@@ -2488,10 +2488,10 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.4408410849449526</v>
+        <v>0.3686707499306042</v>
       </c>
       <c r="C19">
-        <v>0.4408410849449526</v>
+        <v>0.3686707499306042</v>
       </c>
       <c r="D19" t="s">
         <v>252</v>
@@ -2511,10 +2511,10 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.4558728267042159</v>
+        <v>0.3446867212488689</v>
       </c>
       <c r="C20">
-        <v>0.4558728267042159</v>
+        <v>0.3446867212488689</v>
       </c>
       <c r="D20" t="s">
         <v>252</v>
@@ -2534,10 +2534,10 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.1254085601523959</v>
+        <v>0.004615672876032113</v>
       </c>
       <c r="C21">
-        <v>0.1254085601523959</v>
+        <v>0.004615672876032113</v>
       </c>
       <c r="D21" t="s">
         <v>252</v>
@@ -2557,10 +2557,10 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.1296207798567628</v>
+        <v>0.006280258105268914</v>
       </c>
       <c r="C22">
-        <v>0.1296207798567628</v>
+        <v>0.006280258105268914</v>
       </c>
       <c r="D22" t="s">
         <v>252</v>
@@ -2580,10 +2580,10 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.1581457245871749</v>
+        <v>0.01568135473370999</v>
       </c>
       <c r="C23">
-        <v>0.1581457245871749</v>
+        <v>0.01568135473370999</v>
       </c>
       <c r="D23" t="s">
         <v>252</v>
@@ -2603,10 +2603,10 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.1594046967249186</v>
+        <v>0.01667731347788676</v>
       </c>
       <c r="C24">
-        <v>0.1594046967249186</v>
+        <v>0.01667731347788676</v>
       </c>
       <c r="D24" t="s">
         <v>252</v>
@@ -2626,10 +2626,10 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.8552854571170985</v>
+        <v>0.6973020934445018</v>
       </c>
       <c r="C25">
-        <v>0.8552854571170985</v>
+        <v>0.6973020934445018</v>
       </c>
       <c r="D25" t="s">
         <v>252</v>
@@ -2649,10 +2649,10 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.9009845817659277</v>
+        <v>0.8758218333484735</v>
       </c>
       <c r="C26">
-        <v>0.9009845817659277</v>
+        <v>0.8758218333484735</v>
       </c>
       <c r="D26" t="s">
         <v>252</v>
@@ -2672,10 +2672,10 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>1.005114441989536</v>
+        <v>1.148463735507422</v>
       </c>
       <c r="C27">
-        <v>1.005114441989536</v>
+        <v>1.148463735507422</v>
       </c>
       <c r="D27" t="s">
         <v>252</v>
@@ -2695,10 +2695,10 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>1.561722461493026</v>
+        <v>1.890220073918943</v>
       </c>
       <c r="C28">
-        <v>1.561722461493026</v>
+        <v>1.890220073918943</v>
       </c>
       <c r="D28" t="s">
         <v>251</v>
@@ -2718,10 +2718,10 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.7635492063859279</v>
+        <v>0.8283997346504146</v>
       </c>
       <c r="C29">
-        <v>0.7635492063859279</v>
+        <v>0.8283997346504146</v>
       </c>
       <c r="D29" t="s">
         <v>252</v>
@@ -2741,10 +2741,10 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>1.624613533381907</v>
+        <v>2.480959678743628</v>
       </c>
       <c r="C30">
-        <v>1.624613533381907</v>
+        <v>2.480959678743628</v>
       </c>
       <c r="D30" t="s">
         <v>251</v>
@@ -2764,10 +2764,10 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>1.539841802840974</v>
+        <v>2.269290249882573</v>
       </c>
       <c r="C31">
-        <v>1.539841802840974</v>
+        <v>2.269290249882573</v>
       </c>
       <c r="D31" t="s">
         <v>251</v>
@@ -2787,10 +2787,10 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.4105517291065681</v>
+        <v>0.3786738649865685</v>
       </c>
       <c r="C32">
-        <v>0.4105517291065681</v>
+        <v>0.3786738649865685</v>
       </c>
       <c r="D32" t="s">
         <v>252</v>
@@ -2810,13 +2810,13 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>1.080545095889559</v>
+        <v>1.545969569952652</v>
       </c>
       <c r="C33">
-        <v>1.080545095889559</v>
+        <v>1.545969569952652</v>
       </c>
       <c r="D33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E33" t="s">
         <v>284</v>
@@ -2833,10 +2833,10 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>1.881413442010019</v>
+        <v>2.783005555764028</v>
       </c>
       <c r="C34">
-        <v>1.881413442010019</v>
+        <v>2.783005555764028</v>
       </c>
       <c r="D34" t="s">
         <v>251</v>
@@ -2856,10 +2856,10 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.8870129026600648</v>
+        <v>1.105881012846256</v>
       </c>
       <c r="C35">
-        <v>0.8870129026600648</v>
+        <v>1.105881012846256</v>
       </c>
       <c r="D35" t="s">
         <v>252</v>
@@ -2879,10 +2879,10 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>2.298858853714695</v>
+        <v>3.413817644083865</v>
       </c>
       <c r="C36">
-        <v>2.298858853714695</v>
+        <v>3.413817644083865</v>
       </c>
       <c r="D36" t="s">
         <v>251</v>
@@ -2902,10 +2902,10 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.8428874435946355</v>
+        <v>1.156171257276426</v>
       </c>
       <c r="C37">
-        <v>0.8428874435946355</v>
+        <v>1.156171257276426</v>
       </c>
       <c r="D37" t="s">
         <v>252</v>
@@ -2925,10 +2925,10 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>1.621484436044065</v>
+        <v>2.583523628311352</v>
       </c>
       <c r="C38">
-        <v>1.621484436044065</v>
+        <v>2.583523628311352</v>
       </c>
       <c r="D38" t="s">
         <v>251</v>
@@ -2948,13 +2948,13 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>1.144177960975358</v>
+        <v>1.72689368240064</v>
       </c>
       <c r="C39">
-        <v>1.144177960975358</v>
+        <v>1.72689368240064</v>
       </c>
       <c r="D39" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E39" t="s">
         <v>290</v>
@@ -2971,10 +2971,10 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>1.357610882003726</v>
+        <v>1.862018653082905</v>
       </c>
       <c r="C40">
-        <v>1.357610882003726</v>
+        <v>1.862018653082905</v>
       </c>
       <c r="D40" t="s">
         <v>251</v>
@@ -2994,13 +2994,13 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>1.254833717355365</v>
+        <v>1.062504004937968</v>
       </c>
       <c r="C41">
-        <v>1.254833717355365</v>
+        <v>1.062504004937968</v>
       </c>
       <c r="D41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E41" t="s">
         <v>292</v>
@@ -3017,10 +3017,10 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>1.588157448170999</v>
+        <v>2.593733379489021</v>
       </c>
       <c r="C42">
-        <v>1.588157448170999</v>
+        <v>2.593733379489021</v>
       </c>
       <c r="D42" t="s">
         <v>251</v>
@@ -3040,10 +3040,10 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.7976440048555848</v>
+        <v>1.142281247268503</v>
       </c>
       <c r="C43">
-        <v>0.7976440048555848</v>
+        <v>1.142281247268503</v>
       </c>
       <c r="D43" t="s">
         <v>252</v>
@@ -3063,10 +3063,10 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.4224776582924136</v>
+        <v>0.3658856704658335</v>
       </c>
       <c r="C44">
-        <v>0.4224776582924136</v>
+        <v>0.3658856704658335</v>
       </c>
       <c r="D44" t="s">
         <v>252</v>
@@ -3086,10 +3086,10 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.4865161273710955</v>
+        <v>0.4525008938732042</v>
       </c>
       <c r="C45">
-        <v>0.4865161273710955</v>
+        <v>0.4525008938732042</v>
       </c>
       <c r="D45" t="s">
         <v>252</v>
@@ -3109,10 +3109,10 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.4802535898730681</v>
+        <v>0.4291925594151965</v>
       </c>
       <c r="C46">
-        <v>0.4802535898730681</v>
+        <v>0.4291925594151965</v>
       </c>
       <c r="D46" t="s">
         <v>252</v>
@@ -3132,10 +3132,10 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.7236310321082501</v>
+        <v>0.8066717473240186</v>
       </c>
       <c r="C47">
-        <v>0.7236310321082501</v>
+        <v>0.8066717473240186</v>
       </c>
       <c r="D47" t="s">
         <v>252</v>
@@ -3155,10 +3155,10 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.2445725831168871</v>
+        <v>0.09711292703248195</v>
       </c>
       <c r="C48">
-        <v>0.2445725831168871</v>
+        <v>0.09711292703248195</v>
       </c>
       <c r="D48" t="s">
         <v>252</v>
@@ -3178,10 +3178,10 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.1863282553234051</v>
+        <v>0.06163922168024719</v>
       </c>
       <c r="C49">
-        <v>0.1863282553234051</v>
+        <v>0.06163922168024719</v>
       </c>
       <c r="D49" t="s">
         <v>252</v>
@@ -3201,10 +3201,10 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>0.2345679198226612</v>
+        <v>0.1427176606408782</v>
       </c>
       <c r="C50">
-        <v>0.2345679198226612</v>
+        <v>0.1427176606408782</v>
       </c>
       <c r="D50" t="s">
         <v>252</v>
@@ -3224,10 +3224,10 @@
         <v>56</v>
       </c>
       <c r="B51">
-        <v>0.6649078868829655</v>
+        <v>0.710448152141424</v>
       </c>
       <c r="C51">
-        <v>0.6649078868829655</v>
+        <v>0.710448152141424</v>
       </c>
       <c r="D51" t="s">
         <v>252</v>
@@ -3247,10 +3247,10 @@
         <v>57</v>
       </c>
       <c r="B52">
-        <v>0.17454487677178</v>
+        <v>0.1138739879075436</v>
       </c>
       <c r="C52">
-        <v>0.17454487677178</v>
+        <v>0.1138739879075436</v>
       </c>
       <c r="D52" t="s">
         <v>252</v>
@@ -3270,10 +3270,10 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>0.3681225797818403</v>
+        <v>0.3500951041268681</v>
       </c>
       <c r="C53">
-        <v>0.3681225797818403</v>
+        <v>0.3500951041268681</v>
       </c>
       <c r="D53" t="s">
         <v>252</v>
@@ -3293,10 +3293,10 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>0.3065119725170509</v>
+        <v>0.2449817978038795</v>
       </c>
       <c r="C54">
-        <v>0.3065119725170509</v>
+        <v>0.2449817978038795</v>
       </c>
       <c r="D54" t="s">
         <v>252</v>
@@ -3316,10 +3316,10 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>0.67165584942253</v>
+        <v>0.6925005457193725</v>
       </c>
       <c r="C55">
-        <v>0.67165584942253</v>
+        <v>0.6925005457193725</v>
       </c>
       <c r="D55" t="s">
         <v>252</v>
@@ -3339,10 +3339,10 @@
         <v>61</v>
       </c>
       <c r="B56">
-        <v>0.6665161520988496</v>
+        <v>0.8770507556375201</v>
       </c>
       <c r="C56">
-        <v>0.6665161520988496</v>
+        <v>0.8770507556375201</v>
       </c>
       <c r="D56" t="s">
         <v>252</v>
@@ -3362,10 +3362,10 @@
         <v>62</v>
       </c>
       <c r="B57">
-        <v>0.5500379985247736</v>
+        <v>0.6381890087417599</v>
       </c>
       <c r="C57">
-        <v>0.5500379985247736</v>
+        <v>0.6381890087417599</v>
       </c>
       <c r="D57" t="s">
         <v>252</v>
@@ -3385,10 +3385,10 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>0.3402830537818915</v>
+        <v>0.2771276184612754</v>
       </c>
       <c r="C58">
-        <v>0.3402830537818915</v>
+        <v>0.2771276184612754</v>
       </c>
       <c r="D58" t="s">
         <v>252</v>
@@ -3408,10 +3408,10 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>1.20161501879365</v>
+        <v>1.386970361017914</v>
       </c>
       <c r="C59">
-        <v>1.20161501879365</v>
+        <v>1.386970361017914</v>
       </c>
       <c r="D59" t="s">
         <v>251</v>
@@ -3431,10 +3431,10 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>0.4663758170776857</v>
+        <v>0.4636173374067944</v>
       </c>
       <c r="C60">
-        <v>0.4663758170776857</v>
+        <v>0.4636173374067944</v>
       </c>
       <c r="D60" t="s">
         <v>252</v>
@@ -3454,10 +3454,10 @@
         <v>66</v>
       </c>
       <c r="B61">
-        <v>0.9049783635926023</v>
+        <v>1.023506516872447</v>
       </c>
       <c r="C61">
-        <v>0.9049783635926023</v>
+        <v>1.023506516872447</v>
       </c>
       <c r="D61" t="s">
         <v>252</v>
@@ -3477,10 +3477,10 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>0.7836563240848913</v>
+        <v>0.9150587032120517</v>
       </c>
       <c r="C62">
-        <v>0.7836563240848913</v>
+        <v>0.9150587032120517</v>
       </c>
       <c r="D62" t="s">
         <v>252</v>
@@ -3500,10 +3500,10 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>0.5140931127561927</v>
+        <v>0.5680795653311617</v>
       </c>
       <c r="C63">
-        <v>0.5140931127561927</v>
+        <v>0.5680795653311617</v>
       </c>
       <c r="D63" t="s">
         <v>252</v>
@@ -3523,10 +3523,10 @@
         <v>69</v>
       </c>
       <c r="B64">
-        <v>0.598007143711434</v>
+        <v>0.6071784738499169</v>
       </c>
       <c r="C64">
-        <v>0.598007143711434</v>
+        <v>0.6071784738499169</v>
       </c>
       <c r="D64" t="s">
         <v>252</v>
@@ -3546,10 +3546,10 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>0.8484406267923688</v>
+        <v>0.9209495712933591</v>
       </c>
       <c r="C65">
-        <v>0.8484406267923688</v>
+        <v>0.9209495712933591</v>
       </c>
       <c r="D65" t="s">
         <v>252</v>
@@ -3569,10 +3569,10 @@
         <v>71</v>
       </c>
       <c r="B66">
-        <v>0.820775685030958</v>
+        <v>0.9778461626400159</v>
       </c>
       <c r="C66">
-        <v>0.820775685030958</v>
+        <v>0.9778461626400159</v>
       </c>
       <c r="D66" t="s">
         <v>252</v>
@@ -3592,10 +3592,10 @@
         <v>72</v>
       </c>
       <c r="B67">
-        <v>1.875270179428823</v>
+        <v>2.43150088688448</v>
       </c>
       <c r="C67">
-        <v>1.875270179428823</v>
+        <v>2.43150088688448</v>
       </c>
       <c r="D67" t="s">
         <v>251</v>
@@ -3615,10 +3615,10 @@
         <v>73</v>
       </c>
       <c r="B68">
-        <v>0.8652037997032342</v>
+        <v>1.011070657176934</v>
       </c>
       <c r="C68">
-        <v>0.8652037997032342</v>
+        <v>1.011070657176934</v>
       </c>
       <c r="D68" t="s">
         <v>252</v>
@@ -3638,13 +3638,13 @@
         <v>74</v>
       </c>
       <c r="B69">
-        <v>1.167655200140736</v>
+        <v>1.610854575447449</v>
       </c>
       <c r="C69">
-        <v>1.167655200140736</v>
+        <v>1.610854575447449</v>
       </c>
       <c r="D69" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E69" t="s">
         <v>320</v>
@@ -3661,10 +3661,10 @@
         <v>75</v>
       </c>
       <c r="B70">
-        <v>1.363450063127189</v>
+        <v>1.841368755035201</v>
       </c>
       <c r="C70">
-        <v>1.363450063127189</v>
+        <v>1.841368755035201</v>
       </c>
       <c r="D70" t="s">
         <v>251</v>
@@ -3684,10 +3684,10 @@
         <v>76</v>
       </c>
       <c r="B71">
-        <v>1.611424613069323</v>
+        <v>2.406267830178428</v>
       </c>
       <c r="C71">
-        <v>1.611424613069323</v>
+        <v>2.406267830178428</v>
       </c>
       <c r="D71" t="s">
         <v>251</v>
@@ -3707,10 +3707,10 @@
         <v>77</v>
       </c>
       <c r="B72">
-        <v>0.4833375476265242</v>
+        <v>0.5112097017481247</v>
       </c>
       <c r="C72">
-        <v>0.4833375476265242</v>
+        <v>0.5112097017481247</v>
       </c>
       <c r="D72" t="s">
         <v>252</v>
@@ -3730,10 +3730,10 @@
         <v>78</v>
       </c>
       <c r="B73">
-        <v>1.346530819642678</v>
+        <v>1.663153021978641</v>
       </c>
       <c r="C73">
-        <v>1.346530819642678</v>
+        <v>1.663153021978641</v>
       </c>
       <c r="D73" t="s">
         <v>251</v>
@@ -3753,13 +3753,13 @@
         <v>79</v>
       </c>
       <c r="B74">
-        <v>1.116031092758516</v>
+        <v>1.478134440861248</v>
       </c>
       <c r="C74">
-        <v>1.116031092758516</v>
+        <v>1.478134440861248</v>
       </c>
       <c r="D74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E74" t="s">
         <v>325</v>
@@ -3776,10 +3776,10 @@
         <v>80</v>
       </c>
       <c r="B75">
-        <v>1.329911821546185</v>
+        <v>1.840739593500203</v>
       </c>
       <c r="C75">
-        <v>1.329911821546185</v>
+        <v>1.840739593500203</v>
       </c>
       <c r="D75" t="s">
         <v>251</v>
@@ -3799,10 +3799,10 @@
         <v>81</v>
       </c>
       <c r="B76">
-        <v>1.490929959248393</v>
+        <v>1.923645628203002</v>
       </c>
       <c r="C76">
-        <v>1.490929959248393</v>
+        <v>1.923645628203002</v>
       </c>
       <c r="D76" t="s">
         <v>251</v>
@@ -3822,13 +3822,13 @@
         <v>82</v>
       </c>
       <c r="B77">
-        <v>1.00906587477722</v>
+        <v>1.22698503348356</v>
       </c>
       <c r="C77">
-        <v>1.00906587477722</v>
+        <v>1.22698503348356</v>
       </c>
       <c r="D77" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E77" t="s">
         <v>328</v>
@@ -3845,10 +3845,10 @@
         <v>83</v>
       </c>
       <c r="B78">
-        <v>0.6030189726361728</v>
+        <v>0.7352508230320451</v>
       </c>
       <c r="C78">
-        <v>0.6030189726361728</v>
+        <v>0.7352508230320451</v>
       </c>
       <c r="D78" t="s">
         <v>252</v>
@@ -3868,10 +3868,10 @@
         <v>84</v>
       </c>
       <c r="B79">
-        <v>0.3659499811391691</v>
+        <v>0.4295358648657414</v>
       </c>
       <c r="C79">
-        <v>0.3659499811391691</v>
+        <v>0.4295358648657414</v>
       </c>
       <c r="D79" t="s">
         <v>252</v>
@@ -3891,10 +3891,10 @@
         <v>85</v>
       </c>
       <c r="B80">
-        <v>0.6521481851543429</v>
+        <v>0.7435892946243901</v>
       </c>
       <c r="C80">
-        <v>0.6521481851543429</v>
+        <v>0.7435892946243901</v>
       </c>
       <c r="D80" t="s">
         <v>252</v>
@@ -3914,10 +3914,10 @@
         <v>86</v>
       </c>
       <c r="B81">
-        <v>0.3687230329412986</v>
+        <v>0.3671400300116375</v>
       </c>
       <c r="C81">
-        <v>0.3687230329412986</v>
+        <v>0.3671400300116375</v>
       </c>
       <c r="D81" t="s">
         <v>252</v>
@@ -3937,13 +3937,13 @@
         <v>87</v>
       </c>
       <c r="B82">
-        <v>1.168042734047975</v>
+        <v>1.51332134456899</v>
       </c>
       <c r="C82">
-        <v>1.168042734047975</v>
+        <v>1.51332134456899</v>
       </c>
       <c r="D82" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E82" t="s">
         <v>333</v>
@@ -3960,13 +3960,13 @@
         <v>88</v>
       </c>
       <c r="B83">
-        <v>1.194954921144546</v>
+        <v>1.427568808689359</v>
       </c>
       <c r="C83">
-        <v>1.194954921144546</v>
+        <v>1.427568808689359</v>
       </c>
       <c r="D83" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E83" t="s">
         <v>334</v>
@@ -3983,10 +3983,10 @@
         <v>89</v>
       </c>
       <c r="B84">
-        <v>1.30221716199086</v>
+        <v>1.671374250404086</v>
       </c>
       <c r="C84">
-        <v>1.30221716199086</v>
+        <v>1.671374250404086</v>
       </c>
       <c r="D84" t="s">
         <v>251</v>
@@ -4006,10 +4006,10 @@
         <v>90</v>
       </c>
       <c r="B85">
-        <v>1.550695168320296</v>
+        <v>1.94837138683733</v>
       </c>
       <c r="C85">
-        <v>1.550695168320296</v>
+        <v>1.94837138683733</v>
       </c>
       <c r="D85" t="s">
         <v>251</v>
@@ -4029,10 +4029,10 @@
         <v>91</v>
       </c>
       <c r="B86">
-        <v>0.8096393617481863</v>
+        <v>0.9474587793306635</v>
       </c>
       <c r="C86">
-        <v>0.8096393617481863</v>
+        <v>0.9474587793306635</v>
       </c>
       <c r="D86" t="s">
         <v>252</v>
@@ -4052,10 +4052,10 @@
         <v>92</v>
       </c>
       <c r="B87">
-        <v>0.951449725901565</v>
+        <v>1.06828225670024</v>
       </c>
       <c r="C87">
-        <v>0.951449725901565</v>
+        <v>1.06828225670024</v>
       </c>
       <c r="D87" t="s">
         <v>252</v>
@@ -4075,10 +4075,10 @@
         <v>93</v>
       </c>
       <c r="B88">
-        <v>1.48070341252915</v>
+        <v>2.015549077554859</v>
       </c>
       <c r="C88">
-        <v>1.48070341252915</v>
+        <v>2.015549077554859</v>
       </c>
       <c r="D88" t="s">
         <v>251</v>
@@ -4098,10 +4098,10 @@
         <v>94</v>
       </c>
       <c r="B89">
-        <v>1.977295530443556</v>
+        <v>2.781130022560588</v>
       </c>
       <c r="C89">
-        <v>1.977295530443556</v>
+        <v>2.781130022560588</v>
       </c>
       <c r="D89" t="s">
         <v>251</v>
@@ -4121,10 +4121,10 @@
         <v>95</v>
       </c>
       <c r="B90">
-        <v>1.240218885772566</v>
+        <v>1.746769899134736</v>
       </c>
       <c r="C90">
-        <v>1.240218885772566</v>
+        <v>1.746769899134736</v>
       </c>
       <c r="D90" t="s">
         <v>251</v>
@@ -4144,10 +4144,10 @@
         <v>96</v>
       </c>
       <c r="B91">
-        <v>0.72419467717264</v>
+        <v>0.8287380544777219</v>
       </c>
       <c r="C91">
-        <v>0.72419467717264</v>
+        <v>0.8287380544777219</v>
       </c>
       <c r="D91" t="s">
         <v>252</v>
@@ -4167,10 +4167,10 @@
         <v>97</v>
       </c>
       <c r="B92">
-        <v>1.307456276708541</v>
+        <v>2.206819639078817</v>
       </c>
       <c r="C92">
-        <v>1.307456276708541</v>
+        <v>2.206819639078817</v>
       </c>
       <c r="D92" t="s">
         <v>251</v>
@@ -4190,10 +4190,10 @@
         <v>98</v>
       </c>
       <c r="B93">
-        <v>1.632961284307301</v>
+        <v>2.27306014455962</v>
       </c>
       <c r="C93">
-        <v>1.632961284307301</v>
+        <v>2.27306014455962</v>
       </c>
       <c r="D93" t="s">
         <v>251</v>
@@ -4213,13 +4213,13 @@
         <v>99</v>
       </c>
       <c r="B94">
-        <v>1.058781381492569</v>
+        <v>1.292575691484285</v>
       </c>
       <c r="C94">
-        <v>1.058781381492569</v>
+        <v>1.292575691484285</v>
       </c>
       <c r="D94" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E94" t="s">
         <v>345</v>
@@ -4236,10 +4236,10 @@
         <v>100</v>
       </c>
       <c r="B95">
-        <v>0.5148544671676737</v>
+        <v>0.563612932292875</v>
       </c>
       <c r="C95">
-        <v>0.5148544671676737</v>
+        <v>0.563612932292875</v>
       </c>
       <c r="D95" t="s">
         <v>252</v>
@@ -4259,10 +4259,10 @@
         <v>101</v>
       </c>
       <c r="B96">
-        <v>1.379777881810632</v>
+        <v>1.853849805299328</v>
       </c>
       <c r="C96">
-        <v>1.379777881810632</v>
+        <v>1.853849805299328</v>
       </c>
       <c r="D96" t="s">
         <v>251</v>
@@ -4282,10 +4282,10 @@
         <v>102</v>
       </c>
       <c r="B97">
-        <v>0.3131514789997867</v>
+        <v>0.1480991757921845</v>
       </c>
       <c r="C97">
-        <v>0.3131514789997867</v>
+        <v>0.1480991757921845</v>
       </c>
       <c r="D97" t="s">
         <v>252</v>
@@ -4305,10 +4305,10 @@
         <v>103</v>
       </c>
       <c r="B98">
-        <v>0.2968466506075073</v>
+        <v>0.1556927306466424</v>
       </c>
       <c r="C98">
-        <v>0.2968466506075073</v>
+        <v>0.1556927306466424</v>
       </c>
       <c r="D98" t="s">
         <v>252</v>
@@ -4328,10 +4328,10 @@
         <v>104</v>
       </c>
       <c r="B99">
-        <v>0.2573079431943824</v>
+        <v>0.1319466182850752</v>
       </c>
       <c r="C99">
-        <v>0.2573079431943824</v>
+        <v>0.1319466182850752</v>
       </c>
       <c r="D99" t="s">
         <v>252</v>
@@ -4351,10 +4351,10 @@
         <v>105</v>
       </c>
       <c r="B100">
-        <v>0.3060786344535934</v>
+        <v>0.1737901818642173</v>
       </c>
       <c r="C100">
-        <v>0.3060786344535934</v>
+        <v>0.1737901818642173</v>
       </c>
       <c r="D100" t="s">
         <v>252</v>
@@ -4374,10 +4374,10 @@
         <v>106</v>
       </c>
       <c r="B101">
-        <v>0.2390165273021266</v>
+        <v>0.1039576178575747</v>
       </c>
       <c r="C101">
-        <v>0.2390165273021266</v>
+        <v>0.1039576178575747</v>
       </c>
       <c r="D101" t="s">
         <v>252</v>
@@ -4397,10 +4397,10 @@
         <v>107</v>
       </c>
       <c r="B102">
-        <v>0.466551301890559</v>
+        <v>0.3333510578206342</v>
       </c>
       <c r="C102">
-        <v>0.466551301890559</v>
+        <v>0.3333510578206342</v>
       </c>
       <c r="D102" t="s">
         <v>252</v>
@@ -4420,10 +4420,10 @@
         <v>108</v>
       </c>
       <c r="B103">
-        <v>0.2187811037098076</v>
+        <v>0.09244490151007151</v>
       </c>
       <c r="C103">
-        <v>0.2187811037098076</v>
+        <v>0.09244490151007151</v>
       </c>
       <c r="D103" t="s">
         <v>252</v>
@@ -4443,10 +4443,10 @@
         <v>109</v>
       </c>
       <c r="B104">
-        <v>0.1800822122418989</v>
+        <v>0.04399635181730684</v>
       </c>
       <c r="C104">
-        <v>0.1800822122418989</v>
+        <v>0.04399635181730684</v>
       </c>
       <c r="D104" t="s">
         <v>252</v>
@@ -4466,10 +4466,10 @@
         <v>110</v>
       </c>
       <c r="B105">
-        <v>0.4641951140236773</v>
+        <v>0.3460857809748192</v>
       </c>
       <c r="C105">
-        <v>0.4641951140236773</v>
+        <v>0.3460857809748192</v>
       </c>
       <c r="D105" t="s">
         <v>252</v>
@@ -4489,10 +4489,10 @@
         <v>111</v>
       </c>
       <c r="B106">
-        <v>0.319903746295285</v>
+        <v>0.1914680323024075</v>
       </c>
       <c r="C106">
-        <v>0.319903746295285</v>
+        <v>0.1914680323024075</v>
       </c>
       <c r="D106" t="s">
         <v>252</v>
@@ -4512,10 +4512,10 @@
         <v>112</v>
       </c>
       <c r="B107">
-        <v>0.2253895341284574</v>
+        <v>0.1078871154475268</v>
       </c>
       <c r="C107">
-        <v>0.2253895341284574</v>
+        <v>0.1078871154475268</v>
       </c>
       <c r="D107" t="s">
         <v>252</v>
@@ -4535,10 +4535,10 @@
         <v>113</v>
       </c>
       <c r="B108">
-        <v>0.6195892245819334</v>
+        <v>0.6004610584301171</v>
       </c>
       <c r="C108">
-        <v>0.6195892245819334</v>
+        <v>0.6004610584301171</v>
       </c>
       <c r="D108" t="s">
         <v>252</v>
@@ -4558,10 +4558,10 @@
         <v>114</v>
       </c>
       <c r="B109">
-        <v>0.5893378122039625</v>
+        <v>0.6220032085438373</v>
       </c>
       <c r="C109">
-        <v>0.5893378122039625</v>
+        <v>0.6220032085438373</v>
       </c>
       <c r="D109" t="s">
         <v>252</v>
@@ -4581,10 +4581,10 @@
         <v>115</v>
       </c>
       <c r="B110">
-        <v>0.7197804593222257</v>
+        <v>0.6280985299996257</v>
       </c>
       <c r="C110">
-        <v>0.7197804593222257</v>
+        <v>0.6280985299996257</v>
       </c>
       <c r="D110" t="s">
         <v>252</v>
@@ -4604,10 +4604,10 @@
         <v>116</v>
       </c>
       <c r="B111">
-        <v>0.2200032391751138</v>
+        <v>0.1323697577742226</v>
       </c>
       <c r="C111">
-        <v>0.2200032391751138</v>
+        <v>0.1323697577742226</v>
       </c>
       <c r="D111" t="s">
         <v>252</v>
@@ -4627,10 +4627,10 @@
         <v>117</v>
       </c>
       <c r="B112">
-        <v>0.2222369021401799</v>
+        <v>0.1391629703036907</v>
       </c>
       <c r="C112">
-        <v>0.2222369021401799</v>
+        <v>0.1391629703036907</v>
       </c>
       <c r="D112" t="s">
         <v>252</v>
@@ -4650,10 +4650,10 @@
         <v>118</v>
       </c>
       <c r="B113">
-        <v>0.2218139778543431</v>
+        <v>0.104140175306908</v>
       </c>
       <c r="C113">
-        <v>0.2218139778543431</v>
+        <v>0.104140175306908</v>
       </c>
       <c r="D113" t="s">
         <v>252</v>
@@ -4673,10 +4673,10 @@
         <v>119</v>
       </c>
       <c r="B114">
-        <v>0.3036252447493155</v>
+        <v>0.1909323496905523</v>
       </c>
       <c r="C114">
-        <v>0.3036252447493155</v>
+        <v>0.1909323496905523</v>
       </c>
       <c r="D114" t="s">
         <v>252</v>
@@ -4696,10 +4696,10 @@
         <v>120</v>
       </c>
       <c r="B115">
-        <v>0.3433433055249128</v>
+        <v>0.2184545114134147</v>
       </c>
       <c r="C115">
-        <v>0.3433433055249128</v>
+        <v>0.2184545114134147</v>
       </c>
       <c r="D115" t="s">
         <v>252</v>
@@ -4719,10 +4719,10 @@
         <v>121</v>
       </c>
       <c r="B116">
-        <v>0.2602613410816455</v>
+        <v>0.1139777405454676</v>
       </c>
       <c r="C116">
-        <v>0.2602613410816455</v>
+        <v>0.1139777405454676</v>
       </c>
       <c r="D116" t="s">
         <v>252</v>
@@ -4742,10 +4742,10 @@
         <v>122</v>
       </c>
       <c r="B117">
-        <v>0.2159238950116324</v>
+        <v>0.08571532710019537</v>
       </c>
       <c r="C117">
-        <v>0.2159238950116324</v>
+        <v>0.08571532710019537</v>
       </c>
       <c r="D117" t="s">
         <v>252</v>
@@ -4765,10 +4765,10 @@
         <v>123</v>
       </c>
       <c r="B118">
-        <v>0.1941867638097169</v>
+        <v>0.1107193165174211</v>
       </c>
       <c r="C118">
-        <v>0.1941867638097169</v>
+        <v>0.1107193165174211</v>
       </c>
       <c r="D118" t="s">
         <v>252</v>
@@ -4788,10 +4788,10 @@
         <v>124</v>
       </c>
       <c r="B119">
-        <v>0.2534141965724233</v>
+        <v>0.136428983061587</v>
       </c>
       <c r="C119">
-        <v>0.2534141965724233</v>
+        <v>0.136428983061587</v>
       </c>
       <c r="D119" t="s">
         <v>252</v>
@@ -4811,10 +4811,10 @@
         <v>125</v>
       </c>
       <c r="B120">
-        <v>0.3865266611777778</v>
+        <v>0.2621869894183993</v>
       </c>
       <c r="C120">
-        <v>0.3865266611777778</v>
+        <v>0.2621869894183993</v>
       </c>
       <c r="D120" t="s">
         <v>252</v>
@@ -4834,10 +4834,10 @@
         <v>126</v>
       </c>
       <c r="B121">
-        <v>0.4390559432310531</v>
+        <v>0.2868158227881893</v>
       </c>
       <c r="C121">
-        <v>0.4390559432310531</v>
+        <v>0.2868158227881893</v>
       </c>
       <c r="D121" t="s">
         <v>252</v>
@@ -4857,10 +4857,10 @@
         <v>127</v>
       </c>
       <c r="B122">
-        <v>0.3825532123509178</v>
+        <v>0.2370086311844346</v>
       </c>
       <c r="C122">
-        <v>0.3825532123509178</v>
+        <v>0.2370086311844346</v>
       </c>
       <c r="D122" t="s">
         <v>252</v>
@@ -4880,10 +4880,10 @@
         <v>128</v>
       </c>
       <c r="B123">
-        <v>0.1715494415352036</v>
+        <v>0.07378030141656923</v>
       </c>
       <c r="C123">
-        <v>0.1715494415352036</v>
+        <v>0.07378030141656923</v>
       </c>
       <c r="D123" t="s">
         <v>252</v>
@@ -4903,10 +4903,10 @@
         <v>129</v>
       </c>
       <c r="B124">
-        <v>0.3046327674883141</v>
+        <v>0.1778768438265703</v>
       </c>
       <c r="C124">
-        <v>0.3046327674883141</v>
+        <v>0.1778768438265703</v>
       </c>
       <c r="D124" t="s">
         <v>252</v>
@@ -4926,10 +4926,10 @@
         <v>130</v>
       </c>
       <c r="B125">
-        <v>0.2161463463713901</v>
+        <v>0.09956878918128911</v>
       </c>
       <c r="C125">
-        <v>0.2161463463713901</v>
+        <v>0.09956878918128911</v>
       </c>
       <c r="D125" t="s">
         <v>252</v>
@@ -4949,10 +4949,10 @@
         <v>131</v>
       </c>
       <c r="B126">
-        <v>0.5973649336307022</v>
+        <v>0.4219965325828294</v>
       </c>
       <c r="C126">
-        <v>0.5973649336307022</v>
+        <v>0.4219965325828294</v>
       </c>
       <c r="D126" t="s">
         <v>252</v>
@@ -4972,10 +4972,10 @@
         <v>132</v>
       </c>
       <c r="B127">
-        <v>0.1734266660798341</v>
+        <v>0.03002793452721036</v>
       </c>
       <c r="C127">
-        <v>0.1734266660798341</v>
+        <v>0.03002793452721036</v>
       </c>
       <c r="D127" t="s">
         <v>252</v>
@@ -4995,10 +4995,10 @@
         <v>133</v>
       </c>
       <c r="B128">
-        <v>0.1647096964294844</v>
+        <v>0.02458142759255641</v>
       </c>
       <c r="C128">
-        <v>0.1647096964294844</v>
+        <v>0.02458142759255641</v>
       </c>
       <c r="D128" t="s">
         <v>252</v>
@@ -5018,10 +5018,10 @@
         <v>134</v>
       </c>
       <c r="B129">
-        <v>0.1761704169680019</v>
+        <v>0.04824613505489721</v>
       </c>
       <c r="C129">
-        <v>0.1761704169680019</v>
+        <v>0.04824613505489721</v>
       </c>
       <c r="D129" t="s">
         <v>252</v>
@@ -5041,10 +5041,10 @@
         <v>135</v>
       </c>
       <c r="B130">
-        <v>0.1722429524031946</v>
+        <v>0.04590133144398956</v>
       </c>
       <c r="C130">
-        <v>0.1722429524031946</v>
+        <v>0.04590133144398956</v>
       </c>
       <c r="D130" t="s">
         <v>252</v>
@@ -5064,10 +5064,10 @@
         <v>136</v>
       </c>
       <c r="B131">
-        <v>0.3308590192794425</v>
+        <v>0.1941319362386418</v>
       </c>
       <c r="C131">
-        <v>0.3308590192794425</v>
+        <v>0.1941319362386418</v>
       </c>
       <c r="D131" t="s">
         <v>252</v>
@@ -5087,10 +5087,10 @@
         <v>137</v>
       </c>
       <c r="B132">
-        <v>0.1657379992590396</v>
+        <v>0.05579958301746641</v>
       </c>
       <c r="C132">
-        <v>0.1657379992590396</v>
+        <v>0.05579958301746641</v>
       </c>
       <c r="D132" t="s">
         <v>252</v>
@@ -5110,10 +5110,10 @@
         <v>138</v>
       </c>
       <c r="B133">
-        <v>0.9604929381068512</v>
+        <v>1.038365898869324</v>
       </c>
       <c r="C133">
-        <v>0.9604929381068512</v>
+        <v>1.038365898869324</v>
       </c>
       <c r="D133" t="s">
         <v>252</v>
@@ -5133,10 +5133,10 @@
         <v>139</v>
       </c>
       <c r="B134">
-        <v>0.2136023882949683</v>
+        <v>0.09338080348704106</v>
       </c>
       <c r="C134">
-        <v>0.2136023882949683</v>
+        <v>0.09338080348704106</v>
       </c>
       <c r="D134" t="s">
         <v>252</v>
@@ -5156,10 +5156,10 @@
         <v>140</v>
       </c>
       <c r="B135">
-        <v>0.4188791746948259</v>
+        <v>0.2574179329863039</v>
       </c>
       <c r="C135">
-        <v>0.4188791746948259</v>
+        <v>0.2574179329863039</v>
       </c>
       <c r="D135" t="s">
         <v>252</v>
@@ -5179,10 +5179,10 @@
         <v>141</v>
       </c>
       <c r="B136">
-        <v>0.2531390517194896</v>
+        <v>0.08768103180482378</v>
       </c>
       <c r="C136">
-        <v>0.2531390517194896</v>
+        <v>0.08768103180482378</v>
       </c>
       <c r="D136" t="s">
         <v>252</v>
@@ -5202,10 +5202,10 @@
         <v>142</v>
       </c>
       <c r="B137">
-        <v>0.1665947451761763</v>
+        <v>0.04905523277088783</v>
       </c>
       <c r="C137">
-        <v>0.1665947451761763</v>
+        <v>0.04905523277088783</v>
       </c>
       <c r="D137" t="s">
         <v>252</v>
@@ -5225,10 +5225,10 @@
         <v>143</v>
       </c>
       <c r="B138">
-        <v>0.2034208260385811</v>
+        <v>0.0237250240257503</v>
       </c>
       <c r="C138">
-        <v>0.2034208260385811</v>
+        <v>0.0237250240257503</v>
       </c>
       <c r="D138" t="s">
         <v>252</v>
@@ -5248,10 +5248,10 @@
         <v>144</v>
       </c>
       <c r="B139">
-        <v>0.502290209393474</v>
+        <v>0.3566634672254951</v>
       </c>
       <c r="C139">
-        <v>0.502290209393474</v>
+        <v>0.3566634672254951</v>
       </c>
       <c r="D139" t="s">
         <v>252</v>
@@ -5271,10 +5271,10 @@
         <v>145</v>
       </c>
       <c r="B140">
-        <v>0.2968694617400232</v>
+        <v>0.1423193813169185</v>
       </c>
       <c r="C140">
-        <v>0.2968694617400232</v>
+        <v>0.1423193813169185</v>
       </c>
       <c r="D140" t="s">
         <v>252</v>
@@ -5294,10 +5294,10 @@
         <v>146</v>
       </c>
       <c r="B141">
-        <v>0.2100973542289373</v>
+        <v>0.0767975987450165</v>
       </c>
       <c r="C141">
-        <v>0.2100973542289373</v>
+        <v>0.0767975987450165</v>
       </c>
       <c r="D141" t="s">
         <v>252</v>
@@ -5317,10 +5317,10 @@
         <v>147</v>
       </c>
       <c r="B142">
-        <v>0.609415877442453</v>
+        <v>0.3092696978952415</v>
       </c>
       <c r="C142">
-        <v>0.609415877442453</v>
+        <v>0.3092696978952415</v>
       </c>
       <c r="D142" t="s">
         <v>252</v>
@@ -5340,10 +5340,10 @@
         <v>148</v>
       </c>
       <c r="B143">
-        <v>0.7092502755364898</v>
+        <v>0.4576953502332931</v>
       </c>
       <c r="C143">
-        <v>0.7092502755364898</v>
+        <v>0.4576953502332931</v>
       </c>
       <c r="D143" t="s">
         <v>252</v>
@@ -5363,10 +5363,10 @@
         <v>149</v>
       </c>
       <c r="B144">
-        <v>0.2161128012388492</v>
+        <v>0.08923796342116662</v>
       </c>
       <c r="C144">
-        <v>0.2161128012388492</v>
+        <v>0.08923796342116662</v>
       </c>
       <c r="D144" t="s">
         <v>252</v>
@@ -5386,10 +5386,10 @@
         <v>150</v>
       </c>
       <c r="B145">
-        <v>1.098465479909049</v>
+        <v>1.054720585888258</v>
       </c>
       <c r="C145">
-        <v>1.098465479909049</v>
+        <v>1.054720585888258</v>
       </c>
       <c r="D145" t="s">
         <v>252</v>
@@ -5409,10 +5409,10 @@
         <v>151</v>
       </c>
       <c r="B146">
-        <v>0.6751323758121949</v>
+        <v>0.5570901032856199</v>
       </c>
       <c r="C146">
-        <v>0.6751323758121949</v>
+        <v>0.5570901032856199</v>
       </c>
       <c r="D146" t="s">
         <v>252</v>
@@ -5432,10 +5432,10 @@
         <v>152</v>
       </c>
       <c r="B147">
-        <v>0.1613427037280464</v>
+        <v>0.07201643157576339</v>
       </c>
       <c r="C147">
-        <v>0.1613427037280464</v>
+        <v>0.07201643157576339</v>
       </c>
       <c r="D147" t="s">
         <v>252</v>
@@ -5455,10 +5455,10 @@
         <v>153</v>
       </c>
       <c r="B148">
-        <v>0.2016979271231993</v>
+        <v>0.1315742962371494</v>
       </c>
       <c r="C148">
-        <v>0.2016979271231993</v>
+        <v>0.1315742962371494</v>
       </c>
       <c r="D148" t="s">
         <v>252</v>
@@ -5478,10 +5478,10 @@
         <v>154</v>
       </c>
       <c r="B149">
-        <v>0.5417235115004537</v>
+        <v>0.5021604128412138</v>
       </c>
       <c r="C149">
-        <v>0.5417235115004537</v>
+        <v>0.5021604128412138</v>
       </c>
       <c r="D149" t="s">
         <v>252</v>
@@ -5501,13 +5501,13 @@
         <v>155</v>
       </c>
       <c r="B150">
-        <v>1.169148967211045</v>
+        <v>1.224971950771618</v>
       </c>
       <c r="C150">
-        <v>1.169148967211045</v>
+        <v>1.224971950771618</v>
       </c>
       <c r="D150" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E150" t="s">
         <v>401</v>
@@ -5524,10 +5524,10 @@
         <v>156</v>
       </c>
       <c r="B151">
-        <v>0.5254428931665969</v>
+        <v>0.6335257496965883</v>
       </c>
       <c r="C151">
-        <v>0.5254428931665969</v>
+        <v>0.6335257496965883</v>
       </c>
       <c r="D151" t="s">
         <v>252</v>
@@ -5547,10 +5547,10 @@
         <v>157</v>
       </c>
       <c r="B152">
-        <v>0.3695948127950857</v>
+        <v>0.2429767747761467</v>
       </c>
       <c r="C152">
-        <v>0.3695948127950857</v>
+        <v>0.2429767747761467</v>
       </c>
       <c r="D152" t="s">
         <v>252</v>
@@ -5570,10 +5570,10 @@
         <v>158</v>
       </c>
       <c r="B153">
-        <v>0.3155452858147467</v>
+        <v>0.2095538252775485</v>
       </c>
       <c r="C153">
-        <v>0.3155452858147467</v>
+        <v>0.2095538252775485</v>
       </c>
       <c r="D153" t="s">
         <v>252</v>
@@ -5593,10 +5593,10 @@
         <v>159</v>
       </c>
       <c r="B154">
-        <v>0.2164478847925181</v>
+        <v>0.09582256030937465</v>
       </c>
       <c r="C154">
-        <v>0.2164478847925181</v>
+        <v>0.09582256030937465</v>
       </c>
       <c r="D154" t="s">
         <v>252</v>
@@ -5616,10 +5616,10 @@
         <v>160</v>
       </c>
       <c r="B155">
-        <v>0.5903493376873458</v>
+        <v>0.4434410091253622</v>
       </c>
       <c r="C155">
-        <v>0.5903493376873458</v>
+        <v>0.4434410091253622</v>
       </c>
       <c r="D155" t="s">
         <v>252</v>
@@ -5639,10 +5639,10 @@
         <v>161</v>
       </c>
       <c r="B156">
-        <v>1.326327330829845</v>
+        <v>1.451260442358216</v>
       </c>
       <c r="C156">
-        <v>1.326327330829845</v>
+        <v>1.451260442358216</v>
       </c>
       <c r="D156" t="s">
         <v>251</v>
@@ -5662,10 +5662,10 @@
         <v>162</v>
       </c>
       <c r="B157">
-        <v>0.4684406890107497</v>
+        <v>0.460668548423732</v>
       </c>
       <c r="C157">
-        <v>0.4684406890107497</v>
+        <v>0.460668548423732</v>
       </c>
       <c r="D157" t="s">
         <v>252</v>
@@ -5685,10 +5685,10 @@
         <v>163</v>
       </c>
       <c r="B158">
-        <v>0.483951057089578</v>
+        <v>0.4979501736599361</v>
       </c>
       <c r="C158">
-        <v>0.483951057089578</v>
+        <v>0.4979501736599361</v>
       </c>
       <c r="D158" t="s">
         <v>252</v>
@@ -5708,10 +5708,10 @@
         <v>164</v>
       </c>
       <c r="B159">
-        <v>0.7464093754613894</v>
+        <v>0.903553927969851</v>
       </c>
       <c r="C159">
-        <v>0.7464093754613894</v>
+        <v>0.903553927969851</v>
       </c>
       <c r="D159" t="s">
         <v>252</v>
@@ -5731,10 +5731,10 @@
         <v>165</v>
       </c>
       <c r="B160">
-        <v>1.289585902909272</v>
+        <v>1.63252545277109</v>
       </c>
       <c r="C160">
-        <v>1.289585902909272</v>
+        <v>1.63252545277109</v>
       </c>
       <c r="D160" t="s">
         <v>251</v>
@@ -5754,10 +5754,10 @@
         <v>166</v>
       </c>
       <c r="B161">
-        <v>0.556244591313235</v>
+        <v>0.3823243656893545</v>
       </c>
       <c r="C161">
-        <v>0.556244591313235</v>
+        <v>0.3823243656893545</v>
       </c>
       <c r="D161" t="s">
         <v>252</v>
@@ -5777,10 +5777,10 @@
         <v>167</v>
       </c>
       <c r="B162">
-        <v>1.62622438559785</v>
+        <v>1.71371884517039</v>
       </c>
       <c r="C162">
-        <v>1.62622438559785</v>
+        <v>1.71371884517039</v>
       </c>
       <c r="D162" t="s">
         <v>251</v>
@@ -5800,10 +5800,10 @@
         <v>168</v>
       </c>
       <c r="B163">
-        <v>1.150855009169258</v>
+        <v>1.102058814679955</v>
       </c>
       <c r="C163">
-        <v>1.150855009169258</v>
+        <v>1.102058814679955</v>
       </c>
       <c r="D163" t="s">
         <v>252</v>
@@ -5823,10 +5823,10 @@
         <v>169</v>
       </c>
       <c r="B164">
-        <v>0.6685670989348809</v>
+        <v>0.6806301960132526</v>
       </c>
       <c r="C164">
-        <v>0.6685670989348809</v>
+        <v>0.6806301960132526</v>
       </c>
       <c r="D164" t="s">
         <v>252</v>
@@ -5846,10 +5846,10 @@
         <v>170</v>
       </c>
       <c r="B165">
-        <v>0.3885807783693424</v>
+        <v>0.3171937980065652</v>
       </c>
       <c r="C165">
-        <v>0.3885807783693424</v>
+        <v>0.3171937980065652</v>
       </c>
       <c r="D165" t="s">
         <v>252</v>
@@ -5869,10 +5869,10 @@
         <v>171</v>
       </c>
       <c r="B166">
-        <v>0.4230312944424679</v>
+        <v>0.3797034087022544</v>
       </c>
       <c r="C166">
-        <v>0.4230312944424679</v>
+        <v>0.3797034087022544</v>
       </c>
       <c r="D166" t="s">
         <v>252</v>
@@ -5892,10 +5892,10 @@
         <v>172</v>
       </c>
       <c r="B167">
-        <v>0.4181083949139988</v>
+        <v>0.3289841185192852</v>
       </c>
       <c r="C167">
-        <v>0.4181083949139988</v>
+        <v>0.3289841185192852</v>
       </c>
       <c r="D167" t="s">
         <v>252</v>
@@ -5915,10 +5915,10 @@
         <v>173</v>
       </c>
       <c r="B168">
-        <v>0.3616720314041254</v>
+        <v>0.2747919115666675</v>
       </c>
       <c r="C168">
-        <v>0.3616720314041254</v>
+        <v>0.2747919115666675</v>
       </c>
       <c r="D168" t="s">
         <v>252</v>
@@ -5938,10 +5938,10 @@
         <v>174</v>
       </c>
       <c r="B169">
-        <v>0.3446755389533725</v>
+        <v>0.2745726050909509</v>
       </c>
       <c r="C169">
-        <v>0.3446755389533725</v>
+        <v>0.2745726050909509</v>
       </c>
       <c r="D169" t="s">
         <v>252</v>
@@ -5961,10 +5961,10 @@
         <v>175</v>
       </c>
       <c r="B170">
-        <v>0.3217735891837091</v>
+        <v>0.2642644325702156</v>
       </c>
       <c r="C170">
-        <v>0.3217735891837091</v>
+        <v>0.2642644325702156</v>
       </c>
       <c r="D170" t="s">
         <v>252</v>
@@ -5984,10 +5984,10 @@
         <v>176</v>
       </c>
       <c r="B171">
-        <v>0.1988521865343649</v>
+        <v>0.1325370394674327</v>
       </c>
       <c r="C171">
-        <v>0.1988521865343649</v>
+        <v>0.1325370394674327</v>
       </c>
       <c r="D171" t="s">
         <v>252</v>
@@ -6007,10 +6007,10 @@
         <v>177</v>
       </c>
       <c r="B172">
-        <v>0.5689439639341153</v>
+        <v>0.5574040981293495</v>
       </c>
       <c r="C172">
-        <v>0.5689439639341153</v>
+        <v>0.5574040981293495</v>
       </c>
       <c r="D172" t="s">
         <v>252</v>
@@ -6030,10 +6030,10 @@
         <v>178</v>
       </c>
       <c r="B173">
-        <v>0.5696399271064999</v>
+        <v>0.5605076768940984</v>
       </c>
       <c r="C173">
-        <v>0.5696399271064999</v>
+        <v>0.5605076768940984</v>
       </c>
       <c r="D173" t="s">
         <v>252</v>
@@ -6053,10 +6053,10 @@
         <v>179</v>
       </c>
       <c r="B174">
-        <v>0.7976217783846491</v>
+        <v>0.6839381234574877</v>
       </c>
       <c r="C174">
-        <v>0.7976217783846491</v>
+        <v>0.6839381234574877</v>
       </c>
       <c r="D174" t="s">
         <v>252</v>
@@ -6076,10 +6076,10 @@
         <v>180</v>
       </c>
       <c r="B175">
-        <v>0.9862697884587978</v>
+        <v>1.170482694116724</v>
       </c>
       <c r="C175">
-        <v>0.9862697884587978</v>
+        <v>1.170482694116724</v>
       </c>
       <c r="D175" t="s">
         <v>252</v>
@@ -6099,10 +6099,10 @@
         <v>181</v>
       </c>
       <c r="B176">
-        <v>1.070147019417754</v>
+        <v>1.131493896395644</v>
       </c>
       <c r="C176">
-        <v>1.070147019417754</v>
+        <v>1.131493896395644</v>
       </c>
       <c r="D176" t="s">
         <v>252</v>
@@ -6122,10 +6122,10 @@
         <v>182</v>
       </c>
       <c r="B177">
-        <v>1.884359081488862</v>
+        <v>2.624403006124212</v>
       </c>
       <c r="C177">
-        <v>1.884359081488862</v>
+        <v>2.624403006124212</v>
       </c>
       <c r="D177" t="s">
         <v>251</v>
@@ -6145,13 +6145,13 @@
         <v>183</v>
       </c>
       <c r="B178">
-        <v>0.9019259498410475</v>
+        <v>1.25245293398398</v>
       </c>
       <c r="C178">
-        <v>0.9019259498410475</v>
+        <v>1.25245293398398</v>
       </c>
       <c r="D178" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E178" t="s">
         <v>429</v>
@@ -6168,13 +6168,13 @@
         <v>184</v>
       </c>
       <c r="B179">
-        <v>1.179725002970204</v>
+        <v>1.369989823694028</v>
       </c>
       <c r="C179">
-        <v>1.179725002970204</v>
+        <v>1.369989823694028</v>
       </c>
       <c r="D179" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E179" t="s">
         <v>430</v>
@@ -6191,10 +6191,10 @@
         <v>185</v>
       </c>
       <c r="B180">
-        <v>0.818210812776218</v>
+        <v>0.7893420763133792</v>
       </c>
       <c r="C180">
-        <v>0.818210812776218</v>
+        <v>0.7893420763133792</v>
       </c>
       <c r="D180" t="s">
         <v>252</v>
@@ -6214,10 +6214,10 @@
         <v>186</v>
       </c>
       <c r="B181">
-        <v>0.6842416361882694</v>
+        <v>0.674857145117798</v>
       </c>
       <c r="C181">
-        <v>0.6842416361882694</v>
+        <v>0.674857145117798</v>
       </c>
       <c r="D181" t="s">
         <v>252</v>
@@ -6237,10 +6237,10 @@
         <v>187</v>
       </c>
       <c r="B182">
-        <v>0.7388510472993535</v>
+        <v>0.8008364003427096</v>
       </c>
       <c r="C182">
-        <v>0.7388510472993535</v>
+        <v>0.8008364003427096</v>
       </c>
       <c r="D182" t="s">
         <v>252</v>
@@ -6260,10 +6260,10 @@
         <v>188</v>
       </c>
       <c r="B183">
-        <v>2.14559469442563</v>
+        <v>2.483036958882385</v>
       </c>
       <c r="C183">
-        <v>2.14559469442563</v>
+        <v>2.483036958882385</v>
       </c>
       <c r="D183" t="s">
         <v>251</v>
@@ -6283,10 +6283,10 @@
         <v>189</v>
       </c>
       <c r="B184">
-        <v>1.586829791428348</v>
+        <v>1.860063481427304</v>
       </c>
       <c r="C184">
-        <v>1.586829791428348</v>
+        <v>1.860063481427304</v>
       </c>
       <c r="D184" t="s">
         <v>251</v>
@@ -6306,10 +6306,10 @@
         <v>190</v>
       </c>
       <c r="B185">
-        <v>0.1614780333049499</v>
+        <v>0.06174013967373879</v>
       </c>
       <c r="C185">
-        <v>0.1614780333049499</v>
+        <v>0.06174013967373879</v>
       </c>
       <c r="D185" t="s">
         <v>252</v>
@@ -6329,10 +6329,10 @@
         <v>191</v>
       </c>
       <c r="B186">
-        <v>0.3188759614097341</v>
+        <v>0.1434657075515622</v>
       </c>
       <c r="C186">
-        <v>0.3188759614097341</v>
+        <v>0.1434657075515622</v>
       </c>
       <c r="D186" t="s">
         <v>252</v>
@@ -6352,10 +6352,10 @@
         <v>192</v>
       </c>
       <c r="B187">
-        <v>0.3013961929485604</v>
+        <v>0.158041397501559</v>
       </c>
       <c r="C187">
-        <v>0.3013961929485604</v>
+        <v>0.158041397501559</v>
       </c>
       <c r="D187" t="s">
         <v>252</v>
@@ -6375,10 +6375,10 @@
         <v>193</v>
       </c>
       <c r="B188">
-        <v>0.5104389663020492</v>
+        <v>0.4570463824174807</v>
       </c>
       <c r="C188">
-        <v>0.5104389663020492</v>
+        <v>0.4570463824174807</v>
       </c>
       <c r="D188" t="s">
         <v>252</v>
@@ -6398,10 +6398,10 @@
         <v>194</v>
       </c>
       <c r="B189">
-        <v>1.475420576381739</v>
+        <v>1.974038538590118</v>
       </c>
       <c r="C189">
-        <v>1.475420576381739</v>
+        <v>1.974038538590118</v>
       </c>
       <c r="D189" t="s">
         <v>251</v>
@@ -6421,10 +6421,10 @@
         <v>195</v>
       </c>
       <c r="B190">
-        <v>2.923328151727987</v>
+        <v>4.079028428779192</v>
       </c>
       <c r="C190">
-        <v>2.923328151727987</v>
+        <v>4.079028428779192</v>
       </c>
       <c r="D190" t="s">
         <v>251</v>
@@ -6444,10 +6444,10 @@
         <v>196</v>
       </c>
       <c r="B191">
-        <v>2.397565674343954</v>
+        <v>3.404710981467263</v>
       </c>
       <c r="C191">
-        <v>2.397565674343954</v>
+        <v>3.404710981467263</v>
       </c>
       <c r="D191" t="s">
         <v>251</v>
@@ -6467,10 +6467,10 @@
         <v>197</v>
       </c>
       <c r="B192">
-        <v>1.563061655336474</v>
+        <v>2.136895839192944</v>
       </c>
       <c r="C192">
-        <v>1.563061655336474</v>
+        <v>2.136895839192944</v>
       </c>
       <c r="D192" t="s">
         <v>251</v>
@@ -6490,10 +6490,10 @@
         <v>198</v>
       </c>
       <c r="B193">
-        <v>0.376688203544541</v>
+        <v>0.338666290334658</v>
       </c>
       <c r="C193">
-        <v>0.376688203544541</v>
+        <v>0.338666290334658</v>
       </c>
       <c r="D193" t="s">
         <v>252</v>
@@ -6513,10 +6513,10 @@
         <v>199</v>
       </c>
       <c r="B194">
-        <v>3.80581278170723</v>
+        <v>3.507790738225422</v>
       </c>
       <c r="C194">
-        <v>3.80581278170723</v>
+        <v>3.507790738225422</v>
       </c>
       <c r="D194" t="s">
         <v>251</v>
@@ -6536,10 +6536,10 @@
         <v>200</v>
       </c>
       <c r="B195">
-        <v>0.1981190112773145</v>
+        <v>0.05830528853844494</v>
       </c>
       <c r="C195">
-        <v>0.1981190112773145</v>
+        <v>0.05830528853844494</v>
       </c>
       <c r="D195" t="s">
         <v>252</v>
@@ -6559,10 +6559,10 @@
         <v>201</v>
       </c>
       <c r="B196">
-        <v>0.406381757291338</v>
+        <v>0.2221410268447438</v>
       </c>
       <c r="C196">
-        <v>0.406381757291338</v>
+        <v>0.2221410268447438</v>
       </c>
       <c r="D196" t="s">
         <v>252</v>
@@ -6582,10 +6582,10 @@
         <v>202</v>
       </c>
       <c r="B197">
-        <v>0.3518899322823309</v>
+        <v>0.1708254641634057</v>
       </c>
       <c r="C197">
-        <v>0.3518899322823309</v>
+        <v>0.1708254641634057</v>
       </c>
       <c r="D197" t="s">
         <v>252</v>
@@ -6605,10 +6605,10 @@
         <v>203</v>
       </c>
       <c r="B198">
-        <v>0.6097859396082213</v>
+        <v>0.3402863605292384</v>
       </c>
       <c r="C198">
-        <v>0.6097859396082213</v>
+        <v>0.3402863605292384</v>
       </c>
       <c r="D198" t="s">
         <v>252</v>
@@ -6628,10 +6628,10 @@
         <v>204</v>
       </c>
       <c r="B199">
-        <v>0.3996122299553391</v>
+        <v>0.1847658415851018</v>
       </c>
       <c r="C199">
-        <v>0.3996122299553391</v>
+        <v>0.1847658415851018</v>
       </c>
       <c r="D199" t="s">
         <v>252</v>
@@ -6651,10 +6651,10 @@
         <v>205</v>
       </c>
       <c r="B200">
-        <v>1.045554335832944</v>
+        <v>1.174899580793792</v>
       </c>
       <c r="C200">
-        <v>1.045554335832944</v>
+        <v>1.174899580793792</v>
       </c>
       <c r="D200" t="s">
         <v>252</v>
@@ -6674,10 +6674,10 @@
         <v>206</v>
       </c>
       <c r="B201">
-        <v>3.283580159538675</v>
+        <v>4.212143933844713</v>
       </c>
       <c r="C201">
-        <v>3.283580159538675</v>
+        <v>4.212143933844713</v>
       </c>
       <c r="D201" t="s">
         <v>251</v>
@@ -6697,10 +6697,10 @@
         <v>207</v>
       </c>
       <c r="B202">
-        <v>2.507462909583045</v>
+        <v>2.750416072430102</v>
       </c>
       <c r="C202">
-        <v>2.507462909583045</v>
+        <v>2.750416072430102</v>
       </c>
       <c r="D202" t="s">
         <v>251</v>
@@ -6720,10 +6720,10 @@
         <v>208</v>
       </c>
       <c r="B203">
-        <v>1.913256730893455</v>
+        <v>2.657229944943594</v>
       </c>
       <c r="C203">
-        <v>1.913256730893455</v>
+        <v>2.657229944943594</v>
       </c>
       <c r="D203" t="s">
         <v>251</v>
@@ -6743,10 +6743,10 @@
         <v>209</v>
       </c>
       <c r="B204">
-        <v>2.126256744596708</v>
+        <v>2.674942530572557</v>
       </c>
       <c r="C204">
-        <v>2.126256744596708</v>
+        <v>2.674942530572557</v>
       </c>
       <c r="D204" t="s">
         <v>251</v>
@@ -6766,10 +6766,10 @@
         <v>210</v>
       </c>
       <c r="B205">
-        <v>2.067846362335033</v>
+        <v>2.93570024542958</v>
       </c>
       <c r="C205">
-        <v>2.067846362335033</v>
+        <v>2.93570024542958</v>
       </c>
       <c r="D205" t="s">
         <v>251</v>
@@ -6789,13 +6789,13 @@
         <v>211</v>
       </c>
       <c r="B206">
-        <v>1.119479338620849</v>
+        <v>1.457636108873456</v>
       </c>
       <c r="C206">
-        <v>1.119479338620849</v>
+        <v>1.457636108873456</v>
       </c>
       <c r="D206" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E206" t="s">
         <v>457</v>
@@ -6812,10 +6812,10 @@
         <v>212</v>
       </c>
       <c r="B207">
-        <v>2.009240498602042</v>
+        <v>2.920055947853339</v>
       </c>
       <c r="C207">
-        <v>2.009240498602042</v>
+        <v>2.920055947853339</v>
       </c>
       <c r="D207" t="s">
         <v>251</v>
@@ -6835,10 +6835,10 @@
         <v>213</v>
       </c>
       <c r="B208">
-        <v>1.652703653255336</v>
+        <v>2.320181855957014</v>
       </c>
       <c r="C208">
-        <v>1.652703653255336</v>
+        <v>2.320181855957014</v>
       </c>
       <c r="D208" t="s">
         <v>251</v>
@@ -6858,10 +6858,10 @@
         <v>214</v>
       </c>
       <c r="B209">
-        <v>2.168187659485925</v>
+        <v>2.876343623949713</v>
       </c>
       <c r="C209">
-        <v>2.168187659485925</v>
+        <v>2.876343623949713</v>
       </c>
       <c r="D209" t="s">
         <v>251</v>
@@ -6881,10 +6881,10 @@
         <v>215</v>
       </c>
       <c r="B210">
-        <v>2.839752059249172</v>
+        <v>4.299508580918023</v>
       </c>
       <c r="C210">
-        <v>2.839752059249172</v>
+        <v>4.299508580918023</v>
       </c>
       <c r="D210" t="s">
         <v>251</v>
@@ -6904,10 +6904,10 @@
         <v>216</v>
       </c>
       <c r="B211">
-        <v>1.809721902617147</v>
+        <v>1.992067144199189</v>
       </c>
       <c r="C211">
-        <v>1.809721902617147</v>
+        <v>1.992067144199189</v>
       </c>
       <c r="D211" t="s">
         <v>251</v>
@@ -6927,10 +6927,10 @@
         <v>217</v>
       </c>
       <c r="B212">
-        <v>0.1981799572578488</v>
+        <v>0.1191533210081152</v>
       </c>
       <c r="C212">
-        <v>0.1981799572578488</v>
+        <v>0.1191533210081152</v>
       </c>
       <c r="D212" t="s">
         <v>252</v>
@@ -6950,10 +6950,10 @@
         <v>218</v>
       </c>
       <c r="B213">
-        <v>0.276722096118986</v>
+        <v>0.1341771644727442</v>
       </c>
       <c r="C213">
-        <v>0.276722096118986</v>
+        <v>0.1341771644727442</v>
       </c>
       <c r="D213" t="s">
         <v>252</v>
@@ -6973,10 +6973,10 @@
         <v>219</v>
       </c>
       <c r="B214">
-        <v>0.1617796573084457</v>
+        <v>0.04619946501706433</v>
       </c>
       <c r="C214">
-        <v>0.1617796573084457</v>
+        <v>0.04619946501706433</v>
       </c>
       <c r="D214" t="s">
         <v>252</v>
@@ -6996,10 +6996,10 @@
         <v>220</v>
       </c>
       <c r="B215">
-        <v>0.4997036294960714</v>
+        <v>0.3457046067838714</v>
       </c>
       <c r="C215">
-        <v>0.4997036294960714</v>
+        <v>0.3457046067838714</v>
       </c>
       <c r="D215" t="s">
         <v>252</v>
@@ -7019,10 +7019,10 @@
         <v>221</v>
       </c>
       <c r="B216">
-        <v>0.4485530365341921</v>
+        <v>0.4429393136197105</v>
       </c>
       <c r="C216">
-        <v>0.4485530365341921</v>
+        <v>0.4429393136197105</v>
       </c>
       <c r="D216" t="s">
         <v>252</v>
@@ -7042,10 +7042,10 @@
         <v>222</v>
       </c>
       <c r="B217">
-        <v>1.21194703541521</v>
+        <v>1.428000441652872</v>
       </c>
       <c r="C217">
-        <v>1.21194703541521</v>
+        <v>1.428000441652872</v>
       </c>
       <c r="D217" t="s">
         <v>251</v>
@@ -7065,10 +7065,10 @@
         <v>223</v>
       </c>
       <c r="B218">
-        <v>2.017263891660435</v>
+        <v>2.597809385199542</v>
       </c>
       <c r="C218">
-        <v>2.017263891660435</v>
+        <v>2.597809385199542</v>
       </c>
       <c r="D218" t="s">
         <v>251</v>
@@ -7088,10 +7088,10 @@
         <v>224</v>
       </c>
       <c r="B219">
-        <v>0.2506646509293406</v>
+        <v>0.1493017943933463</v>
       </c>
       <c r="C219">
-        <v>0.2506646509293406</v>
+        <v>0.1493017943933463</v>
       </c>
       <c r="D219" t="s">
         <v>252</v>
@@ -7111,10 +7111,10 @@
         <v>225</v>
       </c>
       <c r="B220">
-        <v>2.166418301857287</v>
+        <v>2.398176658559211</v>
       </c>
       <c r="C220">
-        <v>2.166418301857287</v>
+        <v>2.398176658559211</v>
       </c>
       <c r="D220" t="s">
         <v>251</v>
@@ -7134,10 +7134,10 @@
         <v>226</v>
       </c>
       <c r="B221">
-        <v>0.6748452468923527</v>
+        <v>0.6957048782611481</v>
       </c>
       <c r="C221">
-        <v>0.6748452468923527</v>
+        <v>0.6957048782611481</v>
       </c>
       <c r="D221" t="s">
         <v>252</v>
@@ -7157,10 +7157,10 @@
         <v>227</v>
       </c>
       <c r="B222">
-        <v>0.206241838924159</v>
+        <v>0.095873828001104</v>
       </c>
       <c r="C222">
-        <v>0.206241838924159</v>
+        <v>0.095873828001104</v>
       </c>
       <c r="D222" t="s">
         <v>252</v>
@@ -7180,10 +7180,10 @@
         <v>228</v>
       </c>
       <c r="B223">
-        <v>0.3128461833275324</v>
+        <v>0.1770621832155221</v>
       </c>
       <c r="C223">
-        <v>0.3128461833275324</v>
+        <v>0.1770621832155221</v>
       </c>
       <c r="D223" t="s">
         <v>252</v>
@@ -7203,10 +7203,10 @@
         <v>229</v>
       </c>
       <c r="B224">
-        <v>0.2657078875949781</v>
+        <v>0.1161793984875268</v>
       </c>
       <c r="C224">
-        <v>0.2657078875949781</v>
+        <v>0.1161793984875268</v>
       </c>
       <c r="D224" t="s">
         <v>252</v>
@@ -7226,10 +7226,10 @@
         <v>230</v>
       </c>
       <c r="B225">
-        <v>1.157888166541531</v>
+        <v>0.9694107639934955</v>
       </c>
       <c r="C225">
-        <v>1.157888166541531</v>
+        <v>0.9694107639934955</v>
       </c>
       <c r="D225" t="s">
         <v>252</v>
@@ -7249,10 +7249,10 @@
         <v>231</v>
       </c>
       <c r="B226">
-        <v>0.2546266230547727</v>
+        <v>0.09799843272031414</v>
       </c>
       <c r="C226">
-        <v>0.2546266230547727</v>
+        <v>0.09799843272031414</v>
       </c>
       <c r="D226" t="s">
         <v>252</v>
@@ -7272,10 +7272,10 @@
         <v>232</v>
       </c>
       <c r="B227">
-        <v>0.3845460706736431</v>
+        <v>0.2796931613809269</v>
       </c>
       <c r="C227">
-        <v>0.3845460706736431</v>
+        <v>0.2796931613809269</v>
       </c>
       <c r="D227" t="s">
         <v>252</v>
@@ -7295,10 +7295,10 @@
         <v>233</v>
       </c>
       <c r="B228">
-        <v>1.53744586332613</v>
+        <v>1.701970377669855</v>
       </c>
       <c r="C228">
-        <v>1.53744586332613</v>
+        <v>1.701970377669855</v>
       </c>
       <c r="D228" t="s">
         <v>251</v>
@@ -7318,10 +7318,10 @@
         <v>234</v>
       </c>
       <c r="B229">
-        <v>1.901704016569898</v>
+        <v>2.784355390986033</v>
       </c>
       <c r="C229">
-        <v>1.901704016569898</v>
+        <v>2.784355390986033</v>
       </c>
       <c r="D229" t="s">
         <v>251</v>
@@ -7341,10 +7341,10 @@
         <v>235</v>
       </c>
       <c r="B230">
-        <v>2.847586156263175</v>
+        <v>4.394570381357205</v>
       </c>
       <c r="C230">
-        <v>2.847586156263175</v>
+        <v>4.394570381357205</v>
       </c>
       <c r="D230" t="s">
         <v>251</v>
@@ -7364,10 +7364,10 @@
         <v>236</v>
       </c>
       <c r="B231">
-        <v>0.5805746824975025</v>
+        <v>0.5616387572874715</v>
       </c>
       <c r="C231">
-        <v>0.5805746824975025</v>
+        <v>0.5616387572874715</v>
       </c>
       <c r="D231" t="s">
         <v>252</v>
@@ -7387,10 +7387,10 @@
         <v>237</v>
       </c>
       <c r="B232">
-        <v>0.3938039788361174</v>
+        <v>0.2150980172540043</v>
       </c>
       <c r="C232">
-        <v>0.3938039788361174</v>
+        <v>0.2150980172540043</v>
       </c>
       <c r="D232" t="s">
         <v>252</v>
@@ -7410,10 +7410,10 @@
         <v>238</v>
       </c>
       <c r="B233">
-        <v>0.7627801047354767</v>
+        <v>0.404402336960796</v>
       </c>
       <c r="C233">
-        <v>0.7627801047354767</v>
+        <v>0.404402336960796</v>
       </c>
       <c r="D233" t="s">
         <v>252</v>
@@ -7433,10 +7433,10 @@
         <v>239</v>
       </c>
       <c r="B234">
-        <v>0.2389021043175681</v>
+        <v>0.07926329835503224</v>
       </c>
       <c r="C234">
-        <v>0.2389021043175681</v>
+        <v>0.07926329835503224</v>
       </c>
       <c r="D234" t="s">
         <v>252</v>
@@ -7456,10 +7456,10 @@
         <v>240</v>
       </c>
       <c r="B235">
-        <v>0.1462381381999354</v>
+        <v>0.02455137445997722</v>
       </c>
       <c r="C235">
-        <v>0.1462381381999354</v>
+        <v>0.02455137445997722</v>
       </c>
       <c r="D235" t="s">
         <v>252</v>
@@ -7479,10 +7479,10 @@
         <v>241</v>
       </c>
       <c r="B236">
-        <v>0.2426531155041098</v>
+        <v>0.06918160299639438</v>
       </c>
       <c r="C236">
-        <v>0.2426531155041098</v>
+        <v>0.06918160299639438</v>
       </c>
       <c r="D236" t="s">
         <v>252</v>
@@ -7502,10 +7502,10 @@
         <v>242</v>
       </c>
       <c r="B237">
-        <v>0.4031541354566255</v>
+        <v>0.1857302628108379</v>
       </c>
       <c r="C237">
-        <v>0.4031541354566255</v>
+        <v>0.1857302628108379</v>
       </c>
       <c r="D237" t="s">
         <v>252</v>
@@ -7525,10 +7525,10 @@
         <v>243</v>
       </c>
       <c r="B238">
-        <v>1.141686886610116</v>
+        <v>0.8517406595290498</v>
       </c>
       <c r="C238">
-        <v>1.141686886610116</v>
+        <v>0.8517406595290498</v>
       </c>
       <c r="D238" t="s">
         <v>252</v>
@@ -7548,10 +7548,10 @@
         <v>244</v>
       </c>
       <c r="B239">
-        <v>0.2151785004880436</v>
+        <v>0.03776104275103793</v>
       </c>
       <c r="C239">
-        <v>0.2151785004880436</v>
+        <v>0.03776104275103793</v>
       </c>
       <c r="D239" t="s">
         <v>252</v>
@@ -7571,10 +7571,10 @@
         <v>245</v>
       </c>
       <c r="B240">
-        <v>2.682767748598091</v>
+        <v>1.283461503319148</v>
       </c>
       <c r="C240">
-        <v>2.682767748598091</v>
+        <v>1.283461503319148</v>
       </c>
       <c r="D240" t="s">
         <v>251</v>
@@ -7594,13 +7594,13 @@
         <v>246</v>
       </c>
       <c r="B241">
-        <v>3.194026854164585</v>
+        <v>0.7356144743738207</v>
       </c>
       <c r="C241">
-        <v>3.194026854164585</v>
+        <v>0.7356144743738207</v>
       </c>
       <c r="D241" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E241" t="s">
         <v>492</v>
@@ -7617,10 +7617,10 @@
         <v>247</v>
       </c>
       <c r="B242">
-        <v>0.2895092210775965</v>
+        <v>0.1482637754446995</v>
       </c>
       <c r="C242">
-        <v>0.2895092210775965</v>
+        <v>0.1482637754446995</v>
       </c>
       <c r="D242" t="s">
         <v>252</v>
@@ -7640,10 +7640,10 @@
         <v>248</v>
       </c>
       <c r="B243">
-        <v>0.2568121381485905</v>
+        <v>0.1129783004587131</v>
       </c>
       <c r="C243">
-        <v>0.2568121381485905</v>
+        <v>0.1129783004587131</v>
       </c>
       <c r="D243" t="s">
         <v>252</v>
@@ -7663,10 +7663,10 @@
         <v>249</v>
       </c>
       <c r="B244">
-        <v>0.2365235031498298</v>
+        <v>0.156429057930174</v>
       </c>
       <c r="C244">
-        <v>0.2365235031498298</v>
+        <v>0.156429057930174</v>
       </c>
       <c r="D244" t="s">
         <v>252</v>
@@ -7686,10 +7686,10 @@
         <v>250</v>
       </c>
       <c r="B245">
-        <v>0.2639118563389303</v>
+        <v>0.09330452373723186</v>
       </c>
       <c r="C245">
-        <v>0.2639118563389303</v>
+        <v>0.09330452373723186</v>
       </c>
       <c r="D245" t="s">
         <v>252</v>
@@ -7711,7 +7711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7739,48 +7739,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="B2">
-        <v>3.80581278170723</v>
+        <v>4.394570381357205</v>
       </c>
       <c r="C2">
-        <v>3.80581278170723</v>
+        <v>4.394570381357205</v>
       </c>
       <c r="D2" t="s">
         <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>445</v>
+        <v>481</v>
       </c>
       <c r="F2" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="G2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>215</v>
       </c>
       <c r="B3">
-        <v>3.297173999891045</v>
+        <v>4.299508580918023</v>
       </c>
       <c r="C3">
-        <v>3.297173999891045</v>
+        <v>4.299508580918023</v>
       </c>
       <c r="D3" t="s">
         <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>461</v>
       </c>
       <c r="F3" t="s">
-        <v>497</v>
+        <v>544</v>
       </c>
       <c r="G3" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -7788,10 +7788,10 @@
         <v>206</v>
       </c>
       <c r="B4">
-        <v>3.283580159538675</v>
+        <v>4.212143933844713</v>
       </c>
       <c r="C4">
-        <v>3.283580159538675</v>
+        <v>4.212143933844713</v>
       </c>
       <c r="D4" t="s">
         <v>251</v>
@@ -7808,229 +7808,229 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="B5">
-        <v>3.194026854164585</v>
+        <v>4.079028428779192</v>
       </c>
       <c r="C5">
-        <v>3.194026854164585</v>
+        <v>4.079028428779192</v>
       </c>
       <c r="D5" t="s">
         <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>492</v>
+        <v>441</v>
       </c>
       <c r="F5" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="G5" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>2.923328151727987</v>
+        <v>4.076886631703029</v>
       </c>
       <c r="C6">
-        <v>2.923328151727987</v>
+        <v>4.076886631703029</v>
       </c>
       <c r="D6" t="s">
         <v>251</v>
       </c>
       <c r="E6" t="s">
-        <v>441</v>
+        <v>253</v>
       </c>
       <c r="F6" t="s">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="G6" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="B7">
-        <v>2.847586156263175</v>
+        <v>3.507790738225422</v>
       </c>
       <c r="C7">
-        <v>2.847586156263175</v>
+        <v>3.507790738225422</v>
       </c>
       <c r="D7" t="s">
         <v>251</v>
       </c>
       <c r="E7" t="s">
-        <v>481</v>
+        <v>445</v>
       </c>
       <c r="F7" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="G7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>41</v>
       </c>
       <c r="B8">
-        <v>2.839752059249172</v>
+        <v>3.413817644083865</v>
       </c>
       <c r="C8">
-        <v>2.839752059249172</v>
+        <v>3.413817644083865</v>
       </c>
       <c r="D8" t="s">
         <v>251</v>
       </c>
       <c r="E8" t="s">
-        <v>461</v>
+        <v>287</v>
       </c>
       <c r="F8" t="s">
-        <v>544</v>
+        <v>506</v>
       </c>
       <c r="G8" t="s">
-        <v>542</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>196</v>
       </c>
       <c r="B9">
-        <v>2.682767748598091</v>
+        <v>3.404710981467263</v>
       </c>
       <c r="C9">
-        <v>2.682767748598091</v>
+        <v>3.404710981467263</v>
       </c>
       <c r="D9" t="s">
         <v>251</v>
       </c>
       <c r="E9" t="s">
-        <v>491</v>
+        <v>442</v>
       </c>
       <c r="F9" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="G9" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <v>2.507462909583045</v>
+        <v>3.105894377617302</v>
       </c>
       <c r="C10">
-        <v>2.507462909583045</v>
+        <v>3.105894377617302</v>
       </c>
       <c r="D10" t="s">
         <v>251</v>
       </c>
       <c r="E10" t="s">
-        <v>453</v>
+        <v>265</v>
       </c>
       <c r="F10" t="s">
-        <v>542</v>
+        <v>500</v>
       </c>
       <c r="G10" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B11">
-        <v>2.397565674343954</v>
+        <v>2.93570024542958</v>
       </c>
       <c r="C11">
-        <v>2.397565674343954</v>
+        <v>2.93570024542958</v>
       </c>
       <c r="D11" t="s">
         <v>251</v>
       </c>
       <c r="E11" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="F11" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="G11" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>212</v>
       </c>
       <c r="B12">
-        <v>2.354285281895629</v>
+        <v>2.920055947853339</v>
       </c>
       <c r="C12">
-        <v>2.354285281895629</v>
+        <v>2.920055947853339</v>
       </c>
       <c r="D12" t="s">
         <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>261</v>
+        <v>458</v>
       </c>
       <c r="F12" t="s">
-        <v>499</v>
+        <v>544</v>
       </c>
       <c r="G12" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>2.298858853714695</v>
+        <v>2.898550700965599</v>
       </c>
       <c r="C13">
-        <v>2.298858853714695</v>
+        <v>2.898550700965599</v>
       </c>
       <c r="D13" t="s">
         <v>251</v>
       </c>
       <c r="E13" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="F13" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="G13" t="s">
-        <v>503</v>
+        <v>558</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>2.295108353133979</v>
+        <v>2.895962996427035</v>
       </c>
       <c r="C14">
-        <v>2.295108353133979</v>
+        <v>2.895962996427035</v>
       </c>
       <c r="D14" t="s">
         <v>251</v>
       </c>
       <c r="E14" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F14" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G14" t="s">
         <v>558</v>
@@ -8038,68 +8038,68 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>214</v>
       </c>
       <c r="B15">
-        <v>2.1826293124072</v>
+        <v>2.876343623949713</v>
       </c>
       <c r="C15">
-        <v>2.1826293124072</v>
+        <v>2.876343623949713</v>
       </c>
       <c r="D15" t="s">
         <v>251</v>
       </c>
       <c r="E15" t="s">
-        <v>257</v>
+        <v>460</v>
       </c>
       <c r="F15" t="s">
-        <v>498</v>
+        <v>544</v>
       </c>
       <c r="G15" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>2.168187659485925</v>
+        <v>2.821053068360476</v>
       </c>
       <c r="C16">
-        <v>2.168187659485925</v>
+        <v>2.821053068360476</v>
       </c>
       <c r="D16" t="s">
         <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>460</v>
+        <v>259</v>
       </c>
       <c r="F16" t="s">
-        <v>544</v>
+        <v>498</v>
       </c>
       <c r="G16" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B17">
-        <v>2.166418301857287</v>
+        <v>2.784355390986033</v>
       </c>
       <c r="C17">
-        <v>2.166418301857287</v>
+        <v>2.784355390986033</v>
       </c>
       <c r="D17" t="s">
         <v>251</v>
       </c>
       <c r="E17" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="F17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G17" t="s">
         <v>542</v>
@@ -8107,88 +8107,88 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>188</v>
+        <v>39</v>
       </c>
       <c r="B18">
-        <v>2.14559469442563</v>
+        <v>2.783005555764028</v>
       </c>
       <c r="C18">
-        <v>2.14559469442563</v>
+        <v>2.783005555764028</v>
       </c>
       <c r="D18" t="s">
         <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>434</v>
+        <v>285</v>
       </c>
       <c r="F18" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="G18" t="s">
-        <v>539</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>209</v>
+        <v>94</v>
       </c>
       <c r="B19">
-        <v>2.126256744596708</v>
+        <v>2.781130022560588</v>
       </c>
       <c r="C19">
-        <v>2.126256744596708</v>
+        <v>2.781130022560588</v>
       </c>
       <c r="D19" t="s">
         <v>251</v>
       </c>
       <c r="E19" t="s">
-        <v>455</v>
+        <v>340</v>
       </c>
       <c r="F19" t="s">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="G19" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="B20">
-        <v>2.113843492718625</v>
+        <v>2.750416072430102</v>
       </c>
       <c r="C20">
-        <v>2.113843492718625</v>
+        <v>2.750416072430102</v>
       </c>
       <c r="D20" t="s">
         <v>251</v>
       </c>
       <c r="E20" t="s">
-        <v>259</v>
+        <v>453</v>
       </c>
       <c r="F20" t="s">
-        <v>498</v>
+        <v>542</v>
       </c>
       <c r="G20" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21">
-        <v>2.067846362335033</v>
+        <v>2.674942530572557</v>
       </c>
       <c r="C21">
-        <v>2.067846362335033</v>
+        <v>2.674942530572557</v>
       </c>
       <c r="D21" t="s">
         <v>251</v>
       </c>
       <c r="E21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F21" t="s">
         <v>543</v>
@@ -8199,68 +8199,68 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>208</v>
       </c>
       <c r="B22">
-        <v>2.023133253806931</v>
+        <v>2.657229944943594</v>
       </c>
       <c r="C22">
-        <v>2.023133253806931</v>
+        <v>2.657229944943594</v>
       </c>
       <c r="D22" t="s">
         <v>251</v>
       </c>
       <c r="E22" t="s">
-        <v>255</v>
+        <v>454</v>
       </c>
       <c r="F22" t="s">
-        <v>497</v>
+        <v>543</v>
       </c>
       <c r="G22" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="B23">
-        <v>2.017263891660435</v>
+        <v>2.624403006124212</v>
       </c>
       <c r="C23">
-        <v>2.017263891660435</v>
+        <v>2.624403006124212</v>
       </c>
       <c r="D23" t="s">
         <v>251</v>
       </c>
       <c r="E23" t="s">
-        <v>469</v>
+        <v>428</v>
       </c>
       <c r="F23" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="G23" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B24">
-        <v>2.009240498602042</v>
+        <v>2.597809385199542</v>
       </c>
       <c r="C24">
-        <v>2.009240498602042</v>
+        <v>2.597809385199542</v>
       </c>
       <c r="D24" t="s">
         <v>251</v>
       </c>
       <c r="E24" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="F24" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G24" t="s">
         <v>542</v>
@@ -8268,160 +8268,160 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B25">
-        <v>1.977295530443556</v>
+        <v>2.593733379489021</v>
       </c>
       <c r="C25">
-        <v>1.977295530443556</v>
+        <v>2.593733379489021</v>
       </c>
       <c r="D25" t="s">
         <v>251</v>
       </c>
       <c r="E25" t="s">
-        <v>340</v>
+        <v>293</v>
       </c>
       <c r="F25" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="G25" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B26">
-        <v>1.951687028201299</v>
+        <v>2.583523628311352</v>
       </c>
       <c r="C26">
-        <v>1.951687028201299</v>
+        <v>2.583523628311352</v>
       </c>
       <c r="D26" t="s">
         <v>251</v>
       </c>
       <c r="E26" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="F26" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="G26" t="s">
-        <v>558</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="B27">
-        <v>1.913256730893455</v>
+        <v>2.483036958882385</v>
       </c>
       <c r="C27">
-        <v>1.913256730893455</v>
+        <v>2.483036958882385</v>
       </c>
       <c r="D27" t="s">
         <v>251</v>
       </c>
       <c r="E27" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="F27" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="G27" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>234</v>
+        <v>35</v>
       </c>
       <c r="B28">
-        <v>1.901704016569898</v>
+        <v>2.480959678743628</v>
       </c>
       <c r="C28">
-        <v>1.901704016569898</v>
+        <v>2.480959678743628</v>
       </c>
       <c r="D28" t="s">
         <v>251</v>
       </c>
       <c r="E28" t="s">
-        <v>480</v>
+        <v>281</v>
       </c>
       <c r="F28" t="s">
-        <v>547</v>
+        <v>504</v>
       </c>
       <c r="G28" t="s">
-        <v>542</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="B29">
-        <v>1.884359081488862</v>
+        <v>2.43150088688448</v>
       </c>
       <c r="C29">
-        <v>1.884359081488862</v>
+        <v>2.43150088688448</v>
       </c>
       <c r="D29" t="s">
         <v>251</v>
       </c>
       <c r="E29" t="s">
-        <v>428</v>
+        <v>318</v>
       </c>
       <c r="F29" t="s">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="G29" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="B30">
-        <v>1.881413442010019</v>
+        <v>2.426874559313921</v>
       </c>
       <c r="C30">
-        <v>1.881413442010019</v>
+        <v>2.426874559313921</v>
       </c>
       <c r="D30" t="s">
         <v>251</v>
       </c>
       <c r="E30" t="s">
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="F30" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="G30" t="s">
-        <v>503</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B31">
-        <v>1.875270179428823</v>
+        <v>2.406267830178428</v>
       </c>
       <c r="C31">
-        <v>1.875270179428823</v>
+        <v>2.406267830178428</v>
       </c>
       <c r="D31" t="s">
         <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F31" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G31" t="s">
         <v>510</v>
@@ -8429,22 +8429,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B32">
-        <v>1.809721902617147</v>
+        <v>2.398176658559211</v>
       </c>
       <c r="C32">
-        <v>1.809721902617147</v>
+        <v>2.398176658559211</v>
       </c>
       <c r="D32" t="s">
         <v>251</v>
       </c>
       <c r="E32" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="F32" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G32" t="s">
         <v>542</v>
@@ -8452,88 +8452,88 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="B33">
-        <v>1.652703653255336</v>
+        <v>2.397505475294293</v>
       </c>
       <c r="C33">
-        <v>1.652703653255336</v>
+        <v>2.397505475294293</v>
       </c>
       <c r="D33" t="s">
         <v>251</v>
       </c>
       <c r="E33" t="s">
-        <v>459</v>
+        <v>255</v>
       </c>
       <c r="F33" t="s">
-        <v>544</v>
+        <v>497</v>
       </c>
       <c r="G33" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>213</v>
       </c>
       <c r="B34">
-        <v>1.632961284307301</v>
+        <v>2.320181855957014</v>
       </c>
       <c r="C34">
-        <v>1.632961284307301</v>
+        <v>2.320181855957014</v>
       </c>
       <c r="D34" t="s">
         <v>251</v>
       </c>
       <c r="E34" t="s">
-        <v>344</v>
+        <v>459</v>
       </c>
       <c r="F34" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
       <c r="G34" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="B35">
-        <v>1.62622438559785</v>
+        <v>2.27306014455962</v>
       </c>
       <c r="C35">
-        <v>1.62622438559785</v>
+        <v>2.27306014455962</v>
       </c>
       <c r="D35" t="s">
         <v>251</v>
       </c>
       <c r="E35" t="s">
-        <v>413</v>
+        <v>344</v>
       </c>
       <c r="F35" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="G35" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36">
-        <v>1.624613533381907</v>
+        <v>2.269290249882573</v>
       </c>
       <c r="C36">
-        <v>1.624613533381907</v>
+        <v>2.269290249882573</v>
       </c>
       <c r="D36" t="s">
         <v>251</v>
       </c>
       <c r="E36" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F36" t="s">
         <v>504</v>
@@ -8544,111 +8544,111 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="B37">
-        <v>1.621484436044065</v>
+        <v>2.206819639078817</v>
       </c>
       <c r="C37">
-        <v>1.621484436044065</v>
+        <v>2.206819639078817</v>
       </c>
       <c r="D37" t="s">
         <v>251</v>
       </c>
       <c r="E37" t="s">
-        <v>289</v>
+        <v>343</v>
       </c>
       <c r="F37" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="G37" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="B38">
-        <v>1.611424613069323</v>
+        <v>2.136895839192944</v>
       </c>
       <c r="C38">
-        <v>1.611424613069323</v>
+        <v>2.136895839192944</v>
       </c>
       <c r="D38" t="s">
         <v>251</v>
       </c>
       <c r="E38" t="s">
-        <v>322</v>
+        <v>443</v>
       </c>
       <c r="F38" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="G38" t="s">
-        <v>510</v>
+        <v>539</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="B39">
-        <v>1.588157448170999</v>
+        <v>2.015549077554859</v>
       </c>
       <c r="C39">
-        <v>1.588157448170999</v>
+        <v>2.015549077554859</v>
       </c>
       <c r="D39" t="s">
         <v>251</v>
       </c>
       <c r="E39" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="F39" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G39" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="B40">
-        <v>1.586829791428348</v>
+        <v>1.992067144199189</v>
       </c>
       <c r="C40">
-        <v>1.586829791428348</v>
+        <v>1.992067144199189</v>
       </c>
       <c r="D40" t="s">
         <v>251</v>
       </c>
       <c r="E40" t="s">
-        <v>435</v>
+        <v>462</v>
       </c>
       <c r="F40" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="G40" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B41">
-        <v>1.563061655336474</v>
+        <v>1.974038538590118</v>
       </c>
       <c r="C41">
-        <v>1.563061655336474</v>
+        <v>1.974038538590118</v>
       </c>
       <c r="D41" t="s">
         <v>251</v>
       </c>
       <c r="E41" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F41" t="s">
         <v>539</v>
@@ -8659,45 +8659,45 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="B42">
-        <v>1.561722461493026</v>
+        <v>1.94837138683733</v>
       </c>
       <c r="C42">
-        <v>1.561722461493026</v>
+        <v>1.94837138683733</v>
       </c>
       <c r="D42" t="s">
         <v>251</v>
       </c>
       <c r="E42" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
       <c r="F42" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="G42" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B43">
-        <v>1.550695168320296</v>
+        <v>1.923645628203002</v>
       </c>
       <c r="C43">
-        <v>1.550695168320296</v>
+        <v>1.923645628203002</v>
       </c>
       <c r="D43" t="s">
         <v>251</v>
       </c>
       <c r="E43" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F43" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G43" t="s">
         <v>518</v>
@@ -8705,22 +8705,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B44">
-        <v>1.539841802840974</v>
+        <v>1.890220073918943</v>
       </c>
       <c r="C44">
-        <v>1.539841802840974</v>
+        <v>1.890220073918943</v>
       </c>
       <c r="D44" t="s">
         <v>251</v>
       </c>
       <c r="E44" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F44" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G44" t="s">
         <v>503</v>
@@ -8728,68 +8728,68 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>233</v>
+        <v>45</v>
       </c>
       <c r="B45">
-        <v>1.53744586332613</v>
+        <v>1.862018653082905</v>
       </c>
       <c r="C45">
-        <v>1.53744586332613</v>
+        <v>1.862018653082905</v>
       </c>
       <c r="D45" t="s">
         <v>251</v>
       </c>
       <c r="E45" t="s">
-        <v>479</v>
+        <v>291</v>
       </c>
       <c r="F45" t="s">
-        <v>547</v>
+        <v>507</v>
       </c>
       <c r="G45" t="s">
-        <v>542</v>
+        <v>503</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="B46">
-        <v>1.490929959248393</v>
+        <v>1.860063481427304</v>
       </c>
       <c r="C46">
-        <v>1.490929959248393</v>
+        <v>1.860063481427304</v>
       </c>
       <c r="D46" t="s">
         <v>251</v>
       </c>
       <c r="E46" t="s">
-        <v>327</v>
+        <v>435</v>
       </c>
       <c r="F46" t="s">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="G46" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B47">
-        <v>1.48070341252915</v>
+        <v>1.853849805299328</v>
       </c>
       <c r="C47">
-        <v>1.48070341252915</v>
+        <v>1.853849805299328</v>
       </c>
       <c r="D47" t="s">
         <v>251</v>
       </c>
       <c r="E47" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="F47" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G47" t="s">
         <v>518</v>
@@ -8797,45 +8797,45 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>194</v>
+        <v>75</v>
       </c>
       <c r="B48">
-        <v>1.475420576381739</v>
+        <v>1.841368755035201</v>
       </c>
       <c r="C48">
-        <v>1.475420576381739</v>
+        <v>1.841368755035201</v>
       </c>
       <c r="D48" t="s">
         <v>251</v>
       </c>
       <c r="E48" t="s">
-        <v>440</v>
+        <v>321</v>
       </c>
       <c r="F48" t="s">
-        <v>539</v>
+        <v>514</v>
       </c>
       <c r="G48" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="B49">
-        <v>1.379777881810632</v>
+        <v>1.840739593500203</v>
       </c>
       <c r="C49">
-        <v>1.379777881810632</v>
+        <v>1.840739593500203</v>
       </c>
       <c r="D49" t="s">
         <v>251</v>
       </c>
       <c r="E49" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="F49" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G49" t="s">
         <v>518</v>
@@ -8843,42 +8843,42 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B50">
-        <v>1.363450063127189</v>
+        <v>1.746769899134736</v>
       </c>
       <c r="C50">
-        <v>1.363450063127189</v>
+        <v>1.746769899134736</v>
       </c>
       <c r="D50" t="s">
         <v>251</v>
       </c>
       <c r="E50" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="F50" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="G50" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51">
-        <v>1.357610882003726</v>
+        <v>1.72689368240064</v>
       </c>
       <c r="C51">
-        <v>1.357610882003726</v>
+        <v>1.72689368240064</v>
       </c>
       <c r="D51" t="s">
         <v>251</v>
       </c>
       <c r="E51" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F51" t="s">
         <v>507</v>
@@ -8889,91 +8889,91 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="B52">
-        <v>1.346530819642678</v>
+        <v>1.71371884517039</v>
       </c>
       <c r="C52">
-        <v>1.346530819642678</v>
+        <v>1.71371884517039</v>
       </c>
       <c r="D52" t="s">
         <v>251</v>
       </c>
       <c r="E52" t="s">
-        <v>324</v>
+        <v>413</v>
       </c>
       <c r="F52" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="G52" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="B53">
-        <v>1.329911821546185</v>
+        <v>1.701970377669855</v>
       </c>
       <c r="C53">
-        <v>1.329911821546185</v>
+        <v>1.701970377669855</v>
       </c>
       <c r="D53" t="s">
         <v>251</v>
       </c>
       <c r="E53" t="s">
-        <v>326</v>
+        <v>479</v>
       </c>
       <c r="F53" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="G53" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
       <c r="B54">
-        <v>1.326327330829845</v>
+        <v>1.671374250404086</v>
       </c>
       <c r="C54">
-        <v>1.326327330829845</v>
+        <v>1.671374250404086</v>
       </c>
       <c r="D54" t="s">
         <v>251</v>
       </c>
       <c r="E54" t="s">
-        <v>407</v>
+        <v>335</v>
       </c>
       <c r="F54" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="G54" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B55">
-        <v>1.307456276708541</v>
+        <v>1.663153021978641</v>
       </c>
       <c r="C55">
-        <v>1.307456276708541</v>
+        <v>1.663153021978641</v>
       </c>
       <c r="D55" t="s">
         <v>251</v>
       </c>
       <c r="E55" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="F55" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G55" t="s">
         <v>518</v>
@@ -8981,68 +8981,68 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>165</v>
       </c>
       <c r="B56">
-        <v>1.30221716199086</v>
+        <v>1.63252545277109</v>
       </c>
       <c r="C56">
-        <v>1.30221716199086</v>
+        <v>1.63252545277109</v>
       </c>
       <c r="D56" t="s">
         <v>251</v>
       </c>
       <c r="E56" t="s">
-        <v>335</v>
+        <v>411</v>
       </c>
       <c r="F56" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="G56" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="B57">
-        <v>1.289585902909272</v>
+        <v>1.610854575447449</v>
       </c>
       <c r="C57">
-        <v>1.289585902909272</v>
+        <v>1.610854575447449</v>
       </c>
       <c r="D57" t="s">
         <v>251</v>
       </c>
       <c r="E57" t="s">
-        <v>411</v>
+        <v>320</v>
       </c>
       <c r="F57" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="G57" t="s">
-        <v>532</v>
+        <v>510</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B58">
-        <v>1.254833717355365</v>
+        <v>1.545969569952652</v>
       </c>
       <c r="C58">
-        <v>1.254833717355365</v>
+        <v>1.545969569952652</v>
       </c>
       <c r="D58" t="s">
         <v>251</v>
       </c>
       <c r="E58" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="F58" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G58" t="s">
         <v>503</v>
@@ -9050,22 +9050,22 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B59">
-        <v>1.240218885772566</v>
+        <v>1.51332134456899</v>
       </c>
       <c r="C59">
-        <v>1.240218885772566</v>
+        <v>1.51332134456899</v>
       </c>
       <c r="D59" t="s">
         <v>251</v>
       </c>
       <c r="E59" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F59" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G59" t="s">
         <v>518</v>
@@ -9073,48 +9073,324 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="B60">
-        <v>1.21194703541521</v>
+        <v>1.478134440861248</v>
       </c>
       <c r="C60">
-        <v>1.21194703541521</v>
+        <v>1.478134440861248</v>
       </c>
       <c r="D60" t="s">
         <v>251</v>
       </c>
       <c r="E60" t="s">
-        <v>468</v>
+        <v>325</v>
       </c>
       <c r="F60" t="s">
-        <v>545</v>
+        <v>515</v>
       </c>
       <c r="G60" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
+        <v>211</v>
+      </c>
+      <c r="B61">
+        <v>1.457636108873456</v>
+      </c>
+      <c r="C61">
+        <v>1.457636108873456</v>
+      </c>
+      <c r="D61" t="s">
+        <v>251</v>
+      </c>
+      <c r="E61" t="s">
+        <v>457</v>
+      </c>
+      <c r="F61" t="s">
+        <v>543</v>
+      </c>
+      <c r="G61" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>161</v>
+      </c>
+      <c r="B62">
+        <v>1.451260442358216</v>
+      </c>
+      <c r="C62">
+        <v>1.451260442358216</v>
+      </c>
+      <c r="D62" t="s">
+        <v>251</v>
+      </c>
+      <c r="E62" t="s">
+        <v>407</v>
+      </c>
+      <c r="F62" t="s">
+        <v>531</v>
+      </c>
+      <c r="G62" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>222</v>
+      </c>
+      <c r="B63">
+        <v>1.428000441652872</v>
+      </c>
+      <c r="C63">
+        <v>1.428000441652872</v>
+      </c>
+      <c r="D63" t="s">
+        <v>251</v>
+      </c>
+      <c r="E63" t="s">
+        <v>468</v>
+      </c>
+      <c r="F63" t="s">
+        <v>545</v>
+      </c>
+      <c r="G63" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64">
+        <v>1.427568808689359</v>
+      </c>
+      <c r="C64">
+        <v>1.427568808689359</v>
+      </c>
+      <c r="D64" t="s">
+        <v>251</v>
+      </c>
+      <c r="E64" t="s">
+        <v>334</v>
+      </c>
+      <c r="F64" t="s">
+        <v>517</v>
+      </c>
+      <c r="G64" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
         <v>64</v>
       </c>
-      <c r="B61">
-        <v>1.20161501879365</v>
-      </c>
-      <c r="C61">
-        <v>1.20161501879365</v>
-      </c>
-      <c r="D61" t="s">
-        <v>251</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="B65">
+        <v>1.386970361017914</v>
+      </c>
+      <c r="C65">
+        <v>1.386970361017914</v>
+      </c>
+      <c r="D65" t="s">
+        <v>251</v>
+      </c>
+      <c r="E65" t="s">
         <v>310</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F65" t="s">
         <v>511</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G65" t="s">
         <v>510</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>184</v>
+      </c>
+      <c r="B66">
+        <v>1.369989823694028</v>
+      </c>
+      <c r="C66">
+        <v>1.369989823694028</v>
+      </c>
+      <c r="D66" t="s">
+        <v>251</v>
+      </c>
+      <c r="E66" t="s">
+        <v>430</v>
+      </c>
+      <c r="F66" t="s">
+        <v>536</v>
+      </c>
+      <c r="G66" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67">
+        <v>1.327083620851751</v>
+      </c>
+      <c r="C67">
+        <v>1.327083620851751</v>
+      </c>
+      <c r="D67" t="s">
+        <v>251</v>
+      </c>
+      <c r="E67" t="s">
+        <v>262</v>
+      </c>
+      <c r="F67" t="s">
+        <v>499</v>
+      </c>
+      <c r="G67" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68">
+        <v>1.292575691484285</v>
+      </c>
+      <c r="C68">
+        <v>1.292575691484285</v>
+      </c>
+      <c r="D68" t="s">
+        <v>251</v>
+      </c>
+      <c r="E68" t="s">
+        <v>345</v>
+      </c>
+      <c r="F68" t="s">
+        <v>520</v>
+      </c>
+      <c r="G68" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>245</v>
+      </c>
+      <c r="B69">
+        <v>1.283461503319148</v>
+      </c>
+      <c r="C69">
+        <v>1.283461503319148</v>
+      </c>
+      <c r="D69" t="s">
+        <v>251</v>
+      </c>
+      <c r="E69" t="s">
+        <v>491</v>
+      </c>
+      <c r="F69" t="s">
+        <v>552</v>
+      </c>
+      <c r="G69" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B70">
+        <v>1.265892252606359</v>
+      </c>
+      <c r="C70">
+        <v>1.265892252606359</v>
+      </c>
+      <c r="D70" t="s">
+        <v>251</v>
+      </c>
+      <c r="E70" t="s">
+        <v>266</v>
+      </c>
+      <c r="F70" t="s">
+        <v>500</v>
+      </c>
+      <c r="G70" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>183</v>
+      </c>
+      <c r="B71">
+        <v>1.25245293398398</v>
+      </c>
+      <c r="C71">
+        <v>1.25245293398398</v>
+      </c>
+      <c r="D71" t="s">
+        <v>251</v>
+      </c>
+      <c r="E71" t="s">
+        <v>429</v>
+      </c>
+      <c r="F71" t="s">
+        <v>536</v>
+      </c>
+      <c r="G71" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72">
+        <v>1.22698503348356</v>
+      </c>
+      <c r="C72">
+        <v>1.22698503348356</v>
+      </c>
+      <c r="D72" t="s">
+        <v>251</v>
+      </c>
+      <c r="E72" t="s">
+        <v>328</v>
+      </c>
+      <c r="F72" t="s">
+        <v>516</v>
+      </c>
+      <c r="G72" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73">
+        <v>1.224971950771618</v>
+      </c>
+      <c r="C73">
+        <v>1.224971950771618</v>
+      </c>
+      <c r="D73" t="s">
+        <v>251</v>
+      </c>
+      <c r="E73" t="s">
+        <v>401</v>
+      </c>
+      <c r="F73" t="s">
+        <v>529</v>
+      </c>
+      <c r="G73" t="s">
+        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_dinamica_hotspots.xlsx
+++ b/outputs/tables/tabla_dinamica_hotspots.xlsx
@@ -11,13 +11,14 @@
     <sheet name="Hotspots Persistentes" sheetId="2" r:id="rId2"/>
     <sheet name="Hotspots Emergentes" sheetId="3" r:id="rId3"/>
     <sheet name="Hotspots en Declive" sheetId="4" r:id="rId4"/>
+    <sheet name="Nota_Metodologica_Limitacion" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="574">
   <si>
     <t>cod_subcircu</t>
   </si>
@@ -1709,6 +1710,36 @@
   </si>
   <si>
     <t>PLAYAS</t>
+  </si>
+  <si>
+    <t>Aspecto_Metodologico</t>
+  </si>
+  <si>
+    <t>Detalle</t>
+  </si>
+  <si>
+    <t>Estructura del Modelo Espacio-Temporal</t>
+  </si>
+  <si>
+    <t>Ausencia de Interacción Espacio-Temporal (delta_{it})</t>
+  </si>
+  <si>
+    <t>Implicación sobre la Clasificación Dinámica</t>
+  </si>
+  <si>
+    <t>Declaración Formal en la Tesis</t>
+  </si>
+  <si>
+    <t>El modelo bayesiano espacio-temporal implementado posee una formulación aditiva: log(mu_{it}) = alpha + beta_year * I(t=2025) + beta_area * log(Area_i) + phi_i.</t>
+  </si>
+  <si>
+    <t>El modelo no incluye un término de interacción espacio-temporal delta_{it} (Knorr-Held, 2000). Por consiguiente, el riesgo relativo espacial de cada subcircuito relativo a la media cantonal es constante en el tiempo: RR_{i, 2024} = RR_{i, 2025} (ej. Guasmo 1 tiene 4.077 en ambos años).</t>
+  </si>
+  <si>
+    <t>Dado que RR_{i, 2024} == RR_{i, 2025}, todo subcircuito con RR &gt;= 1.2 es catalogado como "HOTSPOT PERSISTENTE" y no existen subcircuitos emergentes o en declive. La clasificación dinámica no aporta información temporal diferencial y debe interpretarse como una partición estática del riesgo.</t>
+  </si>
+  <si>
+    <t>Esta propiedad se documenta explícitamente en la tesis como una limitación metodológica del modelo aditivo y se recomienda la incorporación de términos de interacción Knorr-Held tipo I-IV en trabajos futuros.</t>
   </si>
 </sst>
 </file>
@@ -9462,4 +9493,54 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B4" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>569</v>
+      </c>
+      <c r="B5" t="s">
+        <v>573</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>